--- a/outputs/research-model-evaluation-20260928/research-model-comparison.xlsx
+++ b/outputs/research-model-evaluation-20260928/research-model-comparison.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="1" r:id="R211858b9743d40b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costs" sheetId="2" r:id="Rb5941ddcbaf04c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="3" r:id="R2c689b01eb564984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality" sheetId="4" r:id="R108edd6543424708"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failures" sheetId="5" r:id="R181dfdbbb484409b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="6" r:id="Rac0103970d2b43db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trace metrics" sheetId="7" r:id="R77dc1fd8556d4397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="8" r:id="Rb59eff92043a439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="1" r:id="R3ae7e55b6e0a4d4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costs" sheetId="2" r:id="R3de177a5c0b6430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="3" r:id="R344143695932428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality" sheetId="4" r:id="R1335320c615c4fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failures" sheetId="5" r:id="Ra5dd00000f0d41b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="6" r:id="R4a378d9e3f634f78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trace metrics" sheetId="7" r:id="R325544a3bf544c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="8" r:id="Ra6a9daa03da5417e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -68,7 +68,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -100,6 +100,16 @@
         <x:fgColor rgb="FFDCE9E2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F6FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE9E2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -107,7 +117,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -189,6 +199,37 @@
     <x:xf numFmtId="206" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -197,7 +238,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RunsTable" displayName="RunsTable" ref="A5:L16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RunsTable" displayName="RunsTable" ref="A5:L18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Run"/>
     <x:tableColumn id="2" name="Seller / account"/>
@@ -217,7 +258,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CostsTable" displayName="CostsTable" ref="A5:M17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CostsTable" displayName="CostsTable" ref="A5:M19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="Run"/>
     <x:tableColumn id="2" name="Researcher USD"/>
@@ -238,7 +279,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="JobsTable" displayName="JobsTable" ref="A5:O31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="JobsTable" displayName="JobsTable" ref="A5:O37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="Run"/>
     <x:tableColumn id="2" name="Entity"/>
@@ -261,7 +302,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="QualityTable" displayName="QualityTable" ref="A5:G79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="QualityTable" displayName="QualityTable" ref="A5:G103" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Run"/>
     <x:tableColumn id="2" name="Evidence / behavior"/>
@@ -276,7 +317,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FailuresTable" displayName="FailuresTable" ref="A5:F39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FailuresTable" displayName="FailuresTable" ref="A5:F45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Run"/>
     <x:tableColumn id="2" name="Entity / stage"/>
@@ -290,7 +331,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="OutputsTable" displayName="OutputsTable" ref="A5:F356" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="OutputsTable" displayName="OutputsTable" ref="A5:F405" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Run"/>
     <x:tableColumn id="2" name="Entity / scope"/>
@@ -304,7 +345,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TracemetricsTable" displayName="TracemetricsTable" ref="A5:K31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TracemetricsTable" displayName="TracemetricsTable" ref="A5:K37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Run"/>
     <x:tableColumn id="2" name="Entity"/>
@@ -323,7 +364,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="MethodTable" displayName="MethodTable" ref="A5:B21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="MethodTable" displayName="MethodTable" ref="A5:B23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Topic"/>
     <x:tableColumn id="2" name="Definition / interpretation"/>
@@ -562,7 +603,7 @@
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="7" t="str">
-        <v>11 research attempts across two seller/account pairs. Recorded USD and AI Ark credits are separate. Research wall includes research through final job outcome; total observed also includes later reconciliation or cancellation. Overlapping jobs are not added.</v>
+        <v>13 research attempts across two seller/account pairs. Z7 adds the latest Muse xhigh quality review; Z8 records the GLM retry with different people. Recorded USD and AI Ark credits are separate. Jobs overlap; total observed includes reconciliation.</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1076,2005 +1117,2453 @@
         <v>Open report</v>
       </c>
     </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B17" s="31" t="str">
+        <v>Clue → Zafran</v>
+      </c>
+      <c r="C17" s="31" t="str">
+        <v>muse-spark-1.3</v>
+      </c>
+      <c r="D17" s="31" t="str">
+        <v>xhigh</v>
+      </c>
+      <c r="E17" s="38" t="n">
+        <v>0.011235683518518518</v>
+      </c>
+      <c r="F17" s="38" t="n">
+        <v>0.013019161990740742</v>
+      </c>
+      <c r="G17" s="39" t="n">
+        <f>Costs!K18</f>
+        <v>6.540534249999999</v>
+      </c>
+      <c r="H17" s="37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I17" s="31" t="n">
+        <v>31</v>
+      </c>
+      <c r="J17" s="31" t="str">
+        <v>Vari Kaur: 25 + page
+Nick Fisher: 53 + page</v>
+      </c>
+      <c r="K17" s="31" t="str">
+        <v>All 3 jobs completed; reconciliation recovered. Strong Nick voice; narrower account coverage and Vari wrong-employer attribution.</v>
+      </c>
+      <c r="L17" s="43" t="str">
+        <v>Open report</v>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B18" s="3" t="str">
+        <v>Clue → Zafran</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <v>glm-5.3</v>
+      </c>
+      <c r="D18" s="3" t="str">
+        <v>medium</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>0.02665430107638889</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.027741879837962967</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <f>Costs!K19</f>
+        <v>7.18183739</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J18" s="3" t="str">
+        <v>Tom Anthony: 33 + page
+Sanaz Yashar: 55 + page</v>
+      </c>
+      <c r="K18" s="3" t="str">
+        <v>All dossiers/pages saved; account and reconciliation need review. Wrong people: Tom/Sanaz instead of Nick/Vari. Semantic quality not fully audited.</v>
+      </c>
+      <c r="L18" s="23" t="str">
+        <v>Open report</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L6" r:id="NativeLink1"/>
-    <hyperlink ref="L7" r:id="NativeLink2"/>
-    <hyperlink ref="L8" r:id="NativeLink3"/>
-    <hyperlink ref="L9" r:id="NativeLink4"/>
-    <hyperlink ref="L10" r:id="NativeLink5"/>
-    <hyperlink ref="L11" r:id="NativeLink6"/>
-    <hyperlink ref="L12" r:id="NativeLink7"/>
-    <hyperlink ref="L13" r:id="NativeLink8"/>
-    <hyperlink ref="L14" r:id="NativeLink9"/>
-    <hyperlink ref="L15" r:id="NativeLink10"/>
-    <hyperlink ref="L16" r:id="NativeLink11"/>
+    <hyperlink ref="L6" r:id="VerifiedLink0"/>
+    <hyperlink ref="L7" r:id="VerifiedLink1"/>
+    <hyperlink ref="L8" r:id="VerifiedLink2"/>
+    <hyperlink ref="L9" r:id="VerifiedLink3"/>
+    <hyperlink ref="L10" r:id="VerifiedLink4"/>
+    <hyperlink ref="L11" r:id="VerifiedLink5"/>
+    <hyperlink ref="L12" r:id="VerifiedLink6"/>
+    <hyperlink ref="L13" r:id="VerifiedLink7"/>
+    <hyperlink ref="L14" r:id="VerifiedLink8"/>
+    <hyperlink ref="L15" r:id="VerifiedLink9"/>
+    <hyperlink ref="L16" r:id="VerifiedLink10"/>
+    <hyperlink ref="L17" r:id="VerifiedLink361"/>
+    <hyperlink ref="L18" r:id="VerifiedLink387"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R1e6ecc194733475e"/>
+    <tablePart r:id="R8aa709572fff4b54"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF234B65"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="66" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>Recorded cost breakdown</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
-      <x:c r="K1" s="5"/>
-      <x:c r="L1" s="5"/>
-      <x:c r="M1" s="5"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Researcher = account and person models. Reconciliation is a separate common model. AI Ark credits are not converted to dollars. Setup02/03 have no priced research usage recorded; this does not certify a provider invoice of zero.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
-      <x:c r="J2" s="7"/>
-      <x:c r="K2" s="7"/>
-      <x:c r="L2" s="7"/>
-      <x:c r="M2" s="7"/>
-    </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="7"/>
-      <x:c r="B3" s="7"/>
-      <x:c r="C3" s="7"/>
-      <x:c r="D3" s="7"/>
-      <x:c r="E3" s="7"/>
-      <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7"/>
-      <x:c r="H3" s="7"/>
-      <x:c r="I3" s="7"/>
-      <x:c r="J3" s="7"/>
-      <x:c r="K3" s="7"/>
-      <x:c r="L3" s="7"/>
-      <x:c r="M3" s="7"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="C4" s="3"/>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="F4" s="3"/>
-      <x:c r="G4" s="3"/>
-      <x:c r="H4" s="3"/>
-      <x:c r="I4" s="3"/>
-      <x:c r="J4" s="3"/>
-      <x:c r="K4" s="3"/>
-      <x:c r="L4" s="3"/>
-      <x:c r="M4" s="3"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Run</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>Researcher USD</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>Exa USD</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="str">
-        <x:v>Deepgram USD</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="str">
-        <x:v>Embedding USD</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="str">
-        <x:v>Reconciliation USD</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="str">
-        <x:v>Old continuations USD</x:v>
-      </x:c>
-      <x:c r="H5" s="9" t="str">
-        <x:v>Head brief USD</x:v>
-      </x:c>
-      <x:c r="I5" s="9" t="str">
-        <x:v>Preflight USD</x:v>
-      </x:c>
-      <x:c r="J5" s="9" t="str">
-        <x:v>Other USD</x:v>
-      </x:c>
-      <x:c r="K5" s="9" t="str">
-        <x:v>Known total USD</x:v>
-      </x:c>
-      <x:c r="L5" s="9" t="str">
-        <x:v>AI Ark credits</x:v>
-      </x:c>
-      <x:c r="M5" s="9" t="str">
-        <x:v>Billing limits</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="40" customHeight="1">
-      <x:c r="A6" s="3" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="n">
-        <x:v>8.07496</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="n">
-        <x:v>0.208</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="n">
-        <x:v>4.12588</x:v>
-      </x:c>
-      <x:c r="H6" s="11" t="n">
-        <x:v>0.10485</x:v>
-      </x:c>
-      <x:c r="I6" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="n">
-        <x:f>SUM(B6:J6)</x:f>
-        <x:v>12.513690000000002</x:v>
-      </x:c>
-      <x:c r="L6" s="13" t="n">
-        <x:v>3.1</x:v>
-      </x:c>
-      <x:c r="M6" s="3" t="str">
-        <x:v>Includes old continuations; possible in-flight charge missing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="40" customHeight="1">
-      <x:c r="A7" s="10" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B7" s="12" t="n">
-        <x:v>2.3588940000000003</x:v>
-      </x:c>
-      <x:c r="C7" s="12" t="n">
-        <x:v>0.186</x:v>
-      </x:c>
-      <x:c r="D7" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="12" t="n">
-        <x:f>SUM(B7:J7)</x:f>
-        <x:v>2.544894</x:v>
-      </x:c>
-      <x:c r="L7" s="14" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="str">
-        <x:v>Pending Exa billing unknown</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="40" customHeight="1">
-      <x:c r="A8" s="3" t="str">
-        <x:v>P3</x:v>
-      </x:c>
-      <x:c r="B8" s="11" t="n">
-        <x:v>3.9056290000000002</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="n">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="n">
-        <x:v>0.100531</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="n">
-        <x:v>0.00084375</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="11" t="n">
-        <x:f>SUM(B8:J8)</x:f>
-        <x:v>4.18700375</x:v>
-      </x:c>
-      <x:c r="L8" s="13" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="M8" s="3" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="32" customHeight="1">
-      <x:c r="A9" s="10" t="str">
-        <x:v>P4</x:v>
-      </x:c>
-      <x:c r="B9" s="12" t="n">
-        <x:v>10.384506</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="n">
-        <x:v>0.206</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="n">
-        <x:v>0.15531075</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="12" t="n">
-        <x:v>0.0017984</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" s="12" t="n">
-        <x:f>SUM(B9:J9)</x:f>
-        <x:v>10.74761515</x:v>
-      </x:c>
-      <x:c r="L9" s="14" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="40" customHeight="1">
-      <x:c r="A10" s="3" t="str">
-        <x:v>P5</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="n">
-        <x:v>2.6032821999999998</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="n">
-        <x:v>0.194</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" s="11" t="n">
-        <x:v>0.00052925</x:v>
-      </x:c>
-      <x:c r="J10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="11" t="n">
-        <x:f>SUM(B10:J10)</x:f>
-        <x:v>2.7978114499999998</x:v>
-      </x:c>
-      <x:c r="L10" s="13" t="n">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="M10" s="3" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="32" customHeight="1">
-      <x:c r="A11" s="10" t="str">
-        <x:v>Z1</x:v>
-      </x:c>
-      <x:c r="B11" s="12" t="n">
-        <x:v>12.102434</x:v>
-      </x:c>
-      <x:c r="C11" s="12" t="n">
-        <x:v>0.293</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="n">
-        <x:v>0.081146</x:v>
-      </x:c>
-      <x:c r="E11" s="12" t="n">
-        <x:v>0.001019</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="n">
-        <x:v>0.174809</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="n">
-        <x:v>0.000818</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="12" t="n">
-        <x:f>SUM(B11:J11)</x:f>
-        <x:v>12.653226</x:v>
-      </x:c>
-      <x:c r="L11" s="14" t="n">
-        <x:v>3.1</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
-      <x:c r="A12" s="3" t="str">
-        <x:v>Z2</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="n">
-        <x:v>3.926011</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="n">
-        <x:v>0.095</x:v>
-      </x:c>
-      <x:c r="D12" s="11" t="n">
-        <x:v>0.065516</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="n">
-        <x:v>0.000759</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12" s="11" t="n">
-        <x:v>0.0008864</x:v>
-      </x:c>
-      <x:c r="J12" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="11" t="n">
-        <x:f>SUM(B12:J12)</x:f>
-        <x:v>4.0881723999999995</x:v>
-      </x:c>
-      <x:c r="L12" s="13" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="M12" s="3" t="str">
-        <x:v>Failed call and extra availability probe unpriced</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="32" customHeight="1">
-      <x:c r="A13" s="10" t="str">
-        <x:v>Z3</x:v>
-      </x:c>
-      <x:c r="B13" s="12" t="n">
-        <x:v>1.120041</x:v>
-      </x:c>
-      <x:c r="C13" s="12" t="n">
-        <x:v>0.09</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="n">
-        <x:v>0.05093</x:v>
-      </x:c>
-      <x:c r="E13" s="12" t="n">
-        <x:v>0.000579</x:v>
-      </x:c>
-      <x:c r="F13" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="12" t="n">
-        <x:v>0.000037</x:v>
-      </x:c>
-      <x:c r="J13" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="12" t="n">
-        <x:f>SUM(B13:J13)</x:f>
-        <x:v>1.2615870000000002</x:v>
-      </x:c>
-      <x:c r="L13" s="14" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="M13" s="10" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="32" customHeight="1">
-      <x:c r="A14" s="3" t="str">
-        <x:v>Z4</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="n">
-        <x:v>0.704624</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="n">
-        <x:v>0.09</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="n">
-        <x:f>SUM(B14:J14)</x:f>
-        <x:v>0.794624</x:v>
-      </x:c>
-      <x:c r="L14" s="13" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="M14" s="3" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="32" customHeight="1">
-      <x:c r="A15" s="10" t="str">
-        <x:v>Z5</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="n">
-        <x:v>7.954206</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="n">
-        <x:v>0.201</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="n">
-        <x:v>0.258532</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="n">
-        <x:v>0.0000187776</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="n">
-        <x:f>SUM(B15:J15)</x:f>
-        <x:v>8.4137567776</x:v>
-      </x:c>
-      <x:c r="L15" s="14" t="n">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="M15" s="10" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="32" customHeight="1">
-      <x:c r="A16" s="3" t="str">
-        <x:v>Z6</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="n">
-        <x:v>12.399157</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="n">
-        <x:v>0.338</x:v>
-      </x:c>
-      <x:c r="D16" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="n">
-        <x:v>0.40414</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="n">
-        <x:v>0.000117</x:v>
-      </x:c>
-      <x:c r="J16" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="n">
-        <x:f>SUM(B16:J16)</x:f>
-        <x:v>13.141414</x:v>
-      </x:c>
-      <x:c r="L16" s="13" t="n">
-        <x:v>3.1</x:v>
-      </x:c>
-      <x:c r="M16" s="3" t="str">
-        <x:v>Recorded usage; not invoice reconciled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="40" customHeight="1">
-      <x:c r="A17" s="10" t="str">
-        <x:v>S1</x:v>
-      </x:c>
-      <x:c r="B17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="12" t="n">
-        <x:v>0.118116</x:v>
-      </x:c>
-      <x:c r="I17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K17" s="12" t="n">
-        <x:f>SUM(B17:J17)</x:f>
-        <x:v>0.118116</x:v>
-      </x:c>
-      <x:c r="L17" s="14"/>
-      <x:c r="M17" s="10" t="str">
-        <x:v>Fresh shared Head brief in setup01. Counted once; no research tools.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="16" t="str">
-        <x:v>Total</x:v>
-      </x:c>
-      <x:c r="B19" s="17" t="n">
-        <x:f>SUM(B6:B17)</x:f>
-        <x:v>65.5337442</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="n">
-        <x:f>SUM(C6:C17)</x:f>
-        <x:v>2.081</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="n">
-        <x:f>SUM(D6:D17)</x:f>
-        <x:v>0.19759200000000002</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="n">
-        <x:f>SUM(E6:E17)</x:f>
-        <x:v>0.002357</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="n">
-        <x:f>SUM(F6:F17)</x:f>
-        <x:v>1.09332275</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="n">
-        <x:f>SUM(G6:G17)</x:f>
-        <x:v>4.12588</x:v>
-      </x:c>
-      <x:c r="H19" s="17" t="n">
-        <x:f>SUM(H6:H17)</x:f>
-        <x:v>0.222966</x:v>
-      </x:c>
-      <x:c r="I19" s="17" t="n">
-        <x:f>SUM(I6:I17)</x:f>
-        <x:v>0.0050485776</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:f>SUM(J6:J17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:f>SUM(K6:K17)</x:f>
-        <x:v>73.2619105276</x:v>
-      </x:c>
-      <x:c r="L19" s="18" t="n">
-        <x:f>SUM(L6:L17)</x:f>
-        <x:v>23.600000000000005</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="str">
-        <x:v>Known recorded charges; unpriced uncertainties excluded.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:M1"/>
-    <x:mergeCell ref="A2:M3"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9596e0f570154686"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF234B65"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="66" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="5" t="str">
+        <v>Recorded cost breakdown</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>Researcher = account and person models. Reconciliation is a separate common model. AI Ark credits are not converted to dollars. Setup02/03 have no priced research usage recorded; this does not certify a provider invoice of zero.</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="str">
+        <v>Run</v>
+      </c>
+      <c r="B5" s="9" t="str">
+        <v>Researcher USD</v>
+      </c>
+      <c r="C5" s="9" t="str">
+        <v>Exa USD</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <v>Deepgram USD</v>
+      </c>
+      <c r="E5" s="9" t="str">
+        <v>Embedding USD</v>
+      </c>
+      <c r="F5" s="9" t="str">
+        <v>Reconciliation USD</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <v>Old continuations USD</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <v>Head brief USD</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <v>Preflight USD</v>
+      </c>
+      <c r="J5" s="9" t="str">
+        <v>Other USD</v>
+      </c>
+      <c r="K5" s="9" t="str">
+        <v>Known total USD</v>
+      </c>
+      <c r="L5" s="9" t="str">
+        <v>AI Ark credits</v>
+      </c>
+      <c r="M5" s="9" t="str">
+        <v>Billing limits</v>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="3" t="str">
+        <v>P1</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>8.07496</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>4.12588</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.10485</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <f>SUM(B6:J6)</f>
+        <v>12.513690000000002</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M6" s="3" t="str">
+        <v>Includes old continuations; possible in-flight charge missing</v>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="10" t="str">
+        <v>P2</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>2.3588940000000003</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <f>SUM(B7:J7)</f>
+        <v>2.544894</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M7" s="10" t="str">
+        <v>Pending Exa billing unknown</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="3" t="str">
+        <v>P3</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>3.9056290000000002</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0.100531</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>0.00084375</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <f>SUM(B8:J8)</f>
+        <v>4.18700375</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M8" s="3" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="10" t="str">
+        <v>P4</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>10.384506</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.15531075</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.0017984</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <f>SUM(B9:J9)</f>
+        <v>10.74761515</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M9" s="10" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="3" t="str">
+        <v>P5</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>2.6032821999999998</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0.00052925</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <f>SUM(B10:J10)</f>
+        <v>2.7978114499999998</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M10" s="3" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="10" t="str">
+        <v>Z1</v>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>12.102434</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0.081146</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0.001019</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0.174809</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>0.000818</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <f>SUM(B11:J11)</f>
+        <v>12.653226</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M11" s="10" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="3" t="str">
+        <v>Z2</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>3.926011</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>0.065516</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>0.000759</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>0.0008864</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <f>SUM(B12:J12)</f>
+        <v>4.0881723999999995</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M12" s="3" t="str">
+        <v>Failed call and extra availability probe unpriced</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="str">
+        <v>Z3</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1.120041</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0.000579</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>0.000037</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <f>SUM(B13:J13)</f>
+        <v>1.2615870000000002</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M13" s="10" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="3" t="str">
+        <v>Z4</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>0.704624</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <f>SUM(B14:J14)</f>
+        <v>0.794624</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M14" s="3" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="str">
+        <v>Z5</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>7.954206</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0.258532</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>0.0000187776</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <f>SUM(B15:J15)</f>
+        <v>8.4137567776</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M15" s="10" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="3" t="str">
+        <v>Z6</v>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>12.399157</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.000117</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <f>SUM(B16:J16)</f>
+        <v>13.141414</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M16" s="3" t="str">
+        <v>Recorded usage; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="10" t="str">
+        <v>S1</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0.118116</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <f>SUM(B17:J17)</f>
+        <v>0.118116</v>
+      </c>
+      <c r="L17" s="14"/>
+      <c r="M17" s="10" t="str">
+        <v>Fresh shared Head brief in setup01. Counted once; no research tools.</v>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>5.920997</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>0.338008</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.00052925</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <f>SUM(B18:J18)</f>
+        <v>6.540534249999999</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M18" s="3" t="str">
+        <v>Recorded usage; common reconciliation separate; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B19" s="36" t="n">
+        <v>6.402588</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D19" s="36" t="n">
+        <v>0.184165</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <v>0.002283</v>
+      </c>
+      <c r="F19" s="36" t="n">
+        <v>0.382459</v>
+      </c>
+      <c r="G19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>0.00034239</v>
+      </c>
+      <c r="J19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <f>SUM(B19:J19)</f>
+        <v>7.18183739</v>
+      </c>
+      <c r="L19" s="37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M19" s="31" t="str">
+        <v>Recorded usage; common reconciliation separate; not invoice reconciled</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="33" t="str">
+        <v>Total</v>
+      </c>
+      <c r="B21" s="34" t="n">
+        <f>SUM(B6:B19)</f>
+        <v>77.8573292</v>
+      </c>
+      <c r="C21" s="34" t="n">
+        <f>SUM(C6:C19)</f>
+        <v>2.572</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <f>SUM(D6:D19)</f>
+        <v>0.381757</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <f>SUM(E6:E19)</f>
+        <v>0.00464</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <f>SUM(F6:F19)</f>
+        <v>1.8137897499999998</v>
+      </c>
+      <c r="G21" s="34" t="n">
+        <f>SUM(G6:G19)</f>
+        <v>4.12588</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <f>SUM(H6:H19)</f>
+        <v>0.222966</v>
+      </c>
+      <c r="I21" s="34" t="n">
+        <f>SUM(I6:I19)</f>
+        <v>0.0059202175999999995</v>
+      </c>
+      <c r="J21" s="34" t="n">
+        <f>SUM(J6:J19)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="34" t="n">
+        <f>SUM(K6:K19)</f>
+        <v>86.98428216759999</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <f>SUM(L6:L19)</f>
+        <v>32.300000000000004</v>
+      </c>
+      <c r="M21" s="33" t="str">
+        <v>Known recorded charges; unpriced uncertainties excluded.</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="Rc259872c75aa4946"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF234B65"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="19" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="43" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>Per-account and per-person timing</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
-      <x:c r="K1" s="5"/>
-      <x:c r="L1" s="5"/>
-      <x:c r="M1" s="5"/>
-      <x:c r="N1" s="5"/>
-      <x:c r="O1" s="5"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Times are job wall duration and observed phase boundaries. “Before formation” includes preparation, research and source review. Blank phase times mean no completed milestone. Model cost excludes providers. Zero findings on blocked jobs means none authored, not an empty successful investigation.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
-      <x:c r="J2" s="7"/>
-      <x:c r="K2" s="7"/>
-      <x:c r="L2" s="7"/>
-      <x:c r="M2" s="7"/>
-      <x:c r="N2" s="7"/>
-      <x:c r="O2" s="7"/>
-    </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="7"/>
-      <x:c r="B3" s="7"/>
-      <x:c r="C3" s="7"/>
-      <x:c r="D3" s="7"/>
-      <x:c r="E3" s="7"/>
-      <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7"/>
-      <x:c r="H3" s="7"/>
-      <x:c r="I3" s="7"/>
-      <x:c r="J3" s="7"/>
-      <x:c r="K3" s="7"/>
-      <x:c r="L3" s="7"/>
-      <x:c r="M3" s="7"/>
-      <x:c r="N3" s="7"/>
-      <x:c r="O3" s="7"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="C4" s="3"/>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="F4" s="3"/>
-      <x:c r="G4" s="3"/>
-      <x:c r="H4" s="3"/>
-      <x:c r="I4" s="3"/>
-      <x:c r="J4" s="3"/>
-      <x:c r="K4" s="3"/>
-      <x:c r="L4" s="3"/>
-      <x:c r="M4" s="3"/>
-      <x:c r="N4" s="3"/>
-      <x:c r="O4" s="3"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Run</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>Entity</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="str">
-        <x:v>Job elapsed</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="str">
-        <x:v>Before formation</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="str">
-        <x:v>Formation → import</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="str">
-        <x:v>Import → narrative</x:v>
-      </x:c>
-      <x:c r="H5" s="9" t="str">
-        <x:v>Initial / draft findings</x:v>
-      </x:c>
-      <x:c r="I5" s="9" t="str">
-        <x:v>Latest stored findings</x:v>
-      </x:c>
-      <x:c r="J5" s="9" t="str">
-        <x:v>Researcher narrative</x:v>
-      </x:c>
-      <x:c r="K5" s="9" t="str">
-        <x:v>Model calls</x:v>
-      </x:c>
-      <x:c r="L5" s="9" t="str">
-        <x:v>Model USD</x:v>
-      </x:c>
-      <x:c r="M5" s="9" t="str">
-        <x:v>Start UTC</x:v>
-      </x:c>
-      <x:c r="N5" s="9" t="str">
-        <x:v>End UTC</x:v>
-      </x:c>
-      <x:c r="O5" s="9" t="str">
-        <x:v>Job ID</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="3" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="B6" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C6" s="3" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="D6" s="19" t="n">
-        <x:v>0.01147174449074074</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="n">
-        <x:v>0.004393796296296297</x:v>
-      </x:c>
-      <x:c r="F6" s="19" t="n">
-        <x:v>0.005344433402777778</x:v>
-      </x:c>
-      <x:c r="G6" s="19" t="n">
-        <x:v>0.0013171469212962964</x:v>
-      </x:c>
-      <x:c r="H6" s="3" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I6" s="3" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J6" s="3" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="L6" s="25" t="n">
-        <x:v>4.80246</x:v>
-      </x:c>
-      <x:c r="M6" s="27" t="n">
-        <x:v>46292.8051833912</x:v>
-      </x:c>
-      <x:c r="N6" s="27" t="n">
-        <x:v>46292.816655138886</x:v>
-      </x:c>
-      <x:c r="O6" s="3" t="str">
-        <x:v>8e9c0c15-df34-5047-a1b6-c2a482b42a48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="54" customHeight="1">
-      <x:c r="A7" s="10" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>Todd Greer</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D7" s="20" t="n">
-        <x:v>0.009662378379629629</x:v>
-      </x:c>
-      <x:c r="E7" s="20" t="n">
-        <x:v>0.003990023148148148</x:v>
-      </x:c>
-      <x:c r="F7" s="20" t="n">
-        <x:v>0.001892433240740741</x:v>
-      </x:c>
-      <x:c r="G7" s="20" t="n">
-        <x:v>0.0032585776041666667</x:v>
-      </x:c>
-      <x:c r="H7" s="10" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I7" s="10" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J7" s="10" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K7" s="10" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L7" s="26" t="n">
-        <x:v>3.2725</x:v>
-      </x:c>
-      <x:c r="M7" s="28" t="n">
-        <x:v>46292.814938414354</x:v>
-      </x:c>
-      <x:c r="N7" s="28" t="n">
-        <x:v>46292.82460079861</x:v>
-      </x:c>
-      <x:c r="O7" s="10" t="str">
-        <x:v>51acdfbb-d6c1-5ce2-8c7b-74761f40dddd</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="3" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="n">
-        <x:v>0.005308429513888889</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="n">
-        <x:v>0.0026962847222222223</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="n">
-        <x:v>0.0008861138657407407</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="n">
-        <x:v>0.001514635949074074</x:v>
-      </x:c>
-      <x:c r="H8" s="3" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I8" s="3" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J8" s="3" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K8" s="3" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L8" s="25" t="n">
-        <x:v>1.708644</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="n">
-        <x:v>46293.18825723379</x:v>
-      </x:c>
-      <x:c r="N8" s="27" t="n">
-        <x:v>46293.19356565972</x:v>
-      </x:c>
-      <x:c r="O8" s="3" t="str">
-        <x:v>c80f26cc-33e8-5529-b018-84f06ccbb325</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="54" customHeight="1">
-      <x:c r="A9" s="10" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>Beth Smith</x:v>
-      </x:c>
-      <x:c r="C9" s="10" t="str">
-        <x:v>cancelled_by_user</x:v>
-      </x:c>
-      <x:c r="D9" s="20" t="n">
-        <x:v>0.01432444386574074</x:v>
-      </x:c>
-      <x:c r="E9" s="20"/>
-      <x:c r="F9" s="20"/>
-      <x:c r="G9" s="20"/>
-      <x:c r="H9" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K9" s="10" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L9" s="26" t="n">
-        <x:v>0.65025</x:v>
-      </x:c>
-      <x:c r="M9" s="28" t="n">
-        <x:v>46293.19185565972</x:v>
-      </x:c>
-      <x:c r="N9" s="28" t="n">
-        <x:v>46293.206180092595</x:v>
-      </x:c>
-      <x:c r="O9" s="10" t="str">
-        <x:v>a367f7c4-e2fc-5236-b5c9-ea7133b55e42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="3" t="str">
-        <x:v>P3</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="D10" s="19" t="n">
-        <x:v>0.004923446805555556</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="n">
-        <x:v>0.0027583680555555556</x:v>
-      </x:c>
-      <x:c r="F10" s="19" t="n">
-        <x:v>0.0009250532523148148</x:v>
-      </x:c>
-      <x:c r="G10" s="19" t="n">
-        <x:v>0.0009144024999999999</x:v>
-      </x:c>
-      <x:c r="H10" s="3" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I10" s="3" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J10" s="3" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L10" s="25" t="n">
-        <x:v>1.7524170000000001</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="n">
-        <x:v>46293.22105435185</x:v>
-      </x:c>
-      <x:c r="N10" s="27" t="n">
-        <x:v>46293.22597778935</x:v>
-      </x:c>
-      <x:c r="O10" s="3" t="str">
-        <x:v>c80f26cc-33e8-5529-b018-84f06ccbb325</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="10" t="str">
-        <x:v>P3</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>Beth Smith</x:v>
-      </x:c>
-      <x:c r="C11" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D11" s="20" t="n">
-        <x:v>0.006380603252314815</x:v>
-      </x:c>
-      <x:c r="E11" s="20" t="n">
-        <x:v>0.003127951388888889</x:v>
-      </x:c>
-      <x:c r="F11" s="20" t="n">
-        <x:v>0.0013984964699074074</x:v>
-      </x:c>
-      <x:c r="G11" s="20"/>
-      <x:c r="H11" s="10" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I11" s="10" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J11" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K11" s="10" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L11" s="26" t="n">
-        <x:v>2.153212</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="n">
-        <x:v>46293.22477138889</x:v>
-      </x:c>
-      <x:c r="N11" s="28" t="n">
-        <x:v>46293.23115199074</x:v>
-      </x:c>
-      <x:c r="O11" s="10" t="str">
-        <x:v>ce2ce4f1-ab74-5f41-b739-6dd5a201088e</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="54" customHeight="1">
-      <x:c r="A12" s="3" t="str">
-        <x:v>P4</x:v>
-      </x:c>
-      <x:c r="B12" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C12" s="3" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D12" s="19" t="n">
-        <x:v>0.020604871597222223</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="n">
-        <x:v>0.014622766203703702</x:v>
-      </x:c>
-      <x:c r="F12" s="19" t="n">
-        <x:v>0.003909831793981481</x:v>
-      </x:c>
-      <x:c r="G12" s="19"/>
-      <x:c r="H12" s="3" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="I12" s="3" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J12" s="3" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K12" s="3" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="L12" s="25" t="n">
-        <x:v>5.408576</x:v>
-      </x:c>
-      <x:c r="M12" s="27" t="n">
-        <x:v>46293.25278575232</x:v>
-      </x:c>
-      <x:c r="N12" s="27" t="n">
-        <x:v>46293.273390625</x:v>
-      </x:c>
-      <x:c r="O12" s="3" t="str">
-        <x:v>c80f26cc-33e8-5529-b018-84f06ccbb325</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="54" customHeight="1">
-      <x:c r="A13" s="10" t="str">
-        <x:v>P4</x:v>
-      </x:c>
-      <x:c r="B13" s="10" t="str">
-        <x:v>Todd Greer</x:v>
-      </x:c>
-      <x:c r="C13" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D13" s="20" t="n">
-        <x:v>0.017306598344907408</x:v>
-      </x:c>
-      <x:c r="E13" s="20" t="n">
-        <x:v>0.009533414351851852</x:v>
-      </x:c>
-      <x:c r="F13" s="20" t="n">
-        <x:v>0.0026498268055555555</x:v>
-      </x:c>
-      <x:c r="G13" s="20" t="n">
-        <x:v>0.002891263726851852</x:v>
-      </x:c>
-      <x:c r="H13" s="10" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I13" s="10" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J13" s="10" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K13" s="10" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="L13" s="26" t="n">
-        <x:v>4.97593</x:v>
-      </x:c>
-      <x:c r="M13" s="28" t="n">
-        <x:v>46293.27134496528</x:v>
-      </x:c>
-      <x:c r="N13" s="28" t="n">
-        <x:v>46293.2886515625</x:v>
-      </x:c>
-      <x:c r="O13" s="10" t="str">
-        <x:v>6bc03f41-fd75-5ce8-998d-6ec983efd86c</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="54" customHeight="1">
-      <x:c r="A14" s="3" t="str">
-        <x:v>P5</x:v>
-      </x:c>
-      <x:c r="B14" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C14" s="3" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="D14" s="19" t="n">
-        <x:v>0.005225098449074074</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="n">
-        <x:v>0.003540648148148148</x:v>
-      </x:c>
-      <x:c r="F14" s="19" t="n">
-        <x:v>0.0008538780902777778</x:v>
-      </x:c>
-      <x:c r="G14" s="19" t="n">
-        <x:v>0.00046323849537037036</x:v>
-      </x:c>
-      <x:c r="H14" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I14" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J14" s="3" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K14" s="3" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="L14" s="25" t="n">
-        <x:v>1.54478</x:v>
-      </x:c>
-      <x:c r="M14" s="27" t="n">
-        <x:v>46293.295757824075</x:v>
-      </x:c>
-      <x:c r="N14" s="27" t="n">
-        <x:v>46293.30098292824</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="str">
-        <x:v>c80f26cc-33e8-5529-b018-84f06ccbb325</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="54" customHeight="1">
-      <x:c r="A15" s="10" t="str">
-        <x:v>P5</x:v>
-      </x:c>
-      <x:c r="B15" s="10" t="str">
-        <x:v>Todd Greer</x:v>
-      </x:c>
-      <x:c r="C15" s="10" t="str">
-        <x:v>infrastructure_interrupted</x:v>
-      </x:c>
-      <x:c r="D15" s="20" t="n">
-        <x:v>0.0032579532407407408</x:v>
-      </x:c>
-      <x:c r="E15" s="20"/>
-      <x:c r="F15" s="20"/>
-      <x:c r="G15" s="20"/>
-      <x:c r="H15" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K15" s="10" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L15" s="26" t="n">
-        <x:v>1.0585022</x:v>
-      </x:c>
-      <x:c r="M15" s="28" t="n">
-        <x:v>46293.300175462966</x:v>
-      </x:c>
-      <x:c r="N15" s="28" t="n">
-        <x:v>46293.30343341435</x:v>
-      </x:c>
-      <x:c r="O15" s="10" t="str">
-        <x:v>47c616df-95cf-5bff-8fc4-c91b26554e75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="54" customHeight="1">
-      <x:c r="A16" s="3" t="str">
-        <x:v>Z1</x:v>
-      </x:c>
-      <x:c r="B16" s="3" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C16" s="3" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="D16" s="19" t="n">
-        <x:v>0.010935484583333334</x:v>
-      </x:c>
-      <x:c r="E16" s="19" t="n">
-        <x:v>0.004498038599537037</x:v>
-      </x:c>
-      <x:c r="F16" s="19" t="n">
-        <x:v>0.0030821414930555556</x:v>
-      </x:c>
-      <x:c r="G16" s="19" t="n">
-        <x:v>0.002666686180555556</x:v>
-      </x:c>
-      <x:c r="H16" s="3" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I16" s="3" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J16" s="3" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K16" s="3" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L16" s="25" t="n">
-        <x:v>4.2804</x:v>
-      </x:c>
-      <x:c r="M16" s="27" t="n">
-        <x:v>46293.3615134375</x:v>
-      </x:c>
-      <x:c r="N16" s="27" t="n">
-        <x:v>46293.372448912036</x:v>
-      </x:c>
-      <x:c r="O16" s="3" t="str">
-        <x:v>59d4870e-2207-56ca-a50b-e76ab86f6a53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="54" customHeight="1">
-      <x:c r="A17" s="10" t="str">
-        <x:v>Z1</x:v>
-      </x:c>
-      <x:c r="B17" s="10" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C17" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D17" s="20" t="n">
-        <x:v>0.009306901886574074</x:v>
-      </x:c>
-      <x:c r="E17" s="20" t="n">
-        <x:v>0.004153797349537036</x:v>
-      </x:c>
-      <x:c r="F17" s="20" t="n">
-        <x:v>0.0025064493402777777</x:v>
-      </x:c>
-      <x:c r="G17" s="20" t="n">
-        <x:v>0.0019094427199074075</x:v>
-      </x:c>
-      <x:c r="H17" s="10" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I17" s="10" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J17" s="10" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K17" s="10" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L17" s="26" t="n">
-        <x:v>3.13394</x:v>
-      </x:c>
-      <x:c r="M17" s="28" t="n">
-        <x:v>46293.369176388886</x:v>
-      </x:c>
-      <x:c r="N17" s="28" t="n">
-        <x:v>46293.37848328704</x:v>
-      </x:c>
-      <x:c r="O17" s="10" t="str">
-        <x:v>04070cd2-53e0-510c-8373-2f6511f15052</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="54" customHeight="1">
-      <x:c r="A18" s="3" t="str">
-        <x:v>Z1</x:v>
-      </x:c>
-      <x:c r="B18" s="3" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C18" s="3" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D18" s="19" t="n">
-        <x:v>0.013319931863425925</x:v>
-      </x:c>
-      <x:c r="E18" s="19" t="n">
-        <x:v>0.006750585625</x:v>
-      </x:c>
-      <x:c r="F18" s="19" t="n">
-        <x:v>0.004620488414351851</x:v>
-      </x:c>
-      <x:c r="G18" s="19" t="n">
-        <x:v>0.0012899919791666667</x:v>
-      </x:c>
-      <x:c r="H18" s="3" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I18" s="3" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J18" s="3" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K18" s="3" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L18" s="25" t="n">
-        <x:v>4.688094</x:v>
-      </x:c>
-      <x:c r="M18" s="27" t="n">
-        <x:v>46293.36918052084</x:v>
-      </x:c>
-      <x:c r="N18" s="27" t="n">
-        <x:v>46293.382500451386</x:v>
-      </x:c>
-      <x:c r="O18" s="3" t="str">
-        <x:v>05d4fa83-5d48-5d21-ab82-867e8af0819d</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="32" customHeight="1">
-      <x:c r="A19" s="10" t="str">
-        <x:v>Z2</x:v>
-      </x:c>
-      <x:c r="B19" s="10" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C19" s="10" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="D19" s="20"/>
-      <x:c r="E19" s="20"/>
-      <x:c r="F19" s="20"/>
-      <x:c r="G19" s="20"/>
-      <x:c r="H19" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I19" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K19" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M19" s="28"/>
-      <x:c r="N19" s="28"/>
-      <x:c r="O19" s="10" t="str">
-        <x:v>ea54ef0e-91b7-501e-996e-97ce42a15264</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
-      <x:c r="A20" s="3" t="str">
-        <x:v>Z2</x:v>
-      </x:c>
-      <x:c r="B20" s="3" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C20" s="3" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="D20" s="19"/>
-      <x:c r="E20" s="19"/>
-      <x:c r="F20" s="19"/>
-      <x:c r="G20" s="19"/>
-      <x:c r="H20" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I20" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="3" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K20" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L20" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M20" s="27"/>
-      <x:c r="N20" s="27"/>
-      <x:c r="O20" s="3" t="str">
-        <x:v>5427e1bf-1da3-5af3-80c7-31100873f585</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="54" customHeight="1">
-      <x:c r="A21" s="10" t="str">
-        <x:v>Z2</x:v>
-      </x:c>
-      <x:c r="B21" s="10" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C21" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D21" s="20" t="n">
-        <x:v>0.018485020810185184</x:v>
-      </x:c>
-      <x:c r="E21" s="20" t="n">
-        <x:v>0.011562065601851851</x:v>
-      </x:c>
-      <x:c r="F21" s="20"/>
-      <x:c r="G21" s="20"/>
-      <x:c r="H21" s="10" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I21" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K21" s="10" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="L21" s="26" t="n">
-        <x:v>3.926011</x:v>
-      </x:c>
-      <x:c r="M21" s="28" t="n">
-        <x:v>46293.36151353009</x:v>
-      </x:c>
-      <x:c r="N21" s="28" t="n">
-        <x:v>46293.37999855324</x:v>
-      </x:c>
-      <x:c r="O21" s="10" t="str">
-        <x:v>59d4870e-2207-56ca-a50b-e76ab86f6a53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="32" customHeight="1">
-      <x:c r="A22" s="3" t="str">
-        <x:v>Z3</x:v>
-      </x:c>
-      <x:c r="B22" s="3" t="str">
-        <x:v>Tom Anthony</x:v>
-      </x:c>
-      <x:c r="C22" s="3" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="D22" s="19"/>
-      <x:c r="E22" s="19"/>
-      <x:c r="F22" s="19"/>
-      <x:c r="G22" s="19"/>
-      <x:c r="H22" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I22" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J22" s="3" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K22" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L22" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M22" s="27"/>
-      <x:c r="N22" s="27"/>
-      <x:c r="O22" s="3" t="str">
-        <x:v>631ec33b-a46f-52f4-801e-9eab8cfc2efd</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="32" customHeight="1">
-      <x:c r="A23" s="10" t="str">
-        <x:v>Z3</x:v>
-      </x:c>
-      <x:c r="B23" s="10" t="str">
-        <x:v>Kelly W.</x:v>
-      </x:c>
-      <x:c r="C23" s="10" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="D23" s="20"/>
-      <x:c r="E23" s="20"/>
-      <x:c r="F23" s="20"/>
-      <x:c r="G23" s="20"/>
-      <x:c r="H23" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I23" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J23" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K23" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L23" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M23" s="28"/>
-      <x:c r="N23" s="28"/>
-      <x:c r="O23" s="10" t="str">
-        <x:v>684b62dc-6ab1-5285-aded-984c4d580d49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="54" customHeight="1">
-      <x:c r="A24" s="3" t="str">
-        <x:v>Z3</x:v>
-      </x:c>
-      <x:c r="B24" s="3" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C24" s="3" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D24" s="19" t="n">
-        <x:v>0.0025698396527777776</x:v>
-      </x:c>
-      <x:c r="E24" s="19"/>
-      <x:c r="F24" s="19"/>
-      <x:c r="G24" s="19"/>
-      <x:c r="H24" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I24" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J24" s="3" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K24" s="3" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L24" s="25" t="n">
-        <x:v>1.120041</x:v>
-      </x:c>
-      <x:c r="M24" s="27" t="n">
-        <x:v>46293.36151351852</x:v>
-      </x:c>
-      <x:c r="N24" s="27" t="n">
-        <x:v>46293.36408335648</x:v>
-      </x:c>
-      <x:c r="O24" s="3" t="str">
-        <x:v>59d4870e-2207-56ca-a50b-e76ab86f6a53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="54" customHeight="1">
-      <x:c r="A25" s="10" t="str">
-        <x:v>Z4</x:v>
-      </x:c>
-      <x:c r="B25" s="10" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C25" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D25" s="20" t="n">
-        <x:v>0.001627675</x:v>
-      </x:c>
-      <x:c r="E25" s="20"/>
-      <x:c r="F25" s="20"/>
-      <x:c r="G25" s="20"/>
-      <x:c r="H25" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I25" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J25" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K25" s="10" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L25" s="26" t="n">
-        <x:v>0.704624</x:v>
-      </x:c>
-      <x:c r="M25" s="28" t="n">
-        <x:v>46293.36922835648</x:v>
-      </x:c>
-      <x:c r="N25" s="28" t="n">
-        <x:v>46293.370856030095</x:v>
-      </x:c>
-      <x:c r="O25" s="10" t="str">
-        <x:v>59d4870e-2207-56ca-a50b-e76ab86f6a53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="54" customHeight="1">
-      <x:c r="A26" s="3" t="str">
-        <x:v>Z5</x:v>
-      </x:c>
-      <x:c r="B26" s="3" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C26" s="3" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D26" s="19" t="n">
-        <x:v>0.001657475451388889</x:v>
-      </x:c>
-      <x:c r="E26" s="19"/>
-      <x:c r="F26" s="19"/>
-      <x:c r="G26" s="19"/>
-      <x:c r="H26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="3" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K26" s="3" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L26" s="25" t="n">
-        <x:v>0.736717</x:v>
-      </x:c>
-      <x:c r="M26" s="27" t="n">
-        <x:v>46293.39213855324</x:v>
-      </x:c>
-      <x:c r="N26" s="27" t="n">
-        <x:v>46293.39379603009</x:v>
-      </x:c>
-      <x:c r="O26" s="3" t="str">
-        <x:v>a909b721-e744-59b8-89de-7668baec343b</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="54" customHeight="1">
-      <x:c r="A27" s="10" t="str">
-        <x:v>Z5</x:v>
-      </x:c>
-      <x:c r="B27" s="10" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C27" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D27" s="20" t="n">
-        <x:v>0.02543705539351852</x:v>
-      </x:c>
-      <x:c r="E27" s="20" t="n">
-        <x:v>0.016891375972222223</x:v>
-      </x:c>
-      <x:c r="F27" s="20" t="n">
-        <x:v>0.004934316631944444</x:v>
-      </x:c>
-      <x:c r="G27" s="20"/>
-      <x:c r="H27" s="10" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I27" s="10" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J27" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K27" s="10" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="L27" s="26" t="n">
-        <x:v>2.262775</x:v>
-      </x:c>
-      <x:c r="M27" s="28" t="n">
-        <x:v>46293.39213418982</x:v>
-      </x:c>
-      <x:c r="N27" s="28" t="n">
-        <x:v>46293.41757125</x:v>
-      </x:c>
-      <x:c r="O27" s="10" t="str">
-        <x:v>436cb01b-602f-52fd-a83e-e1f08f8708fe</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="54" customHeight="1">
-      <x:c r="A28" s="3" t="str">
-        <x:v>Z5</x:v>
-      </x:c>
-      <x:c r="B28" s="3" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C28" s="3" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D28" s="19" t="n">
-        <x:v>0.014482020127314815</x:v>
-      </x:c>
-      <x:c r="E28" s="19" t="n">
-        <x:v>0.011770511805555555</x:v>
-      </x:c>
-      <x:c r="F28" s="19" t="n">
-        <x:v>0.001826041076388889</x:v>
-      </x:c>
-      <x:c r="G28" s="19"/>
-      <x:c r="H28" s="3" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="I28" s="3" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J28" s="3" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K28" s="3" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="L28" s="25" t="n">
-        <x:v>4.954714</x:v>
-      </x:c>
-      <x:c r="M28" s="27" t="n">
-        <x:v>46293.378438761574</x:v>
-      </x:c>
-      <x:c r="N28" s="27" t="n">
-        <x:v>46293.39292077546</x:v>
-      </x:c>
-      <x:c r="O28" s="3" t="str">
-        <x:v>59d4870e-2207-56ca-a50b-e76ab86f6a53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="54" customHeight="1">
-      <x:c r="A29" s="10" t="str">
-        <x:v>Z6</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C29" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D29" s="20" t="n">
-        <x:v>0.010493027719907407</x:v>
-      </x:c>
-      <x:c r="E29" s="20" t="n">
-        <x:v>0.005714940462962963</x:v>
-      </x:c>
-      <x:c r="F29" s="20" t="n">
-        <x:v>0.0019973045949074073</x:v>
-      </x:c>
-      <x:c r="G29" s="20" t="n">
-        <x:v>0.002155830162037037</x:v>
-      </x:c>
-      <x:c r="H29" s="10" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I29" s="10" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J29" s="10" t="str">
-        <x:v>Saved</x:v>
-      </x:c>
-      <x:c r="K29" s="10" t="n">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="L29" s="26" t="n">
-        <x:v>3.270071</x:v>
-      </x:c>
-      <x:c r="M29" s="28" t="n">
-        <x:v>46293.40834320602</x:v>
-      </x:c>
-      <x:c r="N29" s="28" t="n">
-        <x:v>46293.41883623842</x:v>
-      </x:c>
-      <x:c r="O29" s="10" t="str">
-        <x:v>59d4870e-2207-56ca-a50b-e76ab86f6a53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="54" customHeight="1">
-      <x:c r="A30" s="3" t="str">
-        <x:v>Z6</x:v>
-      </x:c>
-      <x:c r="B30" s="3" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C30" s="3" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D30" s="19" t="n">
-        <x:v>0.010950602453703705</x:v>
-      </x:c>
-      <x:c r="E30" s="19" t="n">
-        <x:v>0.00706084517361111</x:v>
-      </x:c>
-      <x:c r="F30" s="19" t="n">
-        <x:v>0.002860982627314815</x:v>
-      </x:c>
-      <x:c r="G30" s="19"/>
-      <x:c r="H30" s="3" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="I30" s="3" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J30" s="3" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="L30" s="25" t="n">
-        <x:v>4.16695</x:v>
-      </x:c>
-      <x:c r="M30" s="27" t="n">
-        <x:v>46293.4161315625</x:v>
-      </x:c>
-      <x:c r="N30" s="27" t="n">
-        <x:v>46293.42708217593</x:v>
-      </x:c>
-      <x:c r="O30" s="3" t="str">
-        <x:v>41ba4d68-d1da-57fd-9163-a0ec041a44bd</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="54" customHeight="1">
-      <x:c r="A31" s="10" t="str">
-        <x:v>Z6</x:v>
-      </x:c>
-      <x:c r="B31" s="10" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C31" s="10" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="D31" s="20" t="n">
-        <x:v>0.01604837917824074</x:v>
-      </x:c>
-      <x:c r="E31" s="20" t="n">
-        <x:v>0.009032712430555555</x:v>
-      </x:c>
-      <x:c r="F31" s="20" t="n">
-        <x:v>0.002023377627314815</x:v>
-      </x:c>
-      <x:c r="G31" s="20"/>
-      <x:c r="H31" s="10" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I31" s="10" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="J31" s="10" t="str">
-        <x:v>Not saved</x:v>
-      </x:c>
-      <x:c r="K31" s="10" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="L31" s="26" t="n">
-        <x:v>4.962136</x:v>
-      </x:c>
-      <x:c r="M31" s="28" t="n">
-        <x:v>46293.41613568287</x:v>
-      </x:c>
-      <x:c r="N31" s="28" t="n">
-        <x:v>46293.4321840625</x:v>
-      </x:c>
-      <x:c r="O31" s="10" t="str">
-        <x:v>92047fb7-01a5-5611-802e-c886da87eb6a</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:O1"/>
-    <x:mergeCell ref="A2:O3"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6265689fa844a72"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF234B65"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="19" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="43" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="5" t="str">
+        <v>Per-account and per-person timing</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>Times are job wall duration and observed phase boundaries. “Before formation” includes preparation, research and source review. Blank phase times mean no completed milestone. Model cost excludes providers. Zero findings on blocked jobs means none authored, not an empty successful investigation.</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="str">
+        <v>Run</v>
+      </c>
+      <c r="B5" s="9" t="str">
+        <v>Entity</v>
+      </c>
+      <c r="C5" s="9" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <v>Job elapsed</v>
+      </c>
+      <c r="E5" s="9" t="str">
+        <v>Before formation</v>
+      </c>
+      <c r="F5" s="9" t="str">
+        <v>Formation → import</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <v>Import → narrative</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <v>Initial / draft findings</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <v>Latest stored findings</v>
+      </c>
+      <c r="J5" s="9" t="str">
+        <v>Researcher narrative</v>
+      </c>
+      <c r="K5" s="9" t="str">
+        <v>Model calls</v>
+      </c>
+      <c r="L5" s="9" t="str">
+        <v>Model USD</v>
+      </c>
+      <c r="M5" s="9" t="str">
+        <v>Start UTC</v>
+      </c>
+      <c r="N5" s="9" t="str">
+        <v>End UTC</v>
+      </c>
+      <c r="O5" s="9" t="str">
+        <v>Job ID</v>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="3" t="str">
+        <v>P1</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>0.01147174449074074</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>0.004393796296296297</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.005344433402777778</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.0013171469212962964</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <v>4.80246</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>46292.8051833912</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>46292.816655138886</v>
+      </c>
+      <c r="O6" s="3" t="str">
+        <v>8e9c0c15-df34-5047-a1b6-c2a482b42a48</v>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="10" t="str">
+        <v>P1</v>
+      </c>
+      <c r="B7" s="10" t="str">
+        <v>Todd Greer</v>
+      </c>
+      <c r="C7" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>0.009662378379629629</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>0.003990023148148148</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>0.001892433240740741</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>0.0032585776041666667</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="J7" s="10" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>3.2725</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>46292.814938414354</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>46292.82460079861</v>
+      </c>
+      <c r="O7" s="10" t="str">
+        <v>51acdfbb-d6c1-5ce2-8c7b-74761f40dddd</v>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="3" t="str">
+        <v>P2</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>0.005308429513888889</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>0.0026962847222222223</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.0008861138657407407</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.001514635949074074</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>1.708644</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>46293.18825723379</v>
+      </c>
+      <c r="N8" s="27" t="n">
+        <v>46293.19356565972</v>
+      </c>
+      <c r="O8" s="3" t="str">
+        <v>c80f26cc-33e8-5529-b018-84f06ccbb325</v>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="10" t="str">
+        <v>P2</v>
+      </c>
+      <c r="B9" s="10" t="str">
+        <v>Beth Smith</v>
+      </c>
+      <c r="C9" s="10" t="str">
+        <v>cancelled_by_user</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>0.01432444386574074</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>0.65025</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>46293.19185565972</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>46293.206180092595</v>
+      </c>
+      <c r="O9" s="10" t="str">
+        <v>a367f7c4-e2fc-5236-b5c9-ea7133b55e42</v>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="3" t="str">
+        <v>P3</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>0.004923446805555556</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>0.0027583680555555556</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.0009250532523148148</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.0009144024999999999</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="J10" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" s="25" t="n">
+        <v>1.7524170000000001</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>46293.22105435185</v>
+      </c>
+      <c r="N10" s="27" t="n">
+        <v>46293.22597778935</v>
+      </c>
+      <c r="O10" s="3" t="str">
+        <v>c80f26cc-33e8-5529-b018-84f06ccbb325</v>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="10" t="str">
+        <v>P3</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <v>Beth Smith</v>
+      </c>
+      <c r="C11" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>0.006380603252314815</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>0.003127951388888889</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>0.0013984964699074074</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="J11" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>2.153212</v>
+      </c>
+      <c r="M11" s="28" t="n">
+        <v>46293.22477138889</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>46293.23115199074</v>
+      </c>
+      <c r="O11" s="10" t="str">
+        <v>ce2ce4f1-ab74-5f41-b739-6dd5a201088e</v>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="3" t="str">
+        <v>P4</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>0.020604871597222223</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0.014622766203703702</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.003909831793981481</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="J12" s="3" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="L12" s="25" t="n">
+        <v>5.408576</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>46293.25278575232</v>
+      </c>
+      <c r="N12" s="27" t="n">
+        <v>46293.273390625</v>
+      </c>
+      <c r="O12" s="3" t="str">
+        <v>c80f26cc-33e8-5529-b018-84f06ccbb325</v>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="10" t="str">
+        <v>P4</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <v>Todd Greer</v>
+      </c>
+      <c r="C13" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>0.017306598344907408</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0.009533414351851852</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.0026498268055555555</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.002891263726851852</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="J13" s="10" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>4.97593</v>
+      </c>
+      <c r="M13" s="28" t="n">
+        <v>46293.27134496528</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>46293.2886515625</v>
+      </c>
+      <c r="O13" s="10" t="str">
+        <v>6bc03f41-fd75-5ce8-998d-6ec983efd86c</v>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="3" t="str">
+        <v>P5</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>0.005225098449074074</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>0.003540648148148148</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.0008538780902777778</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.00046323849537037036</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <v>1.54478</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>46293.295757824075</v>
+      </c>
+      <c r="N14" s="27" t="n">
+        <v>46293.30098292824</v>
+      </c>
+      <c r="O14" s="3" t="str">
+        <v>c80f26cc-33e8-5529-b018-84f06ccbb325</v>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="10" t="str">
+        <v>P5</v>
+      </c>
+      <c r="B15" s="10" t="str">
+        <v>Todd Greer</v>
+      </c>
+      <c r="C15" s="10" t="str">
+        <v>infrastructure_interrupted</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>0.0032579532407407408</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>1.0585022</v>
+      </c>
+      <c r="M15" s="28" t="n">
+        <v>46293.300175462966</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>46293.30343341435</v>
+      </c>
+      <c r="O15" s="10" t="str">
+        <v>47c616df-95cf-5bff-8fc4-c91b26554e75</v>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="3" t="str">
+        <v>Z1</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>0.010935484583333334</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>0.004498038599537037</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>0.0030821414930555556</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.002666686180555556</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J16" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="L16" s="25" t="n">
+        <v>4.2804</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>46293.3615134375</v>
+      </c>
+      <c r="N16" s="27" t="n">
+        <v>46293.372448912036</v>
+      </c>
+      <c r="O16" s="3" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="10" t="str">
+        <v>Z1</v>
+      </c>
+      <c r="B17" s="10" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C17" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>0.009306901886574074</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>0.004153797349537036</v>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>0.0025064493402777777</v>
+      </c>
+      <c r="G17" s="20" t="n">
+        <v>0.0019094427199074075</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="J17" s="10" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>3.13394</v>
+      </c>
+      <c r="M17" s="28" t="n">
+        <v>46293.369176388886</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>46293.37848328704</v>
+      </c>
+      <c r="O17" s="10" t="str">
+        <v>04070cd2-53e0-510c-8373-2f6511f15052</v>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="3" t="str">
+        <v>Z1</v>
+      </c>
+      <c r="B18" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>0.013319931863425925</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>0.006750585625</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.004620488414351851</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.0012899919791666667</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J18" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <v>4.688094</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>46293.36918052084</v>
+      </c>
+      <c r="N18" s="27" t="n">
+        <v>46293.382500451386</v>
+      </c>
+      <c r="O18" s="3" t="str">
+        <v>05d4fa83-5d48-5d21-ab82-867e8af0819d</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="10" t="str">
+        <v>Z2</v>
+      </c>
+      <c r="B19" s="10" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C19" s="10" t="str">
+        <v>not_started</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="10" t="str">
+        <v>ea54ef0e-91b7-501e-996e-97ce42a15264</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="3" t="str">
+        <v>Z2</v>
+      </c>
+      <c r="B20" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <v>not_started</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="3" t="str">
+        <v>5427e1bf-1da3-5af3-80c7-31100873f585</v>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="10" t="str">
+        <v>Z2</v>
+      </c>
+      <c r="B21" s="10" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C21" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>0.018485020810185184</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>0.011562065601851851</v>
+      </c>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>3.926011</v>
+      </c>
+      <c r="M21" s="28" t="n">
+        <v>46293.36151353009</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>46293.37999855324</v>
+      </c>
+      <c r="O21" s="10" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="3" t="str">
+        <v>Z3</v>
+      </c>
+      <c r="B22" s="3" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <v>not_started</v>
+      </c>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="3" t="str">
+        <v>631ec33b-a46f-52f4-801e-9eab8cfc2efd</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="10" t="str">
+        <v>Z3</v>
+      </c>
+      <c r="B23" s="10" t="str">
+        <v>Kelly W.</v>
+      </c>
+      <c r="C23" s="10" t="str">
+        <v>not_started</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="10" t="str">
+        <v>684b62dc-6ab1-5285-aded-984c4d580d49</v>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="3" t="str">
+        <v>Z3</v>
+      </c>
+      <c r="B24" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C24" s="3" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0.0025698396527777776</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <v>1.120041</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>46293.36151351852</v>
+      </c>
+      <c r="N24" s="27" t="n">
+        <v>46293.36408335648</v>
+      </c>
+      <c r="O24" s="3" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="10" t="str">
+        <v>Z4</v>
+      </c>
+      <c r="B25" s="10" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C25" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>0.001627675</v>
+      </c>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>0.704624</v>
+      </c>
+      <c r="M25" s="28" t="n">
+        <v>46293.36922835648</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>46293.370856030095</v>
+      </c>
+      <c r="O25" s="10" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="3" t="str">
+        <v>Z5</v>
+      </c>
+      <c r="B26" s="3" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C26" s="3" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0.001657475451388889</v>
+      </c>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L26" s="25" t="n">
+        <v>0.736717</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>46293.39213855324</v>
+      </c>
+      <c r="N26" s="27" t="n">
+        <v>46293.39379603009</v>
+      </c>
+      <c r="O26" s="3" t="str">
+        <v>a909b721-e744-59b8-89de-7668baec343b</v>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="10" t="str">
+        <v>Z5</v>
+      </c>
+      <c r="B27" s="10" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C27" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>0.02543705539351852</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>0.016891375972222223</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0.004934316631944444</v>
+      </c>
+      <c r="G27" s="20"/>
+      <c r="H27" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="J27" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>2.262775</v>
+      </c>
+      <c r="M27" s="28" t="n">
+        <v>46293.39213418982</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>46293.41757125</v>
+      </c>
+      <c r="O27" s="10" t="str">
+        <v>436cb01b-602f-52fd-a83e-e1f08f8708fe</v>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="3" t="str">
+        <v>Z5</v>
+      </c>
+      <c r="B28" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>0.014482020127314815</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>0.011770511805555555</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>0.001826041076388889</v>
+      </c>
+      <c r="G28" s="19"/>
+      <c r="H28" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J28" s="3" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="L28" s="25" t="n">
+        <v>4.954714</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>46293.378438761574</v>
+      </c>
+      <c r="N28" s="27" t="n">
+        <v>46293.39292077546</v>
+      </c>
+      <c r="O28" s="3" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="10" t="str">
+        <v>Z6</v>
+      </c>
+      <c r="B29" s="10" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C29" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>0.010493027719907407</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0.005714940462962963</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.0019973045949074073</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0.002155830162037037</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="J29" s="10" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>3.270071</v>
+      </c>
+      <c r="M29" s="28" t="n">
+        <v>46293.40834320602</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>46293.41883623842</v>
+      </c>
+      <c r="O29" s="10" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="3" t="str">
+        <v>Z6</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>0.010950602453703705</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>0.00706084517361111</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>0.002860982627314815</v>
+      </c>
+      <c r="G30" s="19"/>
+      <c r="H30" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="J30" s="3" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="L30" s="25" t="n">
+        <v>4.16695</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>46293.4161315625</v>
+      </c>
+      <c r="N30" s="27" t="n">
+        <v>46293.42708217593</v>
+      </c>
+      <c r="O30" s="3" t="str">
+        <v>41ba4d68-d1da-57fd-9163-a0ec041a44bd</v>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="10" t="str">
+        <v>Z6</v>
+      </c>
+      <c r="B31" s="10" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C31" s="10" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>0.01604837917824074</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0.009032712430555555</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0.002023377627314815</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="J31" s="10" t="str">
+        <v>Not saved</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>4.962136</v>
+      </c>
+      <c r="M31" s="28" t="n">
+        <v>46293.41613568287</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>46293.4321840625</v>
+      </c>
+      <c r="O31" s="10" t="str">
+        <v>92047fb7-01a5-5611-802e-c886da87eb6a</v>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B32" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C32" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>0.0049308391435185185</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>0.002574656215277778</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>0.0011624419675925926</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>0.000586124675925926</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="J32" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L32" s="25" t="n">
+        <v>1.69375</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>46293.485895844904</v>
+      </c>
+      <c r="N32" s="27" t="n">
+        <v>46293.490826678244</v>
+      </c>
+      <c r="O32" s="3" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B33" s="31" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C33" s="31" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D33" s="38" t="n">
+        <v>0.006230505347222222</v>
+      </c>
+      <c r="E33" s="38" t="n">
+        <v>0.0034335118981481476</v>
+      </c>
+      <c r="F33" s="38" t="n">
+        <v>0.0012797492013888888</v>
+      </c>
+      <c r="G33" s="38" t="n">
+        <v>0.0013288225231481482</v>
+      </c>
+      <c r="H33" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="I33" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="J33" s="31" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K33" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="L33" s="40" t="n">
+        <v>1.844799</v>
+      </c>
+      <c r="M33" s="41" t="n">
+        <v>46293.48974427083</v>
+      </c>
+      <c r="N33" s="41" t="n">
+        <v>46293.49597476852</v>
+      </c>
+      <c r="O33" s="31" t="str">
+        <v>d9a7b71f-fa01-5b6b-8599-3119e6461527</v>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B34" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>0.007391702523148148</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>0.004000149548611111</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>0.002492175347222222</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>0.0005386652546296296</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="J34" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L34" s="25" t="n">
+        <v>2.382448</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>46293.48973981482</v>
+      </c>
+      <c r="N34" s="27" t="n">
+        <v>46293.49713152778</v>
+      </c>
+      <c r="O34" s="3" t="str">
+        <v>1a912ee3-806b-50ca-a0b5-d927cab2f677</v>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B35" s="31" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C35" s="31" t="str">
+        <v>needs_review</v>
+      </c>
+      <c r="D35" s="38" t="n">
+        <v>0.00783620886574074</v>
+      </c>
+      <c r="E35" s="38" t="n">
+        <v>0.0034936127083333335</v>
+      </c>
+      <c r="F35" s="38" t="n">
+        <v>0.0010293632060185186</v>
+      </c>
+      <c r="G35" s="38" t="n">
+        <v>0.0024442326157407407</v>
+      </c>
+      <c r="H35" s="31" t="n">
+        <v>49</v>
+      </c>
+      <c r="I35" s="31" t="n">
+        <v>49</v>
+      </c>
+      <c r="J35" s="31" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K35" s="31" t="n">
+        <v>86</v>
+      </c>
+      <c r="L35" s="40" t="n">
+        <v>2.295134</v>
+      </c>
+      <c r="M35" s="41" t="n">
+        <v>46293.48589585648</v>
+      </c>
+      <c r="N35" s="41" t="n">
+        <v>46293.49373206018</v>
+      </c>
+      <c r="O35" s="31" t="str">
+        <v>59d4870e-2207-56ca-a50b-e76ab86f6a53</v>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B36" s="3" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>0.006397073148148149</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>0.00300347443287037</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>0.0015125450810185186</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>0.0007983950231481481</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J36" s="3" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="L36" s="25" t="n">
+        <v>1.693585</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>46293.49205502315</v>
+      </c>
+      <c r="N36" s="27" t="n">
+        <v>46293.49845209491</v>
+      </c>
+      <c r="O36" s="3" t="str">
+        <v>23a89a4c-2a62-5501-9c22-24797bd232d0</v>
+      </c>
+    </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B37" s="31" t="str">
+        <v>Sanaz Yashar</v>
+      </c>
+      <c r="C37" s="31" t="str">
+        <v>completed</v>
+      </c>
+      <c r="D37" s="38" t="n">
+        <v>0.020490879907407406</v>
+      </c>
+      <c r="E37" s="38" t="n">
+        <v>0.008288524236111112</v>
+      </c>
+      <c r="F37" s="38" t="n">
+        <v>0.010730826597222222</v>
+      </c>
+      <c r="G37" s="38" t="n">
+        <v>0.0010439758564814814</v>
+      </c>
+      <c r="H37" s="31" t="n">
+        <v>55</v>
+      </c>
+      <c r="I37" s="31" t="n">
+        <v>55</v>
+      </c>
+      <c r="J37" s="31" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="K37" s="31" t="n">
+        <v>99</v>
+      </c>
+      <c r="L37" s="40" t="n">
+        <v>2.413869</v>
+      </c>
+      <c r="M37" s="41" t="n">
+        <v>46293.492059282406</v>
+      </c>
+      <c r="N37" s="41" t="n">
+        <v>46293.512550162035</v>
+      </c>
+      <c r="O37" s="31" t="str">
+        <v>2242afe2-3187-5d99-94aa-2cdced22669d</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="R33d9c66724044fa5"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4816,90 +5305,656 @@
         <v>Open evidence</v>
       </c>
     </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B80" s="3" t="str">
+        <v>Vari’s own ABM-building and Sales-partnership words</v>
+      </c>
+      <c r="C80" s="3" t="str">
+        <v>preserved</v>
+      </c>
+      <c r="D80" s="3" t="str">
+        <v>Like Grok A41/V22–23: preserves Vari’s own end-to-end ABM and Sales-partnership words. Strong useful signal.</v>
+      </c>
+      <c r="E80" s="3" t="str">
+        <v>account F026, vari F016</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G80" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="81" ht="68" customHeight="1">
+      <c r="A81" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B81" s="31" t="str">
+        <v>Lean ABM team, HubSpot build and measurable outcomes</v>
+      </c>
+      <c r="C81" s="31" t="str">
+        <v>preserved bundled</v>
+      </c>
+      <c r="D81" s="31" t="str">
+        <v>Hands-on HubSpot work, account tiers, buying groups and outcome measures survive. Grok A30–32 separates the units better. Muse interpretation “production-constrained” is stronger than a lean-role requirement proves.</v>
+      </c>
+      <c r="E81" s="31" t="str">
+        <v>account F011, account F012, account F013, vari F021, vari F022</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="G81" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="82" ht="54" customHeight="1">
+      <c r="A82" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B82" s="3" t="str">
+        <v>Nick’s Monday report with five-tool workflow</v>
+      </c>
+      <c r="C82" s="3" t="str">
+        <v>account omission recovered person</v>
+      </c>
+      <c r="D82" s="3" t="str">
+        <v>The full workflow was in account media-discovery results but omitted from the account JSON. Nick later preserves all five tools and the self-built Claude workflow. Grok retained it at account stage.</v>
+      </c>
+      <c r="E82" s="3" t="str">
+        <v>nick F047</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="83" ht="54" customHeight="1">
+      <c r="A83" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B83" s="31" t="str">
+        <v>AI-first GTM hiring: shipping real workflows</v>
+      </c>
+      <c r="C83" s="31" t="str">
+        <v>preserved bundled</v>
+      </c>
+      <c r="D83" s="31" t="str">
+        <v>Distinctive “shipping real workflows” survives in both stages. Account F024 unnecessarily combines the 2026 hiring post with a separate April 2024 joining/Gong article.</v>
+      </c>
+      <c r="E83" s="31" t="str">
+        <v>account F024, nick F061</v>
+      </c>
+      <c r="F83" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="84" ht="68" customHeight="1">
+      <c r="A84" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B84" s="3" t="str">
+        <v>AI overwriting pipeline / prospect-blast warning</v>
+      </c>
+      <c r="C84" s="3" t="str">
+        <v>account omission recovered person</v>
+      </c>
+      <c r="D84" s="3" t="str">
+        <v>Account acquired the warning but omitted it. Nick quotes both concrete harms, improving on the earlier Muse max run. Grok also recovered both in person research, with clearer attribution of the relayed Lemkin practices.</v>
+      </c>
+      <c r="E84" s="3" t="str">
+        <v>nick F046</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="85" ht="54" customHeight="1">
+      <c r="A85" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B85" s="31" t="str">
+        <v>Idea to working demo in hours</v>
+      </c>
+      <c r="C85" s="31" t="str">
+        <v>account omission recovered person</v>
+      </c>
+      <c r="D85" s="31" t="str">
+        <v>Exact idea-to-demo-in-hours passage was in account-deep returned sources but absent from account findings. Nick restores it. Grok retained it at both stages.</v>
+      </c>
+      <c r="E85" s="31" t="str">
+        <v>nick F048</v>
+      </c>
+      <c r="F85" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="86" ht="54" customHeight="1">
+      <c r="A86" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B86" s="3" t="str">
+        <v>Nick’s record-store and comic-store marketing methods</v>
+      </c>
+      <c r="C86" s="3" t="str">
+        <v>partial account recovered person</v>
+      </c>
+      <c r="D86" s="3" t="str">
+        <v>Account retained the 2024 record-store campaign but omitted acquired 2026 comic-store details. Nick preserves both distinct tactics and reported results, broadly comparable to Grok person depth.</v>
+      </c>
+      <c r="E86" s="3" t="str">
+        <v>account F023, nick F043, nick F044, nick F070</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G86" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="87" ht="68" customHeight="1">
+      <c r="A87" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B87" s="31" t="str">
+        <v>Exposure Gateway and Zero Day Agent details</v>
+      </c>
+      <c r="C87" s="31" t="str">
+        <v>selection and discovery gaps</v>
+      </c>
+      <c r="D87" s="31" t="str">
+        <v>Zero Day Agent and the September Asset Ownership Agent announcement were returned but have no substantive findings. Exposure Gateway was not found in the targeted saved-result scan. Grok A21/A22 retained dated author, mechanism, integrations and response workflow.</v>
+      </c>
+      <c r="E87" s="31" t="str">
+        <v>account F001</v>
+      </c>
+      <c r="F87" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="88" ht="68" customHeight="1">
+      <c r="A88" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B88" s="3" t="str">
+        <v>Funding versus revenue/ARR and adverse reporting</v>
+      </c>
+      <c r="C88" s="3" t="str">
+        <v>partial with omission</v>
+      </c>
+      <c r="D88" s="3" t="str">
+        <v>Series C and Cisco survive. A direct February Amex announcement was retrieved but omitted. Grok also captured later journalist ARR/acquisition context; that adverse reporting was not located in Muse returned-result scans. Funding is not marketing budget.</v>
+      </c>
+      <c r="E88" s="3" t="str">
+        <v>account F006, account F007</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="89" ht="68" customHeight="1">
+      <c r="A89" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B89" s="31" t="str">
+        <v>Snir departure versus stale CPO listing</v>
+      </c>
+      <c r="C89" s="31" t="str">
+        <v>discovery gap</v>
+      </c>
+      <c r="D89" s="31" t="str">
+        <v>No departure passage located in Muse returned results. Grok A91 retained a qualified secondary report. Muse founder/leadership lists do not replace this dated contrary evidence; neither run proves the external report is true.</v>
+      </c>
+      <c r="E89" s="31" t="str">
+        <v>account F027</v>
+      </c>
+      <c r="F89" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="90" ht="54" customHeight="1">
+      <c r="A90" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B90" s="3" t="str">
+        <v>Sanaz’s ambiguous “5X in new $$$$$” public wording</v>
+      </c>
+      <c r="C90" s="3" t="str">
+        <v>selection omission</v>
+      </c>
+      <c r="D90" s="3" t="str">
+        <v>The same account-deep results include Sanaz’s “5X in new $$$$$” and almost-80% MTTR statement. Neither appears in Muse authored findings. Grok also omitted the 5X signal: the baseline is not complete.</v>
+      </c>
+      <c r="E90" s="3" t="str"/>
+      <c r="F90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="91" ht="68" customHeight="1">
+      <c r="A91" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B91" s="31" t="str">
+        <v>Career tools versus employer deployment</v>
+      </c>
+      <c r="C91" s="31" t="str">
+        <v>mixed scope and contradiction</v>
+      </c>
+      <c r="D91" s="31" t="str">
+        <v>Career tools and employer installations are usually distinguished well. But account F019 says Gong was not named in any Zafran source while F024 already cites Nick’s first-week Gong-call research. That contradiction survives the final account narrative.</v>
+      </c>
+      <c r="E91" s="31" t="str">
+        <v>account F019, account F024, nick F041, nick F065, vari F020</v>
+      </c>
+      <c r="F91" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="G91" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="92" ht="68" customHeight="1">
+      <c r="A92" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B92" s="3" t="str">
+        <v>Cocktail Chemistry, book and audience feedback</v>
+      </c>
+      <c r="C92" s="3" t="str">
+        <v>rich shortform preservation</v>
+      </c>
+      <c r="D92" s="3" t="str">
+        <v>Strong book/hobby/audience-feedback wording, visible on the contact page. Grok also had an additional first-person kitchen/hobby passage not located in Muse acquisition. One very large Muse book finding bundles several independently usable details.</v>
+      </c>
+      <c r="E92" s="3" t="str">
+        <v>nick F030, nick F031, nick F032</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="93" ht="68" customHeight="1">
+      <c r="A93" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B93" s="31" t="str">
+        <v>CocktailGPT project follow-through</v>
+      </c>
+      <c r="C93" s="31" t="str">
+        <v>lead only</v>
+      </c>
+      <c r="D93" s="31" t="str">
+        <v>Project name, profile description and date retained; no project-site fetch. Similar limitation to Grok, behind the earlier Muse max run which inspected the site. Do not claim all available side-project depth was exhausted.</v>
+      </c>
+      <c r="E93" s="31" t="str">
+        <v>nick F033</v>
+      </c>
+      <c r="F93" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="94" ht="54" customHeight="1">
+      <c r="A94" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B94" s="3" t="str">
+        <v>Nick’s authored PMM principles and credibility deck</v>
+      </c>
+      <c r="C94" s="3" t="str">
+        <v>lead only</v>
+      </c>
+      <c r="D94" s="3" t="str">
+        <v>Publication titles survive, not the actual old article/deck arguments. Both this retry and Grok miss substance found by the earlier Muse max run; a reason to retain a cross-run evidence union.</v>
+      </c>
+      <c r="E94" s="3" t="str">
+        <v>nick F034</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="95" ht="68" customHeight="1">
+      <c r="A95" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B95" s="31" t="str">
+        <v>Nick’s ISMG interview: actual speech versus listing</v>
+      </c>
+      <c r="C95" s="31" t="str">
+        <v>listing only no transcription</v>
+      </c>
+      <c r="D95" s="31" t="str">
+        <v>Muse keeps ISMG/Okta metadata, performs no recording-resolution or transcription call, and stops after discovering listings. Grok obtained actual ISMG speech with speaker/history qualifications. No failed transcription attempt establishes provider unavailability here.</v>
+      </c>
+      <c r="E95" s="31" t="str">
+        <v>nick F080, nick F081, nick F082, nick F083, nick F084</v>
+      </c>
+      <c r="F95" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="96" ht="68" customHeight="1">
+      <c r="A96" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B96" s="3" t="str">
+        <v>Vari’s employer-specific Salesforce–HubSpot work</v>
+      </c>
+      <c r="C96" s="3" t="str">
+        <v>source review failure</v>
+      </c>
+      <c r="D96" s="3" t="str">
+        <v>Axiom integration is present but downgraded to synthesis-only insufficient context, despite the directly returned profile containing the full Salesforce–HubSpot quote. Grok V10 uses that passage correctly. Both preserve the truncated 25% metric without inventing an endpoint.</v>
+      </c>
+      <c r="E96" s="3" t="str">
+        <v>vari F009, vari F010</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="97" ht="68" customHeight="1">
+      <c r="A97" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B97" s="31" t="str">
+        <v>Vari’s credentials and thin personal footprint</v>
+      </c>
+      <c r="C97" s="31" t="str">
+        <v>thinner profile discovery</v>
+      </c>
+      <c r="D97" s="31" t="str">
+        <v>Education and thin outside-work footprint are qualified. Explicit 6sense/Demandbase certification findings are absent; exact credential passages not located in acquired-result scan. Grok retains credentials; neither should invent hobbies.</v>
+      </c>
+      <c r="E97" s="31" t="str">
+        <v>vari F014, vari F024, vari F025</v>
+      </c>
+      <c r="F97" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="98" ht="82" customHeight="1">
+      <c r="A98" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B98" s="3" t="str">
+        <v>Wrong entity, research bookkeeping and bundling</v>
+      </c>
+      <c r="C98" s="3" t="str">
+        <v>material attribution and claim hygiene defects</v>
+      </c>
+      <c r="D98" s="3" t="str">
+        <v>Vari F004 assigns Secureworks and Ivanti experience to current Zafran. Research gaps and analyst characterizations are stored as supported observations. Independent posts/events/people remain bundled. Grok also has bookkeeping, duplication and bundling defects; it is a comparative baseline, not gold truth.</v>
+      </c>
+      <c r="E98" s="3" t="str">
+        <v>account F015, account F024, account F030, account F031, nick F084, nick F091, nick F100, vari F004, vari F006, vari F023, vari F024</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="99" ht="82" customHeight="1">
+      <c r="A99" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B99" s="31" t="str">
+        <v>Initial narrative usefulness and fidelity</v>
+      </c>
+      <c r="C99" s="31" t="str">
+        <v>published useful but inaccurate in places</v>
+      </c>
+      <c r="D99" s="31" t="str">
+        <v>All initial pages are saved. Nick’s page preserves strong quotations and seller-relevance caveats. Vari’s page repeats the wrong-employer remit; account tooling contradicts its own Gong evidence. Final account page includes common Muse reconciliation, assessed separately from initial authoring.</v>
+      </c>
+      <c r="E99" s="31" t="str">
+        <v>account F019, account F024, nick F046, nick F047, vari F004</v>
+      </c>
+      <c r="F99" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B100" s="3" t="str">
+        <v>Wrong-employer attribution</v>
+      </c>
+      <c r="C100" s="3" t="str">
+        <v>Confirmed source contradiction</v>
+      </c>
+      <c r="D100" s="3" t="str">
+        <v>Secureworks and Ivanti bullets became current Zafran remit; error reaches Vari page. Full returned profile clearly separates employers.</v>
+      </c>
+      <c r="E100" s="3" t="str">
+        <v>Vari F004 vs F006 and profile headings</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="101" ht="54" customHeight="1">
+      <c r="A101" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B101" s="31" t="str">
+        <v>Narrative citation support</v>
+      </c>
+      <c r="C101" s="31" t="str">
+        <v>Specifics absent from cited claim</v>
+      </c>
+      <c r="D101" s="31" t="str">
+        <v>Initial Amex February event cites only Cisco F007; hackathon hours cite F024 hiring/joining. Facts have raw support, but cited claims do not contain those specifics.</v>
+      </c>
+      <c r="E101" s="31" t="str">
+        <v>Initial money-and-momentum / why-now</v>
+      </c>
+      <c r="F101" s="31"/>
+      <c r="G101" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="102" ht="54" customHeight="1">
+      <c r="A102" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B102" s="3" t="str">
+        <v>Import text fidelity</v>
+      </c>
+      <c r="C102" s="3" t="str">
+        <v>109 of 109 preserved</v>
+      </c>
+      <c r="D102" s="3" t="str">
+        <v>Programmatic comparison found no finding-text differences between 109 authored entries and imported records. This does not validate factual accuracy or prove all research was selected.</v>
+      </c>
+      <c r="E102" s="3" t="str">
+        <v>31 account / 53 Nick / 25 Vari</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="103" ht="54" customHeight="1">
+      <c r="A103" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B103" s="31" t="str">
+        <v>Comparable person research</v>
+      </c>
+      <c r="C103" s="31" t="str">
+        <v>Not the requested subjects</v>
+      </c>
+      <c r="D103" s="31" t="str">
+        <v>GLM selected Tom/Sanaz rather than fixed Nick/Vari. Final outputs are available; no new full semantic grading of these different people in this update.</v>
+      </c>
+      <c r="E103" s="31" t="str">
+        <v>49 account / 33 Tom / 55 Sanaz</v>
+      </c>
+      <c r="F103" s="31"/>
+      <c r="G103" s="43" t="str">
+        <v>Open status</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G6" r:id="NativeLink1"/>
-    <hyperlink ref="G7" r:id="NativeLink2"/>
-    <hyperlink ref="G8" r:id="NativeLink3"/>
-    <hyperlink ref="G9" r:id="NativeLink4"/>
-    <hyperlink ref="G10" r:id="NativeLink5"/>
-    <hyperlink ref="G11" r:id="NativeLink6"/>
-    <hyperlink ref="G12" r:id="NativeLink7"/>
-    <hyperlink ref="G13" r:id="NativeLink8"/>
-    <hyperlink ref="G14" r:id="NativeLink9"/>
-    <hyperlink ref="G15" r:id="NativeLink10"/>
-    <hyperlink ref="G16" r:id="NativeLink11"/>
-    <hyperlink ref="G17" r:id="NativeLink12"/>
-    <hyperlink ref="G18" r:id="NativeLink13"/>
-    <hyperlink ref="G19" r:id="NativeLink14"/>
-    <hyperlink ref="G20" r:id="NativeLink15"/>
-    <hyperlink ref="G21" r:id="NativeLink16"/>
-    <hyperlink ref="G22" r:id="NativeLink17"/>
-    <hyperlink ref="G23" r:id="NativeLink18"/>
-    <hyperlink ref="G24" r:id="NativeLink19"/>
-    <hyperlink ref="G25" r:id="NativeLink20"/>
-    <hyperlink ref="G26" r:id="NativeLink21"/>
-    <hyperlink ref="G27" r:id="NativeLink22"/>
-    <hyperlink ref="G28" r:id="NativeLink23"/>
-    <hyperlink ref="G29" r:id="NativeLink24"/>
-    <hyperlink ref="G30" r:id="NativeLink25"/>
-    <hyperlink ref="G31" r:id="NativeLink26"/>
-    <hyperlink ref="G32" r:id="NativeLink27"/>
-    <hyperlink ref="G33" r:id="NativeLink28"/>
-    <hyperlink ref="G34" r:id="NativeLink29"/>
-    <hyperlink ref="G35" r:id="NativeLink30"/>
-    <hyperlink ref="G36" r:id="NativeLink31"/>
-    <hyperlink ref="G37" r:id="NativeLink32"/>
-    <hyperlink ref="G38" r:id="NativeLink33"/>
-    <hyperlink ref="G39" r:id="NativeLink34"/>
-    <hyperlink ref="G40" r:id="NativeLink35"/>
-    <hyperlink ref="G41" r:id="NativeLink36"/>
-    <hyperlink ref="G42" r:id="NativeLink37"/>
-    <hyperlink ref="G43" r:id="NativeLink38"/>
-    <hyperlink ref="G44" r:id="NativeLink39"/>
-    <hyperlink ref="G45" r:id="NativeLink40"/>
-    <hyperlink ref="G46" r:id="NativeLink41"/>
-    <hyperlink ref="G47" r:id="NativeLink42"/>
-    <hyperlink ref="G48" r:id="NativeLink43"/>
-    <hyperlink ref="G49" r:id="NativeLink44"/>
-    <hyperlink ref="G50" r:id="NativeLink45"/>
-    <hyperlink ref="G51" r:id="NativeLink46"/>
-    <hyperlink ref="G52" r:id="NativeLink47"/>
-    <hyperlink ref="G53" r:id="NativeLink48"/>
-    <hyperlink ref="G54" r:id="NativeLink49"/>
-    <hyperlink ref="G55" r:id="NativeLink50"/>
-    <hyperlink ref="G56" r:id="NativeLink51"/>
-    <hyperlink ref="G57" r:id="NativeLink52"/>
-    <hyperlink ref="G58" r:id="NativeLink53"/>
-    <hyperlink ref="G59" r:id="NativeLink54"/>
-    <hyperlink ref="G60" r:id="NativeLink55"/>
-    <hyperlink ref="G61" r:id="NativeLink56"/>
-    <hyperlink ref="G62" r:id="NativeLink57"/>
-    <hyperlink ref="G63" r:id="NativeLink58"/>
-    <hyperlink ref="G64" r:id="NativeLink59"/>
-    <hyperlink ref="G65" r:id="NativeLink60"/>
-    <hyperlink ref="G66" r:id="NativeLink61"/>
-    <hyperlink ref="G67" r:id="NativeLink62"/>
-    <hyperlink ref="G68" r:id="NativeLink63"/>
-    <hyperlink ref="G69" r:id="NativeLink64"/>
-    <hyperlink ref="G70" r:id="NativeLink65"/>
-    <hyperlink ref="G71" r:id="NativeLink66"/>
-    <hyperlink ref="G72" r:id="NativeLink67"/>
-    <hyperlink ref="G73" r:id="NativeLink68"/>
-    <hyperlink ref="G74" r:id="NativeLink69"/>
-    <hyperlink ref="G75" r:id="NativeLink70"/>
-    <hyperlink ref="G76" r:id="NativeLink71"/>
-    <hyperlink ref="G77" r:id="NativeLink72"/>
-    <hyperlink ref="G78" r:id="NativeLink73"/>
-    <hyperlink ref="G79" r:id="NativeLink74"/>
+    <hyperlink ref="G6" r:id="VerifiedLink11"/>
+    <hyperlink ref="G7" r:id="VerifiedLink12"/>
+    <hyperlink ref="G8" r:id="VerifiedLink13"/>
+    <hyperlink ref="G9" r:id="VerifiedLink14"/>
+    <hyperlink ref="G10" r:id="VerifiedLink15"/>
+    <hyperlink ref="G11" r:id="VerifiedLink16"/>
+    <hyperlink ref="G12" r:id="VerifiedLink17"/>
+    <hyperlink ref="G13" r:id="VerifiedLink18"/>
+    <hyperlink ref="G14" r:id="VerifiedLink19"/>
+    <hyperlink ref="G15" r:id="VerifiedLink20"/>
+    <hyperlink ref="G16" r:id="VerifiedLink21"/>
+    <hyperlink ref="G17" r:id="VerifiedLink22"/>
+    <hyperlink ref="G18" r:id="VerifiedLink23"/>
+    <hyperlink ref="G19" r:id="VerifiedLink24"/>
+    <hyperlink ref="G20" r:id="VerifiedLink25"/>
+    <hyperlink ref="G21" r:id="VerifiedLink26"/>
+    <hyperlink ref="G22" r:id="VerifiedLink27"/>
+    <hyperlink ref="G23" r:id="VerifiedLink28"/>
+    <hyperlink ref="G24" r:id="VerifiedLink29"/>
+    <hyperlink ref="G25" r:id="VerifiedLink30"/>
+    <hyperlink ref="G26" r:id="VerifiedLink31"/>
+    <hyperlink ref="G27" r:id="VerifiedLink32"/>
+    <hyperlink ref="G28" r:id="VerifiedLink33"/>
+    <hyperlink ref="G29" r:id="VerifiedLink34"/>
+    <hyperlink ref="G30" r:id="VerifiedLink35"/>
+    <hyperlink ref="G31" r:id="VerifiedLink36"/>
+    <hyperlink ref="G32" r:id="VerifiedLink37"/>
+    <hyperlink ref="G33" r:id="VerifiedLink38"/>
+    <hyperlink ref="G34" r:id="VerifiedLink39"/>
+    <hyperlink ref="G35" r:id="VerifiedLink40"/>
+    <hyperlink ref="G36" r:id="VerifiedLink41"/>
+    <hyperlink ref="G37" r:id="VerifiedLink42"/>
+    <hyperlink ref="G38" r:id="VerifiedLink43"/>
+    <hyperlink ref="G39" r:id="VerifiedLink44"/>
+    <hyperlink ref="G40" r:id="VerifiedLink45"/>
+    <hyperlink ref="G41" r:id="VerifiedLink46"/>
+    <hyperlink ref="G42" r:id="VerifiedLink47"/>
+    <hyperlink ref="G43" r:id="VerifiedLink48"/>
+    <hyperlink ref="G44" r:id="VerifiedLink49"/>
+    <hyperlink ref="G45" r:id="VerifiedLink50"/>
+    <hyperlink ref="G46" r:id="VerifiedLink51"/>
+    <hyperlink ref="G47" r:id="VerifiedLink52"/>
+    <hyperlink ref="G48" r:id="VerifiedLink53"/>
+    <hyperlink ref="G49" r:id="VerifiedLink54"/>
+    <hyperlink ref="G50" r:id="VerifiedLink55"/>
+    <hyperlink ref="G51" r:id="VerifiedLink56"/>
+    <hyperlink ref="G52" r:id="VerifiedLink57"/>
+    <hyperlink ref="G53" r:id="VerifiedLink58"/>
+    <hyperlink ref="G54" r:id="VerifiedLink59"/>
+    <hyperlink ref="G55" r:id="VerifiedLink60"/>
+    <hyperlink ref="G56" r:id="VerifiedLink61"/>
+    <hyperlink ref="G57" r:id="VerifiedLink62"/>
+    <hyperlink ref="G58" r:id="VerifiedLink63"/>
+    <hyperlink ref="G59" r:id="VerifiedLink64"/>
+    <hyperlink ref="G60" r:id="VerifiedLink65"/>
+    <hyperlink ref="G61" r:id="VerifiedLink66"/>
+    <hyperlink ref="G62" r:id="VerifiedLink67"/>
+    <hyperlink ref="G63" r:id="VerifiedLink68"/>
+    <hyperlink ref="G64" r:id="VerifiedLink69"/>
+    <hyperlink ref="G65" r:id="VerifiedLink70"/>
+    <hyperlink ref="G66" r:id="VerifiedLink71"/>
+    <hyperlink ref="G67" r:id="VerifiedLink72"/>
+    <hyperlink ref="G68" r:id="VerifiedLink73"/>
+    <hyperlink ref="G69" r:id="VerifiedLink74"/>
+    <hyperlink ref="G70" r:id="VerifiedLink75"/>
+    <hyperlink ref="G71" r:id="VerifiedLink76"/>
+    <hyperlink ref="G72" r:id="VerifiedLink77"/>
+    <hyperlink ref="G73" r:id="VerifiedLink78"/>
+    <hyperlink ref="G74" r:id="VerifiedLink79"/>
+    <hyperlink ref="G75" r:id="VerifiedLink80"/>
+    <hyperlink ref="G76" r:id="VerifiedLink81"/>
+    <hyperlink ref="G77" r:id="VerifiedLink82"/>
+    <hyperlink ref="G78" r:id="VerifiedLink83"/>
+    <hyperlink ref="G79" r:id="VerifiedLink84"/>
+    <hyperlink ref="G80" r:id="VerifiedLink412"/>
+    <hyperlink ref="G81" r:id="VerifiedLink413"/>
+    <hyperlink ref="G82" r:id="VerifiedLink414"/>
+    <hyperlink ref="G83" r:id="VerifiedLink415"/>
+    <hyperlink ref="G84" r:id="VerifiedLink416"/>
+    <hyperlink ref="G85" r:id="VerifiedLink417"/>
+    <hyperlink ref="G86" r:id="VerifiedLink418"/>
+    <hyperlink ref="G87" r:id="VerifiedLink419"/>
+    <hyperlink ref="G88" r:id="VerifiedLink420"/>
+    <hyperlink ref="G89" r:id="VerifiedLink421"/>
+    <hyperlink ref="G90" r:id="VerifiedLink422"/>
+    <hyperlink ref="G91" r:id="VerifiedLink423"/>
+    <hyperlink ref="G92" r:id="VerifiedLink424"/>
+    <hyperlink ref="G93" r:id="VerifiedLink425"/>
+    <hyperlink ref="G94" r:id="VerifiedLink426"/>
+    <hyperlink ref="G95" r:id="VerifiedLink427"/>
+    <hyperlink ref="G96" r:id="VerifiedLink428"/>
+    <hyperlink ref="G97" r:id="VerifiedLink429"/>
+    <hyperlink ref="G98" r:id="VerifiedLink430"/>
+    <hyperlink ref="G99" r:id="VerifiedLink431"/>
+    <hyperlink ref="G100" r:id="VerifiedLink432"/>
+    <hyperlink ref="G101" r:id="VerifiedLink433"/>
+    <hyperlink ref="G102" r:id="VerifiedLink434"/>
+    <hyperlink ref="G103" r:id="VerifiedLink435"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R0986ddf37d07417d"/>
+    <tablePart r:id="R59c9011b8fc747f4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5655,50 +6710,176 @@
         <v>Open evidence</v>
       </c>
     </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B40" s="3" t="str">
+        <v>Common reconciliation</v>
+      </c>
+      <c r="C40" s="3" t="str">
+        <v>Response-shape contract</v>
+      </c>
+      <c r="D40" s="3" t="str">
+        <v>Revision175 failed: Each update needs page and section only. Revision176 completed. All research jobs and pages survived.</v>
+      </c>
+      <c r="E40" s="3" t="str">
+        <v>Confirmed logs; common Muse model, separate from researcher</v>
+      </c>
+      <c r="F40" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B41" s="31" t="str">
+        <v>Vari narrative</v>
+      </c>
+      <c r="C41" s="31" t="str">
+        <v>Recovered tool arguments</v>
+      </c>
+      <c r="D41" s="31" t="str">
+        <v>Narrative shape/quotation errors required revised calls; final contact page stored and job completed.</v>
+      </c>
+      <c r="E41" s="31" t="str">
+        <v>Observed recovery; semantic attribution error remains separately</v>
+      </c>
+      <c r="F41" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B42" s="3" t="str">
+        <v>Committee selection</v>
+      </c>
+      <c r="C42" s="3" t="str">
+        <v>Assignment deviation</v>
+      </c>
+      <c r="D42" s="3" t="str">
+        <v>Account nominated Tom Anthony and Sanaz Yashar instead of the fixed Nick Fisher and Vari Kaur. Both nominated people completed.</v>
+      </c>
+      <c r="E42" s="3" t="str">
+        <v>Confirmed subjects; not a controlled person comparison</v>
+      </c>
+      <c r="F42" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="43" ht="54" customHeight="1">
+      <c r="A43" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B43" s="31" t="str">
+        <v>Account finalization</v>
+      </c>
+      <c r="C43" s="31" t="str">
+        <v>Invalid references / unresolved tool failures</v>
+      </c>
+      <c r="D43" s="31" t="str">
+        <v>Rejected invalid unprocessed-source IDs, then nine unresolved failed nodes. Account ended needs_review despite saved49 findings and two pages.</v>
+      </c>
+      <c r="E43" s="31" t="str">
+        <v>Confirmed; do not equate failure with lost research</v>
+      </c>
+      <c r="F43" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B44" s="3" t="str">
+        <v>Tom finalization</v>
+      </c>
+      <c r="C44" s="3" t="str">
+        <v>Recovered completion schema</v>
+      </c>
+      <c r="D44" s="3" t="str">
+        <v>Unsupported subject_id in CompletionNotes rejected; corrected and completed.</v>
+      </c>
+      <c r="E44" s="3" t="str">
+        <v>Confirmed recovery</v>
+      </c>
+      <c r="F44" s="23" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B45" s="31" t="str">
+        <v>Common reconciliation</v>
+      </c>
+      <c r="C45" s="31" t="str">
+        <v>Response-shape contract</v>
+      </c>
+      <c r="D45" s="31" t="str">
+        <v>Revisions203 and204 failed: Each update needs page and section only. Generation settled needs_review with existing pages intact.</v>
+      </c>
+      <c r="E45" s="31" t="str">
+        <v>Confirmed; common Muse reconciliation, not GLM researcher</v>
+      </c>
+      <c r="F45" s="43" t="str">
+        <v>Open evidence</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="NativeLink1"/>
-    <hyperlink ref="F7" r:id="NativeLink2"/>
-    <hyperlink ref="F8" r:id="NativeLink3"/>
-    <hyperlink ref="F9" r:id="NativeLink4"/>
-    <hyperlink ref="F10" r:id="NativeLink5"/>
-    <hyperlink ref="F11" r:id="NativeLink6"/>
-    <hyperlink ref="F12" r:id="NativeLink7"/>
-    <hyperlink ref="F13" r:id="NativeLink8"/>
-    <hyperlink ref="F14" r:id="NativeLink9"/>
-    <hyperlink ref="F15" r:id="NativeLink10"/>
-    <hyperlink ref="F16" r:id="NativeLink11"/>
-    <hyperlink ref="F17" r:id="NativeLink12"/>
-    <hyperlink ref="F18" r:id="NativeLink13"/>
-    <hyperlink ref="F19" r:id="NativeLink14"/>
-    <hyperlink ref="F20" r:id="NativeLink15"/>
-    <hyperlink ref="F21" r:id="NativeLink16"/>
-    <hyperlink ref="F22" r:id="NativeLink17"/>
-    <hyperlink ref="F23" r:id="NativeLink18"/>
-    <hyperlink ref="F24" r:id="NativeLink19"/>
-    <hyperlink ref="F25" r:id="NativeLink20"/>
-    <hyperlink ref="F26" r:id="NativeLink21"/>
-    <hyperlink ref="F27" r:id="NativeLink22"/>
-    <hyperlink ref="F28" r:id="NativeLink23"/>
-    <hyperlink ref="F29" r:id="NativeLink24"/>
-    <hyperlink ref="F30" r:id="NativeLink25"/>
-    <hyperlink ref="F31" r:id="NativeLink26"/>
-    <hyperlink ref="F32" r:id="NativeLink27"/>
-    <hyperlink ref="F33" r:id="NativeLink28"/>
-    <hyperlink ref="F34" r:id="NativeLink29"/>
-    <hyperlink ref="F35" r:id="NativeLink30"/>
-    <hyperlink ref="F36" r:id="NativeLink31"/>
-    <hyperlink ref="F37" r:id="NativeLink32"/>
-    <hyperlink ref="F38" r:id="NativeLink33"/>
-    <hyperlink ref="F39" r:id="NativeLink34"/>
+    <hyperlink ref="F6" r:id="VerifiedLink85"/>
+    <hyperlink ref="F7" r:id="VerifiedLink86"/>
+    <hyperlink ref="F8" r:id="VerifiedLink87"/>
+    <hyperlink ref="F9" r:id="VerifiedLink88"/>
+    <hyperlink ref="F10" r:id="VerifiedLink89"/>
+    <hyperlink ref="F11" r:id="VerifiedLink90"/>
+    <hyperlink ref="F12" r:id="VerifiedLink91"/>
+    <hyperlink ref="F13" r:id="VerifiedLink92"/>
+    <hyperlink ref="F14" r:id="VerifiedLink93"/>
+    <hyperlink ref="F15" r:id="VerifiedLink94"/>
+    <hyperlink ref="F16" r:id="VerifiedLink95"/>
+    <hyperlink ref="F17" r:id="VerifiedLink96"/>
+    <hyperlink ref="F18" r:id="VerifiedLink97"/>
+    <hyperlink ref="F19" r:id="VerifiedLink98"/>
+    <hyperlink ref="F20" r:id="VerifiedLink99"/>
+    <hyperlink ref="F21" r:id="VerifiedLink100"/>
+    <hyperlink ref="F22" r:id="VerifiedLink101"/>
+    <hyperlink ref="F23" r:id="VerifiedLink102"/>
+    <hyperlink ref="F24" r:id="VerifiedLink103"/>
+    <hyperlink ref="F25" r:id="VerifiedLink104"/>
+    <hyperlink ref="F26" r:id="VerifiedLink105"/>
+    <hyperlink ref="F27" r:id="VerifiedLink106"/>
+    <hyperlink ref="F28" r:id="VerifiedLink107"/>
+    <hyperlink ref="F29" r:id="VerifiedLink108"/>
+    <hyperlink ref="F30" r:id="VerifiedLink109"/>
+    <hyperlink ref="F31" r:id="VerifiedLink110"/>
+    <hyperlink ref="F32" r:id="VerifiedLink111"/>
+    <hyperlink ref="F33" r:id="VerifiedLink112"/>
+    <hyperlink ref="F34" r:id="VerifiedLink113"/>
+    <hyperlink ref="F35" r:id="VerifiedLink114"/>
+    <hyperlink ref="F36" r:id="VerifiedLink115"/>
+    <hyperlink ref="F37" r:id="VerifiedLink116"/>
+    <hyperlink ref="F38" r:id="VerifiedLink117"/>
+    <hyperlink ref="F39" r:id="VerifiedLink118"/>
+    <hyperlink ref="F40" r:id="VerifiedLink436"/>
+    <hyperlink ref="F41" r:id="VerifiedLink437"/>
+    <hyperlink ref="F42" r:id="VerifiedLink438"/>
+    <hyperlink ref="F43" r:id="VerifiedLink439"/>
+    <hyperlink ref="F44" r:id="VerifiedLink440"/>
+    <hyperlink ref="F45" r:id="VerifiedLink441"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R0f3877d485e74d99"/>
+    <tablePart r:id="R04377d9c323447c1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11926,1310 +13107,2467 @@
         <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/arv4-insight-premier-muse-20260928-run03</v>
       </c>
     </row>
+    <row r="357" ht="54" customHeight="1">
+      <c r="A357" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B357" s="31" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C357" s="31" t="str">
+        <v>Claim JSON</v>
+      </c>
+      <c r="D357" s="43" t="str">
+        <v>Open Claim JSON</v>
+      </c>
+      <c r="E357" s="31" t="str"/>
+      <c r="F357" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/59d4870e-2207-56ca-a50b-e76ab86f6a53/dossier.json</v>
+      </c>
+    </row>
+    <row r="358" ht="54" customHeight="1">
+      <c r="A358" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B358" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C358" s="3" t="str">
+        <v>Readable dossier</v>
+      </c>
+      <c r="D358" s="23" t="str">
+        <v>Open Readable dossier</v>
+      </c>
+      <c r="E358" s="3" t="str"/>
+      <c r="F358" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/59d4870e-2207-56ca-a50b-e76ab86f6a53/dossier.md</v>
+      </c>
+    </row>
+    <row r="359" ht="54" customHeight="1">
+      <c r="A359" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B359" s="31" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C359" s="31" t="str">
+        <v>Imported claims</v>
+      </c>
+      <c r="D359" s="43" t="str">
+        <v>Open Imported claims</v>
+      </c>
+      <c r="E359" s="31" t="str"/>
+      <c r="F359" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/59d4870e-2207-56ca-a50b-e76ab86f6a53/imported-claims.json</v>
+      </c>
+    </row>
+    <row r="360" ht="40" customHeight="1">
+      <c r="A360" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B360" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C360" s="3" t="str">
+        <v>Saved narrative</v>
+      </c>
+      <c r="D360" s="23" t="str">
+        <v>Open Saved narrative</v>
+      </c>
+      <c r="E360" s="3" t="str">
+        <v>Account may include common reconciliation; see initial version separately.</v>
+      </c>
+      <c r="F360" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/account/page.md</v>
+      </c>
+    </row>
+    <row r="361" ht="40" customHeight="1">
+      <c r="A361" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B361" s="31" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C361" s="31" t="str">
+        <v>Langfuse execution</v>
+      </c>
+      <c r="D361" s="43" t="str">
+        <v>Open Langfuse execution</v>
+      </c>
+      <c r="E361" s="31" t="str">
+        <v>Observable execution; private deliberations not reproduced.</v>
+      </c>
+      <c r="F361" s="31" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/3c4b89a3e01af9b71a8756e0b20def38</v>
+      </c>
+    </row>
+    <row r="362" ht="54" customHeight="1">
+      <c r="A362" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B362" s="3" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C362" s="3" t="str">
+        <v>Claim JSON</v>
+      </c>
+      <c r="D362" s="23" t="str">
+        <v>Open Claim JSON</v>
+      </c>
+      <c r="E362" s="3" t="str"/>
+      <c r="F362" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/d9a7b71f-fa01-5b6b-8599-3119e6461527/dossier.json</v>
+      </c>
+    </row>
+    <row r="363" ht="54" customHeight="1">
+      <c r="A363" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B363" s="31" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C363" s="31" t="str">
+        <v>Readable dossier</v>
+      </c>
+      <c r="D363" s="43" t="str">
+        <v>Open Readable dossier</v>
+      </c>
+      <c r="E363" s="31" t="str"/>
+      <c r="F363" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/d9a7b71f-fa01-5b6b-8599-3119e6461527/dossier.md</v>
+      </c>
+    </row>
+    <row r="364" ht="54" customHeight="1">
+      <c r="A364" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B364" s="3" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C364" s="3" t="str">
+        <v>Imported claims</v>
+      </c>
+      <c r="D364" s="23" t="str">
+        <v>Open Imported claims</v>
+      </c>
+      <c r="E364" s="3" t="str"/>
+      <c r="F364" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/d9a7b71f-fa01-5b6b-8599-3119e6461527/imported-claims.json</v>
+      </c>
+    </row>
+    <row r="365" ht="54" customHeight="1">
+      <c r="A365" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B365" s="31" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C365" s="31" t="str">
+        <v>Saved narrative</v>
+      </c>
+      <c r="D365" s="43" t="str">
+        <v>Open Saved narrative</v>
+      </c>
+      <c r="E365" s="31" t="str">
+        <v>Researcher-authored contact page.</v>
+      </c>
+      <c r="F365" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/person-b0b87722-4292-444b-bfc5-4eaa371b7ca8/page.md</v>
+      </c>
+    </row>
+    <row r="366" ht="40" customHeight="1">
+      <c r="A366" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B366" s="3" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C366" s="3" t="str">
+        <v>Langfuse execution</v>
+      </c>
+      <c r="D366" s="23" t="str">
+        <v>Open Langfuse execution</v>
+      </c>
+      <c r="E366" s="3" t="str">
+        <v>Observable execution; private deliberations not reproduced.</v>
+      </c>
+      <c r="F366" s="3" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/64418da8b191c25e19e2cc56d074e444</v>
+      </c>
+    </row>
+    <row r="367" ht="54" customHeight="1">
+      <c r="A367" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B367" s="31" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C367" s="31" t="str">
+        <v>Claim JSON</v>
+      </c>
+      <c r="D367" s="43" t="str">
+        <v>Open Claim JSON</v>
+      </c>
+      <c r="E367" s="31" t="str"/>
+      <c r="F367" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/1a912ee3-806b-50ca-a0b5-d927cab2f677/dossier.json</v>
+      </c>
+    </row>
+    <row r="368" ht="54" customHeight="1">
+      <c r="A368" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B368" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C368" s="3" t="str">
+        <v>Readable dossier</v>
+      </c>
+      <c r="D368" s="23" t="str">
+        <v>Open Readable dossier</v>
+      </c>
+      <c r="E368" s="3" t="str"/>
+      <c r="F368" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/1a912ee3-806b-50ca-a0b5-d927cab2f677/dossier.md</v>
+      </c>
+    </row>
+    <row r="369" ht="54" customHeight="1">
+      <c r="A369" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B369" s="31" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C369" s="31" t="str">
+        <v>Imported claims</v>
+      </c>
+      <c r="D369" s="43" t="str">
+        <v>Open Imported claims</v>
+      </c>
+      <c r="E369" s="31" t="str"/>
+      <c r="F369" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/1a912ee3-806b-50ca-a0b5-d927cab2f677/imported-claims.json</v>
+      </c>
+    </row>
+    <row r="370" ht="54" customHeight="1">
+      <c r="A370" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B370" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C370" s="3" t="str">
+        <v>Saved narrative</v>
+      </c>
+      <c r="D370" s="23" t="str">
+        <v>Open Saved narrative</v>
+      </c>
+      <c r="E370" s="3" t="str">
+        <v>Researcher-authored contact page.</v>
+      </c>
+      <c r="F370" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/person-a503cf2b-0ce4-4867-8e80-d47764e89d01/page.md</v>
+      </c>
+    </row>
+    <row r="371" ht="40" customHeight="1">
+      <c r="A371" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B371" s="31" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C371" s="31" t="str">
+        <v>Langfuse execution</v>
+      </c>
+      <c r="D371" s="43" t="str">
+        <v>Open Langfuse execution</v>
+      </c>
+      <c r="E371" s="31" t="str">
+        <v>Observable execution; private deliberations not reproduced.</v>
+      </c>
+      <c r="F371" s="31" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/21aa93f9a4145e91b6b6e06adaa4554a</v>
+      </c>
+    </row>
+    <row r="372" ht="40" customHeight="1">
+      <c r="A372" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B372" s="3" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C372" s="3" t="str">
+        <v>Review report</v>
+      </c>
+      <c r="D372" s="23" t="str">
+        <v>Open Review report</v>
+      </c>
+      <c r="E372" s="3" t="str"/>
+      <c r="F372" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/research-model-evaluation-20260928/MUSE-XHIGH-QUALITY.md</v>
+      </c>
+    </row>
+    <row r="373" ht="40" customHeight="1">
+      <c r="A373" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B373" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C373" s="31" t="str">
+        <v>Source acquisition manifest</v>
+      </c>
+      <c r="D373" s="43" t="str">
+        <v>Open Source acquisition manifest</v>
+      </c>
+      <c r="E373" s="31" t="str"/>
+      <c r="F373" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/all-raw/manifest.json</v>
+      </c>
+    </row>
+    <row r="374" ht="40" customHeight="1">
+      <c r="A374" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B374" s="3" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C374" s="3" t="str">
+        <v>Action summary</v>
+      </c>
+      <c r="D374" s="23" t="str">
+        <v>Open Action summary</v>
+      </c>
+      <c r="E374" s="3" t="str"/>
+      <c r="F374" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/activity-latest.json</v>
+      </c>
+    </row>
+    <row r="375" ht="40" customHeight="1">
+      <c r="A375" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B375" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C375" s="31" t="str">
+        <v>Timing</v>
+      </c>
+      <c r="D375" s="43" t="str">
+        <v>Open Timing</v>
+      </c>
+      <c r="E375" s="31" t="str"/>
+      <c r="F375" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/timing.json</v>
+      </c>
+    </row>
+    <row r="376" ht="40" customHeight="1">
+      <c r="A376" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B376" s="3" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C376" s="3" t="str">
+        <v>Model call metadata</v>
+      </c>
+      <c r="D376" s="23" t="str">
+        <v>Open Model call metadata</v>
+      </c>
+      <c r="E376" s="3" t="str"/>
+      <c r="F376" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/agent_model_call.json</v>
+      </c>
+    </row>
+    <row r="377" ht="40" customHeight="1">
+      <c r="A377" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B377" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C377" s="31" t="str">
+        <v>Provider cost ledger</v>
+      </c>
+      <c r="D377" s="43" t="str">
+        <v>Open Provider cost ledger</v>
+      </c>
+      <c r="E377" s="31" t="str"/>
+      <c r="F377" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/review/provider_call_ledger.json</v>
+      </c>
+    </row>
+    <row r="378" ht="40" customHeight="1">
+      <c r="A378" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B378" s="3" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C378" s="3" t="str">
+        <v>Trace verification</v>
+      </c>
+      <c r="D378" s="23" t="str">
+        <v>Open Trace verification</v>
+      </c>
+      <c r="E378" s="3" t="str"/>
+      <c r="F378" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/trace-verification.json</v>
+      </c>
+    </row>
+    <row r="379" ht="40" customHeight="1">
+      <c r="A379" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B379" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C379" s="31" t="str">
+        <v>Initial account narrative</v>
+      </c>
+      <c r="D379" s="43" t="str">
+        <v>Open Initial account narrative</v>
+      </c>
+      <c r="E379" s="31" t="str"/>
+      <c r="F379" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/muse-xhigh/account-initial/page.md</v>
+      </c>
+    </row>
+    <row r="380" ht="40" customHeight="1">
+      <c r="A380" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B380" s="3" t="str">
+        <v>Common Muse reconciler</v>
+      </c>
+      <c r="C380" s="3" t="str">
+        <v>Langfuse reconciliation</v>
+      </c>
+      <c r="D380" s="23" t="str">
+        <v>Open Langfuse reconciliation</v>
+      </c>
+      <c r="E380" s="3" t="str"/>
+      <c r="F380" s="3" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/8821347724217b0a4a1a133916149b39</v>
+      </c>
+    </row>
+    <row r="381" ht="40" customHeight="1">
+      <c r="A381" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B381" s="31" t="str">
+        <v>Common Muse reconciler</v>
+      </c>
+      <c r="C381" s="31" t="str">
+        <v>Langfuse reconciliation</v>
+      </c>
+      <c r="D381" s="43" t="str">
+        <v>Open Langfuse reconciliation</v>
+      </c>
+      <c r="E381" s="31" t="str"/>
+      <c r="F381" s="31" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/bf446b64ca93d74f6a6af58bee2b13c8</v>
+      </c>
+    </row>
+    <row r="382" ht="54" customHeight="1">
+      <c r="A382" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B382" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C382" s="3" t="str">
+        <v>Claim JSON</v>
+      </c>
+      <c r="D382" s="23" t="str">
+        <v>Open Claim JSON</v>
+      </c>
+      <c r="E382" s="3" t="str"/>
+      <c r="F382" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/59d4870e-2207-56ca-a50b-e76ab86f6a53/dossier.json</v>
+      </c>
+    </row>
+    <row r="383" ht="54" customHeight="1">
+      <c r="A383" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B383" s="31" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C383" s="31" t="str">
+        <v>Readable dossier</v>
+      </c>
+      <c r="D383" s="43" t="str">
+        <v>Open Readable dossier</v>
+      </c>
+      <c r="E383" s="31" t="str"/>
+      <c r="F383" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/59d4870e-2207-56ca-a50b-e76ab86f6a53/dossier.md</v>
+      </c>
+    </row>
+    <row r="384" ht="54" customHeight="1">
+      <c r="A384" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B384" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C384" s="3" t="str">
+        <v>Imported claims</v>
+      </c>
+      <c r="D384" s="23" t="str">
+        <v>Open Imported claims</v>
+      </c>
+      <c r="E384" s="3" t="str"/>
+      <c r="F384" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/59d4870e-2207-56ca-a50b-e76ab86f6a53/imported-claims.json</v>
+      </c>
+    </row>
+    <row r="385" ht="40" customHeight="1">
+      <c r="A385" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B385" s="31" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C385" s="31" t="str">
+        <v>Saved narrative</v>
+      </c>
+      <c r="D385" s="43" t="str">
+        <v>Open Saved narrative</v>
+      </c>
+      <c r="E385" s="31" t="str">
+        <v>Account may include common reconciliation; see initial version separately.</v>
+      </c>
+      <c r="F385" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/account/page.md</v>
+      </c>
+    </row>
+    <row r="386" ht="40" customHeight="1">
+      <c r="A386" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B386" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C386" s="3" t="str">
+        <v>Langfuse execution</v>
+      </c>
+      <c r="D386" s="23" t="str">
+        <v>Open Langfuse execution</v>
+      </c>
+      <c r="E386" s="3" t="str">
+        <v>Observable execution; private deliberations not reproduced.</v>
+      </c>
+      <c r="F386" s="3" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/8478a8cd513437570318159ecfedecee</v>
+      </c>
+    </row>
+    <row r="387" ht="54" customHeight="1">
+      <c r="A387" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B387" s="31" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C387" s="31" t="str">
+        <v>Claim JSON</v>
+      </c>
+      <c r="D387" s="43" t="str">
+        <v>Open Claim JSON</v>
+      </c>
+      <c r="E387" s="31" t="str"/>
+      <c r="F387" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/23a89a4c-2a62-5501-9c22-24797bd232d0/dossier.json</v>
+      </c>
+    </row>
+    <row r="388" ht="54" customHeight="1">
+      <c r="A388" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B388" s="3" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C388" s="3" t="str">
+        <v>Readable dossier</v>
+      </c>
+      <c r="D388" s="23" t="str">
+        <v>Open Readable dossier</v>
+      </c>
+      <c r="E388" s="3" t="str"/>
+      <c r="F388" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/23a89a4c-2a62-5501-9c22-24797bd232d0/dossier.md</v>
+      </c>
+    </row>
+    <row r="389" ht="54" customHeight="1">
+      <c r="A389" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B389" s="31" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C389" s="31" t="str">
+        <v>Imported claims</v>
+      </c>
+      <c r="D389" s="43" t="str">
+        <v>Open Imported claims</v>
+      </c>
+      <c r="E389" s="31" t="str"/>
+      <c r="F389" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/23a89a4c-2a62-5501-9c22-24797bd232d0/imported-claims.json</v>
+      </c>
+    </row>
+    <row r="390" ht="54" customHeight="1">
+      <c r="A390" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B390" s="3" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C390" s="3" t="str">
+        <v>Saved narrative</v>
+      </c>
+      <c r="D390" s="23" t="str">
+        <v>Open Saved narrative</v>
+      </c>
+      <c r="E390" s="3" t="str">
+        <v>Researcher-authored contact page.</v>
+      </c>
+      <c r="F390" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/person-62653922-ea6f-43ec-8a7d-0cfe8b5fd8d5/page.md</v>
+      </c>
+    </row>
+    <row r="391" ht="40" customHeight="1">
+      <c r="A391" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B391" s="31" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C391" s="31" t="str">
+        <v>Langfuse execution</v>
+      </c>
+      <c r="D391" s="43" t="str">
+        <v>Open Langfuse execution</v>
+      </c>
+      <c r="E391" s="31" t="str">
+        <v>Observable execution; private deliberations not reproduced.</v>
+      </c>
+      <c r="F391" s="31" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/cb063dcc8b1bc8b30905c09ba7d1dc46</v>
+      </c>
+    </row>
+    <row r="392" ht="54" customHeight="1">
+      <c r="A392" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B392" s="3" t="str">
+        <v>Sanaz Yashar</v>
+      </c>
+      <c r="C392" s="3" t="str">
+        <v>Claim JSON</v>
+      </c>
+      <c r="D392" s="23" t="str">
+        <v>Open Claim JSON</v>
+      </c>
+      <c r="E392" s="3" t="str"/>
+      <c r="F392" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/2242afe2-3187-5d99-94aa-2cdced22669d/dossier.json</v>
+      </c>
+    </row>
+    <row r="393" ht="54" customHeight="1">
+      <c r="A393" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B393" s="31" t="str">
+        <v>Sanaz Yashar</v>
+      </c>
+      <c r="C393" s="31" t="str">
+        <v>Readable dossier</v>
+      </c>
+      <c r="D393" s="43" t="str">
+        <v>Open Readable dossier</v>
+      </c>
+      <c r="E393" s="31" t="str"/>
+      <c r="F393" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/2242afe2-3187-5d99-94aa-2cdced22669d/dossier.md</v>
+      </c>
+    </row>
+    <row r="394" ht="54" customHeight="1">
+      <c r="A394" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B394" s="3" t="str">
+        <v>Sanaz Yashar</v>
+      </c>
+      <c r="C394" s="3" t="str">
+        <v>Imported claims</v>
+      </c>
+      <c r="D394" s="23" t="str">
+        <v>Open Imported claims</v>
+      </c>
+      <c r="E394" s="3" t="str"/>
+      <c r="F394" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/2242afe2-3187-5d99-94aa-2cdced22669d/imported-claims.json</v>
+      </c>
+    </row>
+    <row r="395" ht="54" customHeight="1">
+      <c r="A395" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B395" s="31" t="str">
+        <v>Sanaz Yashar</v>
+      </c>
+      <c r="C395" s="31" t="str">
+        <v>Saved narrative</v>
+      </c>
+      <c r="D395" s="43" t="str">
+        <v>Open Saved narrative</v>
+      </c>
+      <c r="E395" s="31" t="str">
+        <v>Researcher-authored contact page.</v>
+      </c>
+      <c r="F395" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/person-913a23df-a0a3-4f67-9fc0-b62d3b611077/page.md</v>
+      </c>
+    </row>
+    <row r="396" ht="40" customHeight="1">
+      <c r="A396" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B396" s="3" t="str">
+        <v>Sanaz Yashar</v>
+      </c>
+      <c r="C396" s="3" t="str">
+        <v>Langfuse execution</v>
+      </c>
+      <c r="D396" s="23" t="str">
+        <v>Open Langfuse execution</v>
+      </c>
+      <c r="E396" s="3" t="str">
+        <v>Observable execution; private deliberations not reproduced.</v>
+      </c>
+      <c r="F396" s="3" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/0061b14dad5cbbcd9166a8cc3c4e20ad</v>
+      </c>
+    </row>
+    <row r="397" ht="40" customHeight="1">
+      <c r="A397" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B397" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C397" s="31" t="str">
+        <v>Review report</v>
+      </c>
+      <c r="D397" s="43" t="str">
+        <v>Open Review report</v>
+      </c>
+      <c r="E397" s="31" t="str"/>
+      <c r="F397" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/FINAL-STATUS.md</v>
+      </c>
+    </row>
+    <row r="398" ht="40" customHeight="1">
+      <c r="A398" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B398" s="3" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C398" s="3" t="str">
+        <v>Source acquisition manifest</v>
+      </c>
+      <c r="D398" s="23" t="str">
+        <v>Open Source acquisition manifest</v>
+      </c>
+      <c r="E398" s="3" t="str"/>
+      <c r="F398" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/all-raw/manifest.json</v>
+      </c>
+    </row>
+    <row r="399" ht="40" customHeight="1">
+      <c r="A399" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B399" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C399" s="31" t="str">
+        <v>Action summary</v>
+      </c>
+      <c r="D399" s="43" t="str">
+        <v>Open Action summary</v>
+      </c>
+      <c r="E399" s="31" t="str"/>
+      <c r="F399" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/activity-latest.json</v>
+      </c>
+    </row>
+    <row r="400" ht="40" customHeight="1">
+      <c r="A400" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B400" s="3" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C400" s="3" t="str">
+        <v>Timing</v>
+      </c>
+      <c r="D400" s="23" t="str">
+        <v>Open Timing</v>
+      </c>
+      <c r="E400" s="3" t="str"/>
+      <c r="F400" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/timing.json</v>
+      </c>
+    </row>
+    <row r="401" ht="40" customHeight="1">
+      <c r="A401" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B401" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C401" s="31" t="str">
+        <v>Model call metadata</v>
+      </c>
+      <c r="D401" s="43" t="str">
+        <v>Open Model call metadata</v>
+      </c>
+      <c r="E401" s="31" t="str"/>
+      <c r="F401" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/agent_model_call.json</v>
+      </c>
+    </row>
+    <row r="402" ht="40" customHeight="1">
+      <c r="A402" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B402" s="3" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C402" s="3" t="str">
+        <v>Provider cost ledger</v>
+      </c>
+      <c r="D402" s="23" t="str">
+        <v>Open Provider cost ledger</v>
+      </c>
+      <c r="E402" s="3" t="str"/>
+      <c r="F402" s="3" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/review/provider_call_ledger.json</v>
+      </c>
+    </row>
+    <row r="403" ht="40" customHeight="1">
+      <c r="A403" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B403" s="31" t="str">
+        <v>Run</v>
+      </c>
+      <c r="C403" s="31" t="str">
+        <v>Trace verification</v>
+      </c>
+      <c r="D403" s="43" t="str">
+        <v>Open Trace verification</v>
+      </c>
+      <c r="E403" s="31" t="str"/>
+      <c r="F403" s="31" t="str">
+        <v>/Users/aryankeshri/conductor/workspaces/research-and-data/jerusalem-v1/.artifacts/zafran-muse-xhigh-glm-retry-20260928/glm53-medium/trace-verification.json</v>
+      </c>
+    </row>
+    <row r="404" ht="40" customHeight="1">
+      <c r="A404" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B404" s="3" t="str">
+        <v>Common Muse reconciler</v>
+      </c>
+      <c r="C404" s="3" t="str">
+        <v>Langfuse reconciliation</v>
+      </c>
+      <c r="D404" s="23" t="str">
+        <v>Open Langfuse reconciliation</v>
+      </c>
+      <c r="E404" s="3" t="str"/>
+      <c r="F404" s="3" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/38a4925c1acc5930af3bfb1ef3bdfce3</v>
+      </c>
+    </row>
+    <row r="405" ht="40" customHeight="1">
+      <c r="A405" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B405" s="31" t="str">
+        <v>Common Muse reconciler</v>
+      </c>
+      <c r="C405" s="31" t="str">
+        <v>Langfuse reconciliation</v>
+      </c>
+      <c r="D405" s="43" t="str">
+        <v>Open Langfuse reconciliation</v>
+      </c>
+      <c r="E405" s="31" t="str"/>
+      <c r="F405" s="31" t="str">
+        <v>https://us.cloud.langfuse.com/project/cmu2j8vra0137ad0clp5vylx2/traces/57a55c51c8095929225144a1f26cff95</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="NativeLink1"/>
-    <hyperlink ref="D7" r:id="NativeLink2"/>
-    <hyperlink ref="D8" r:id="NativeLink3"/>
-    <hyperlink ref="D9" r:id="NativeLink4"/>
-    <hyperlink ref="D10" r:id="NativeLink5"/>
-    <hyperlink ref="D12" r:id="NativeLink6"/>
-    <hyperlink ref="D13" r:id="NativeLink7"/>
-    <hyperlink ref="D14" r:id="NativeLink8"/>
-    <hyperlink ref="D15" r:id="NativeLink9"/>
-    <hyperlink ref="D16" r:id="NativeLink10"/>
-    <hyperlink ref="D17" r:id="NativeLink11"/>
-    <hyperlink ref="D18" r:id="NativeLink12"/>
-    <hyperlink ref="D20" r:id="NativeLink13"/>
-    <hyperlink ref="D21" r:id="NativeLink14"/>
-    <hyperlink ref="D22" r:id="NativeLink15"/>
-    <hyperlink ref="D23" r:id="NativeLink16"/>
-    <hyperlink ref="D24" r:id="NativeLink17"/>
-    <hyperlink ref="D25" r:id="NativeLink18"/>
-    <hyperlink ref="D26" r:id="NativeLink19"/>
-    <hyperlink ref="D27" r:id="NativeLink20"/>
-    <hyperlink ref="D28" r:id="NativeLink21"/>
-    <hyperlink ref="D29" r:id="NativeLink22"/>
-    <hyperlink ref="D30" r:id="NativeLink23"/>
-    <hyperlink ref="D31" r:id="NativeLink24"/>
-    <hyperlink ref="D32" r:id="NativeLink25"/>
-    <hyperlink ref="D33" r:id="NativeLink26"/>
-    <hyperlink ref="D34" r:id="NativeLink27"/>
-    <hyperlink ref="D36" r:id="NativeLink28"/>
-    <hyperlink ref="D37" r:id="NativeLink29"/>
-    <hyperlink ref="D44" r:id="NativeLink30"/>
-    <hyperlink ref="D45" r:id="NativeLink31"/>
-    <hyperlink ref="D46" r:id="NativeLink32"/>
-    <hyperlink ref="D47" r:id="NativeLink33"/>
-    <hyperlink ref="D48" r:id="NativeLink34"/>
-    <hyperlink ref="D49" r:id="NativeLink35"/>
-    <hyperlink ref="D50" r:id="NativeLink36"/>
-    <hyperlink ref="D51" r:id="NativeLink37"/>
-    <hyperlink ref="D52" r:id="NativeLink38"/>
-    <hyperlink ref="D53" r:id="NativeLink39"/>
-    <hyperlink ref="D54" r:id="NativeLink40"/>
-    <hyperlink ref="D55" r:id="NativeLink41"/>
-    <hyperlink ref="D57" r:id="NativeLink42"/>
-    <hyperlink ref="D58" r:id="NativeLink43"/>
-    <hyperlink ref="D59" r:id="NativeLink44"/>
-    <hyperlink ref="D60" r:id="NativeLink45"/>
-    <hyperlink ref="D61" r:id="NativeLink46"/>
-    <hyperlink ref="D64" r:id="NativeLink47"/>
-    <hyperlink ref="D65" r:id="NativeLink48"/>
-    <hyperlink ref="D66" r:id="NativeLink49"/>
-    <hyperlink ref="D67" r:id="NativeLink50"/>
-    <hyperlink ref="D68" r:id="NativeLink51"/>
-    <hyperlink ref="D69" r:id="NativeLink52"/>
-    <hyperlink ref="D70" r:id="NativeLink53"/>
-    <hyperlink ref="D71" r:id="NativeLink54"/>
-    <hyperlink ref="D72" r:id="NativeLink55"/>
-    <hyperlink ref="D73" r:id="NativeLink56"/>
-    <hyperlink ref="D74" r:id="NativeLink57"/>
-    <hyperlink ref="D75" r:id="NativeLink58"/>
-    <hyperlink ref="D76" r:id="NativeLink59"/>
-    <hyperlink ref="D77" r:id="NativeLink60"/>
-    <hyperlink ref="D78" r:id="NativeLink61"/>
-    <hyperlink ref="D79" r:id="NativeLink62"/>
-    <hyperlink ref="D80" r:id="NativeLink63"/>
-    <hyperlink ref="D82" r:id="NativeLink64"/>
-    <hyperlink ref="D84" r:id="NativeLink65"/>
-    <hyperlink ref="D85" r:id="NativeLink66"/>
-    <hyperlink ref="D86" r:id="NativeLink67"/>
-    <hyperlink ref="D87" r:id="NativeLink68"/>
-    <hyperlink ref="D88" r:id="NativeLink69"/>
-    <hyperlink ref="D89" r:id="NativeLink70"/>
-    <hyperlink ref="D90" r:id="NativeLink71"/>
-    <hyperlink ref="D92" r:id="NativeLink72"/>
-    <hyperlink ref="D93" r:id="NativeLink73"/>
-    <hyperlink ref="D94" r:id="NativeLink74"/>
-    <hyperlink ref="D95" r:id="NativeLink75"/>
-    <hyperlink ref="D96" r:id="NativeLink76"/>
-    <hyperlink ref="D97" r:id="NativeLink77"/>
-    <hyperlink ref="D98" r:id="NativeLink78"/>
-    <hyperlink ref="D99" r:id="NativeLink79"/>
-    <hyperlink ref="D100" r:id="NativeLink80"/>
-    <hyperlink ref="D101" r:id="NativeLink81"/>
-    <hyperlink ref="D102" r:id="NativeLink82"/>
-    <hyperlink ref="D103" r:id="NativeLink83"/>
-    <hyperlink ref="D104" r:id="NativeLink84"/>
-    <hyperlink ref="D105" r:id="NativeLink85"/>
-    <hyperlink ref="D106" r:id="NativeLink86"/>
-    <hyperlink ref="D107" r:id="NativeLink87"/>
-    <hyperlink ref="D108" r:id="NativeLink88"/>
-    <hyperlink ref="D109" r:id="NativeLink89"/>
-    <hyperlink ref="D111" r:id="NativeLink90"/>
-    <hyperlink ref="D112" r:id="NativeLink91"/>
-    <hyperlink ref="D119" r:id="NativeLink92"/>
-    <hyperlink ref="D120" r:id="NativeLink93"/>
-    <hyperlink ref="D121" r:id="NativeLink94"/>
-    <hyperlink ref="D122" r:id="NativeLink95"/>
-    <hyperlink ref="D123" r:id="NativeLink96"/>
-    <hyperlink ref="D124" r:id="NativeLink97"/>
-    <hyperlink ref="D125" r:id="NativeLink98"/>
-    <hyperlink ref="D126" r:id="NativeLink99"/>
-    <hyperlink ref="D127" r:id="NativeLink100"/>
-    <hyperlink ref="D128" r:id="NativeLink101"/>
-    <hyperlink ref="D129" r:id="NativeLink102"/>
-    <hyperlink ref="D130" r:id="NativeLink103"/>
-    <hyperlink ref="D131" r:id="NativeLink104"/>
-    <hyperlink ref="D132" r:id="NativeLink105"/>
-    <hyperlink ref="D133" r:id="NativeLink106"/>
-    <hyperlink ref="D135" r:id="NativeLink107"/>
-    <hyperlink ref="D137" r:id="NativeLink108"/>
-    <hyperlink ref="D138" r:id="NativeLink109"/>
-    <hyperlink ref="D139" r:id="NativeLink110"/>
-    <hyperlink ref="D140" r:id="NativeLink111"/>
-    <hyperlink ref="D142" r:id="NativeLink112"/>
-    <hyperlink ref="D144" r:id="NativeLink113"/>
-    <hyperlink ref="D145" r:id="NativeLink114"/>
-    <hyperlink ref="D146" r:id="NativeLink115"/>
-    <hyperlink ref="D147" r:id="NativeLink116"/>
-    <hyperlink ref="D149" r:id="NativeLink117"/>
-    <hyperlink ref="D151" r:id="NativeLink118"/>
-    <hyperlink ref="D152" r:id="NativeLink119"/>
-    <hyperlink ref="D153" r:id="NativeLink120"/>
-    <hyperlink ref="D154" r:id="NativeLink121"/>
-    <hyperlink ref="D155" r:id="NativeLink122"/>
-    <hyperlink ref="D156" r:id="NativeLink123"/>
-    <hyperlink ref="D158" r:id="NativeLink124"/>
-    <hyperlink ref="D159" r:id="NativeLink125"/>
-    <hyperlink ref="D160" r:id="NativeLink126"/>
-    <hyperlink ref="D161" r:id="NativeLink127"/>
-    <hyperlink ref="D162" r:id="NativeLink128"/>
-    <hyperlink ref="D163" r:id="NativeLink129"/>
-    <hyperlink ref="D164" r:id="NativeLink130"/>
-    <hyperlink ref="D165" r:id="NativeLink131"/>
-    <hyperlink ref="D166" r:id="NativeLink132"/>
-    <hyperlink ref="D167" r:id="NativeLink133"/>
-    <hyperlink ref="D168" r:id="NativeLink134"/>
-    <hyperlink ref="D169" r:id="NativeLink135"/>
-    <hyperlink ref="D170" r:id="NativeLink136"/>
-    <hyperlink ref="D171" r:id="NativeLink137"/>
-    <hyperlink ref="D172" r:id="NativeLink138"/>
-    <hyperlink ref="D185" r:id="NativeLink139"/>
-    <hyperlink ref="D186" r:id="NativeLink140"/>
-    <hyperlink ref="D191" r:id="NativeLink141"/>
-    <hyperlink ref="D192" r:id="NativeLink142"/>
-    <hyperlink ref="D198" r:id="NativeLink143"/>
-    <hyperlink ref="D199" r:id="NativeLink144"/>
-    <hyperlink ref="D200" r:id="NativeLink145"/>
-    <hyperlink ref="D201" r:id="NativeLink146"/>
-    <hyperlink ref="D202" r:id="NativeLink147"/>
-    <hyperlink ref="D203" r:id="NativeLink148"/>
-    <hyperlink ref="D204" r:id="NativeLink149"/>
-    <hyperlink ref="D205" r:id="NativeLink150"/>
-    <hyperlink ref="D206" r:id="NativeLink151"/>
-    <hyperlink ref="D207" r:id="NativeLink152"/>
-    <hyperlink ref="D208" r:id="NativeLink153"/>
-    <hyperlink ref="D209" r:id="NativeLink154"/>
-    <hyperlink ref="D228" r:id="NativeLink155"/>
-    <hyperlink ref="D229" r:id="NativeLink156"/>
-    <hyperlink ref="D234" r:id="NativeLink157"/>
-    <hyperlink ref="D235" r:id="NativeLink158"/>
-    <hyperlink ref="D236" r:id="NativeLink159"/>
-    <hyperlink ref="D237" r:id="NativeLink160"/>
-    <hyperlink ref="D238" r:id="NativeLink161"/>
-    <hyperlink ref="D239" r:id="NativeLink162"/>
-    <hyperlink ref="D240" r:id="NativeLink163"/>
-    <hyperlink ref="D241" r:id="NativeLink164"/>
-    <hyperlink ref="D242" r:id="NativeLink165"/>
-    <hyperlink ref="D243" r:id="NativeLink166"/>
-    <hyperlink ref="D244" r:id="NativeLink167"/>
-    <hyperlink ref="D245" r:id="NativeLink168"/>
-    <hyperlink ref="D246" r:id="NativeLink169"/>
-    <hyperlink ref="D253" r:id="NativeLink170"/>
-    <hyperlink ref="D254" r:id="NativeLink171"/>
-    <hyperlink ref="D259" r:id="NativeLink172"/>
-    <hyperlink ref="D260" r:id="NativeLink173"/>
-    <hyperlink ref="D261" r:id="NativeLink174"/>
-    <hyperlink ref="D262" r:id="NativeLink175"/>
-    <hyperlink ref="D263" r:id="NativeLink176"/>
-    <hyperlink ref="D264" r:id="NativeLink177"/>
-    <hyperlink ref="D265" r:id="NativeLink178"/>
-    <hyperlink ref="D266" r:id="NativeLink179"/>
-    <hyperlink ref="D267" r:id="NativeLink180"/>
-    <hyperlink ref="D268" r:id="NativeLink181"/>
-    <hyperlink ref="D269" r:id="NativeLink182"/>
-    <hyperlink ref="D270" r:id="NativeLink183"/>
-    <hyperlink ref="D271" r:id="NativeLink184"/>
-    <hyperlink ref="D278" r:id="NativeLink185"/>
-    <hyperlink ref="D279" r:id="NativeLink186"/>
-    <hyperlink ref="D280" r:id="NativeLink187"/>
-    <hyperlink ref="D285" r:id="NativeLink188"/>
-    <hyperlink ref="D286" r:id="NativeLink189"/>
-    <hyperlink ref="D287" r:id="NativeLink190"/>
-    <hyperlink ref="D292" r:id="NativeLink191"/>
-    <hyperlink ref="D293" r:id="NativeLink192"/>
-    <hyperlink ref="D294" r:id="NativeLink193"/>
-    <hyperlink ref="D295" r:id="NativeLink194"/>
-    <hyperlink ref="D299" r:id="NativeLink195"/>
-    <hyperlink ref="D300" r:id="NativeLink196"/>
-    <hyperlink ref="D301" r:id="NativeLink197"/>
-    <hyperlink ref="D302" r:id="NativeLink198"/>
-    <hyperlink ref="D303" r:id="NativeLink199"/>
-    <hyperlink ref="D304" r:id="NativeLink200"/>
-    <hyperlink ref="D305" r:id="NativeLink201"/>
-    <hyperlink ref="D306" r:id="NativeLink202"/>
-    <hyperlink ref="D307" r:id="NativeLink203"/>
-    <hyperlink ref="D308" r:id="NativeLink204"/>
-    <hyperlink ref="D309" r:id="NativeLink205"/>
-    <hyperlink ref="D310" r:id="NativeLink206"/>
-    <hyperlink ref="D311" r:id="NativeLink207"/>
-    <hyperlink ref="D312" r:id="NativeLink208"/>
-    <hyperlink ref="D313" r:id="NativeLink209"/>
-    <hyperlink ref="D314" r:id="NativeLink210"/>
-    <hyperlink ref="D315" r:id="NativeLink211"/>
-    <hyperlink ref="D317" r:id="NativeLink212"/>
-    <hyperlink ref="D319" r:id="NativeLink213"/>
-    <hyperlink ref="D320" r:id="NativeLink214"/>
-    <hyperlink ref="D321" r:id="NativeLink215"/>
-    <hyperlink ref="D326" r:id="NativeLink216"/>
-    <hyperlink ref="D327" r:id="NativeLink217"/>
-    <hyperlink ref="D328" r:id="NativeLink218"/>
-    <hyperlink ref="D332" r:id="NativeLink219"/>
-    <hyperlink ref="D333" r:id="NativeLink220"/>
-    <hyperlink ref="D334" r:id="NativeLink221"/>
-    <hyperlink ref="D335" r:id="NativeLink222"/>
-    <hyperlink ref="D336" r:id="NativeLink223"/>
-    <hyperlink ref="D337" r:id="NativeLink224"/>
-    <hyperlink ref="D338" r:id="NativeLink225"/>
-    <hyperlink ref="D340" r:id="NativeLink226"/>
-    <hyperlink ref="D341" r:id="NativeLink227"/>
-    <hyperlink ref="D342" r:id="NativeLink228"/>
-    <hyperlink ref="D343" r:id="NativeLink229"/>
-    <hyperlink ref="D344" r:id="NativeLink230"/>
-    <hyperlink ref="D345" r:id="NativeLink231"/>
-    <hyperlink ref="D346" r:id="NativeLink232"/>
-    <hyperlink ref="D347" r:id="NativeLink233"/>
-    <hyperlink ref="D348" r:id="NativeLink234"/>
-    <hyperlink ref="D349" r:id="NativeLink235"/>
-    <hyperlink ref="D350" r:id="NativeLink236"/>
-    <hyperlink ref="D351" r:id="NativeLink237"/>
-    <hyperlink ref="D352" r:id="NativeLink238"/>
-    <hyperlink ref="D353" r:id="NativeLink239"/>
-    <hyperlink ref="D354" r:id="NativeLink240"/>
-    <hyperlink ref="D355" r:id="NativeLink241"/>
-    <hyperlink ref="D356" r:id="NativeLink242"/>
+    <hyperlink ref="D6" r:id="VerifiedLink119"/>
+    <hyperlink ref="D7" r:id="VerifiedLink120"/>
+    <hyperlink ref="D8" r:id="VerifiedLink121"/>
+    <hyperlink ref="D9" r:id="VerifiedLink122"/>
+    <hyperlink ref="D10" r:id="VerifiedLink123"/>
+    <hyperlink ref="D12" r:id="VerifiedLink124"/>
+    <hyperlink ref="D13" r:id="VerifiedLink125"/>
+    <hyperlink ref="D14" r:id="VerifiedLink126"/>
+    <hyperlink ref="D15" r:id="VerifiedLink127"/>
+    <hyperlink ref="D16" r:id="VerifiedLink128"/>
+    <hyperlink ref="D17" r:id="VerifiedLink129"/>
+    <hyperlink ref="D18" r:id="VerifiedLink130"/>
+    <hyperlink ref="D20" r:id="VerifiedLink131"/>
+    <hyperlink ref="D21" r:id="VerifiedLink132"/>
+    <hyperlink ref="D22" r:id="VerifiedLink133"/>
+    <hyperlink ref="D23" r:id="VerifiedLink134"/>
+    <hyperlink ref="D24" r:id="VerifiedLink135"/>
+    <hyperlink ref="D25" r:id="VerifiedLink136"/>
+    <hyperlink ref="D26" r:id="VerifiedLink137"/>
+    <hyperlink ref="D27" r:id="VerifiedLink138"/>
+    <hyperlink ref="D28" r:id="VerifiedLink139"/>
+    <hyperlink ref="D29" r:id="VerifiedLink140"/>
+    <hyperlink ref="D30" r:id="VerifiedLink141"/>
+    <hyperlink ref="D31" r:id="VerifiedLink142"/>
+    <hyperlink ref="D32" r:id="VerifiedLink143"/>
+    <hyperlink ref="D33" r:id="VerifiedLink144"/>
+    <hyperlink ref="D34" r:id="VerifiedLink145"/>
+    <hyperlink ref="D36" r:id="VerifiedLink146"/>
+    <hyperlink ref="D37" r:id="VerifiedLink147"/>
+    <hyperlink ref="D44" r:id="VerifiedLink148"/>
+    <hyperlink ref="D45" r:id="VerifiedLink149"/>
+    <hyperlink ref="D46" r:id="VerifiedLink150"/>
+    <hyperlink ref="D47" r:id="VerifiedLink151"/>
+    <hyperlink ref="D48" r:id="VerifiedLink152"/>
+    <hyperlink ref="D49" r:id="VerifiedLink153"/>
+    <hyperlink ref="D50" r:id="VerifiedLink154"/>
+    <hyperlink ref="D51" r:id="VerifiedLink155"/>
+    <hyperlink ref="D52" r:id="VerifiedLink156"/>
+    <hyperlink ref="D53" r:id="VerifiedLink157"/>
+    <hyperlink ref="D54" r:id="VerifiedLink158"/>
+    <hyperlink ref="D55" r:id="VerifiedLink159"/>
+    <hyperlink ref="D57" r:id="VerifiedLink160"/>
+    <hyperlink ref="D58" r:id="VerifiedLink161"/>
+    <hyperlink ref="D59" r:id="VerifiedLink162"/>
+    <hyperlink ref="D60" r:id="VerifiedLink163"/>
+    <hyperlink ref="D61" r:id="VerifiedLink164"/>
+    <hyperlink ref="D64" r:id="VerifiedLink165"/>
+    <hyperlink ref="D65" r:id="VerifiedLink166"/>
+    <hyperlink ref="D66" r:id="VerifiedLink167"/>
+    <hyperlink ref="D67" r:id="VerifiedLink168"/>
+    <hyperlink ref="D68" r:id="VerifiedLink169"/>
+    <hyperlink ref="D69" r:id="VerifiedLink170"/>
+    <hyperlink ref="D70" r:id="VerifiedLink171"/>
+    <hyperlink ref="D71" r:id="VerifiedLink172"/>
+    <hyperlink ref="D72" r:id="VerifiedLink173"/>
+    <hyperlink ref="D73" r:id="VerifiedLink174"/>
+    <hyperlink ref="D74" r:id="VerifiedLink175"/>
+    <hyperlink ref="D75" r:id="VerifiedLink176"/>
+    <hyperlink ref="D76" r:id="VerifiedLink177"/>
+    <hyperlink ref="D77" r:id="VerifiedLink178"/>
+    <hyperlink ref="D78" r:id="VerifiedLink179"/>
+    <hyperlink ref="D79" r:id="VerifiedLink180"/>
+    <hyperlink ref="D80" r:id="VerifiedLink181"/>
+    <hyperlink ref="D82" r:id="VerifiedLink182"/>
+    <hyperlink ref="D84" r:id="VerifiedLink183"/>
+    <hyperlink ref="D85" r:id="VerifiedLink184"/>
+    <hyperlink ref="D86" r:id="VerifiedLink185"/>
+    <hyperlink ref="D87" r:id="VerifiedLink186"/>
+    <hyperlink ref="D88" r:id="VerifiedLink187"/>
+    <hyperlink ref="D89" r:id="VerifiedLink188"/>
+    <hyperlink ref="D90" r:id="VerifiedLink189"/>
+    <hyperlink ref="D92" r:id="VerifiedLink190"/>
+    <hyperlink ref="D93" r:id="VerifiedLink191"/>
+    <hyperlink ref="D94" r:id="VerifiedLink192"/>
+    <hyperlink ref="D95" r:id="VerifiedLink193"/>
+    <hyperlink ref="D96" r:id="VerifiedLink194"/>
+    <hyperlink ref="D97" r:id="VerifiedLink195"/>
+    <hyperlink ref="D98" r:id="VerifiedLink196"/>
+    <hyperlink ref="D99" r:id="VerifiedLink197"/>
+    <hyperlink ref="D100" r:id="VerifiedLink198"/>
+    <hyperlink ref="D101" r:id="VerifiedLink199"/>
+    <hyperlink ref="D102" r:id="VerifiedLink200"/>
+    <hyperlink ref="D103" r:id="VerifiedLink201"/>
+    <hyperlink ref="D104" r:id="VerifiedLink202"/>
+    <hyperlink ref="D105" r:id="VerifiedLink203"/>
+    <hyperlink ref="D106" r:id="VerifiedLink204"/>
+    <hyperlink ref="D107" r:id="VerifiedLink205"/>
+    <hyperlink ref="D108" r:id="VerifiedLink206"/>
+    <hyperlink ref="D109" r:id="VerifiedLink207"/>
+    <hyperlink ref="D111" r:id="VerifiedLink208"/>
+    <hyperlink ref="D112" r:id="VerifiedLink209"/>
+    <hyperlink ref="D119" r:id="VerifiedLink210"/>
+    <hyperlink ref="D120" r:id="VerifiedLink211"/>
+    <hyperlink ref="D121" r:id="VerifiedLink212"/>
+    <hyperlink ref="D122" r:id="VerifiedLink213"/>
+    <hyperlink ref="D123" r:id="VerifiedLink214"/>
+    <hyperlink ref="D124" r:id="VerifiedLink215"/>
+    <hyperlink ref="D125" r:id="VerifiedLink216"/>
+    <hyperlink ref="D126" r:id="VerifiedLink217"/>
+    <hyperlink ref="D127" r:id="VerifiedLink218"/>
+    <hyperlink ref="D128" r:id="VerifiedLink219"/>
+    <hyperlink ref="D129" r:id="VerifiedLink220"/>
+    <hyperlink ref="D130" r:id="VerifiedLink221"/>
+    <hyperlink ref="D131" r:id="VerifiedLink222"/>
+    <hyperlink ref="D132" r:id="VerifiedLink223"/>
+    <hyperlink ref="D133" r:id="VerifiedLink224"/>
+    <hyperlink ref="D135" r:id="VerifiedLink225"/>
+    <hyperlink ref="D137" r:id="VerifiedLink226"/>
+    <hyperlink ref="D138" r:id="VerifiedLink227"/>
+    <hyperlink ref="D139" r:id="VerifiedLink228"/>
+    <hyperlink ref="D140" r:id="VerifiedLink229"/>
+    <hyperlink ref="D142" r:id="VerifiedLink230"/>
+    <hyperlink ref="D144" r:id="VerifiedLink231"/>
+    <hyperlink ref="D145" r:id="VerifiedLink232"/>
+    <hyperlink ref="D146" r:id="VerifiedLink233"/>
+    <hyperlink ref="D147" r:id="VerifiedLink234"/>
+    <hyperlink ref="D149" r:id="VerifiedLink235"/>
+    <hyperlink ref="D151" r:id="VerifiedLink236"/>
+    <hyperlink ref="D152" r:id="VerifiedLink237"/>
+    <hyperlink ref="D153" r:id="VerifiedLink238"/>
+    <hyperlink ref="D154" r:id="VerifiedLink239"/>
+    <hyperlink ref="D155" r:id="VerifiedLink240"/>
+    <hyperlink ref="D156" r:id="VerifiedLink241"/>
+    <hyperlink ref="D158" r:id="VerifiedLink242"/>
+    <hyperlink ref="D159" r:id="VerifiedLink243"/>
+    <hyperlink ref="D160" r:id="VerifiedLink244"/>
+    <hyperlink ref="D161" r:id="VerifiedLink245"/>
+    <hyperlink ref="D162" r:id="VerifiedLink246"/>
+    <hyperlink ref="D163" r:id="VerifiedLink247"/>
+    <hyperlink ref="D164" r:id="VerifiedLink248"/>
+    <hyperlink ref="D165" r:id="VerifiedLink249"/>
+    <hyperlink ref="D166" r:id="VerifiedLink250"/>
+    <hyperlink ref="D167" r:id="VerifiedLink251"/>
+    <hyperlink ref="D168" r:id="VerifiedLink252"/>
+    <hyperlink ref="D169" r:id="VerifiedLink253"/>
+    <hyperlink ref="D170" r:id="VerifiedLink254"/>
+    <hyperlink ref="D171" r:id="VerifiedLink255"/>
+    <hyperlink ref="D172" r:id="VerifiedLink256"/>
+    <hyperlink ref="D185" r:id="VerifiedLink257"/>
+    <hyperlink ref="D186" r:id="VerifiedLink258"/>
+    <hyperlink ref="D191" r:id="VerifiedLink259"/>
+    <hyperlink ref="D192" r:id="VerifiedLink260"/>
+    <hyperlink ref="D198" r:id="VerifiedLink261"/>
+    <hyperlink ref="D199" r:id="VerifiedLink262"/>
+    <hyperlink ref="D200" r:id="VerifiedLink263"/>
+    <hyperlink ref="D201" r:id="VerifiedLink264"/>
+    <hyperlink ref="D202" r:id="VerifiedLink265"/>
+    <hyperlink ref="D203" r:id="VerifiedLink266"/>
+    <hyperlink ref="D204" r:id="VerifiedLink267"/>
+    <hyperlink ref="D205" r:id="VerifiedLink268"/>
+    <hyperlink ref="D206" r:id="VerifiedLink269"/>
+    <hyperlink ref="D207" r:id="VerifiedLink270"/>
+    <hyperlink ref="D208" r:id="VerifiedLink271"/>
+    <hyperlink ref="D209" r:id="VerifiedLink272"/>
+    <hyperlink ref="D228" r:id="VerifiedLink273"/>
+    <hyperlink ref="D229" r:id="VerifiedLink274"/>
+    <hyperlink ref="D234" r:id="VerifiedLink275"/>
+    <hyperlink ref="D235" r:id="VerifiedLink276"/>
+    <hyperlink ref="D236" r:id="VerifiedLink277"/>
+    <hyperlink ref="D237" r:id="VerifiedLink278"/>
+    <hyperlink ref="D238" r:id="VerifiedLink279"/>
+    <hyperlink ref="D239" r:id="VerifiedLink280"/>
+    <hyperlink ref="D240" r:id="VerifiedLink281"/>
+    <hyperlink ref="D241" r:id="VerifiedLink282"/>
+    <hyperlink ref="D242" r:id="VerifiedLink283"/>
+    <hyperlink ref="D243" r:id="VerifiedLink284"/>
+    <hyperlink ref="D244" r:id="VerifiedLink285"/>
+    <hyperlink ref="D245" r:id="VerifiedLink286"/>
+    <hyperlink ref="D246" r:id="VerifiedLink287"/>
+    <hyperlink ref="D253" r:id="VerifiedLink288"/>
+    <hyperlink ref="D254" r:id="VerifiedLink289"/>
+    <hyperlink ref="D259" r:id="VerifiedLink290"/>
+    <hyperlink ref="D260" r:id="VerifiedLink291"/>
+    <hyperlink ref="D261" r:id="VerifiedLink292"/>
+    <hyperlink ref="D262" r:id="VerifiedLink293"/>
+    <hyperlink ref="D263" r:id="VerifiedLink294"/>
+    <hyperlink ref="D264" r:id="VerifiedLink295"/>
+    <hyperlink ref="D265" r:id="VerifiedLink296"/>
+    <hyperlink ref="D266" r:id="VerifiedLink297"/>
+    <hyperlink ref="D267" r:id="VerifiedLink298"/>
+    <hyperlink ref="D268" r:id="VerifiedLink299"/>
+    <hyperlink ref="D269" r:id="VerifiedLink300"/>
+    <hyperlink ref="D270" r:id="VerifiedLink301"/>
+    <hyperlink ref="D271" r:id="VerifiedLink302"/>
+    <hyperlink ref="D278" r:id="VerifiedLink303"/>
+    <hyperlink ref="D279" r:id="VerifiedLink304"/>
+    <hyperlink ref="D280" r:id="VerifiedLink305"/>
+    <hyperlink ref="D285" r:id="VerifiedLink306"/>
+    <hyperlink ref="D286" r:id="VerifiedLink307"/>
+    <hyperlink ref="D287" r:id="VerifiedLink308"/>
+    <hyperlink ref="D292" r:id="VerifiedLink309"/>
+    <hyperlink ref="D293" r:id="VerifiedLink310"/>
+    <hyperlink ref="D294" r:id="VerifiedLink311"/>
+    <hyperlink ref="D295" r:id="VerifiedLink312"/>
+    <hyperlink ref="D299" r:id="VerifiedLink313"/>
+    <hyperlink ref="D300" r:id="VerifiedLink314"/>
+    <hyperlink ref="D301" r:id="VerifiedLink315"/>
+    <hyperlink ref="D302" r:id="VerifiedLink316"/>
+    <hyperlink ref="D303" r:id="VerifiedLink317"/>
+    <hyperlink ref="D304" r:id="VerifiedLink318"/>
+    <hyperlink ref="D305" r:id="VerifiedLink319"/>
+    <hyperlink ref="D306" r:id="VerifiedLink320"/>
+    <hyperlink ref="D307" r:id="VerifiedLink321"/>
+    <hyperlink ref="D308" r:id="VerifiedLink322"/>
+    <hyperlink ref="D309" r:id="VerifiedLink323"/>
+    <hyperlink ref="D310" r:id="VerifiedLink324"/>
+    <hyperlink ref="D311" r:id="VerifiedLink325"/>
+    <hyperlink ref="D312" r:id="VerifiedLink326"/>
+    <hyperlink ref="D313" r:id="VerifiedLink327"/>
+    <hyperlink ref="D314" r:id="VerifiedLink328"/>
+    <hyperlink ref="D315" r:id="VerifiedLink329"/>
+    <hyperlink ref="D317" r:id="VerifiedLink330"/>
+    <hyperlink ref="D319" r:id="VerifiedLink331"/>
+    <hyperlink ref="D320" r:id="VerifiedLink332"/>
+    <hyperlink ref="D321" r:id="VerifiedLink333"/>
+    <hyperlink ref="D326" r:id="VerifiedLink334"/>
+    <hyperlink ref="D327" r:id="VerifiedLink335"/>
+    <hyperlink ref="D328" r:id="VerifiedLink336"/>
+    <hyperlink ref="D332" r:id="VerifiedLink337"/>
+    <hyperlink ref="D333" r:id="VerifiedLink338"/>
+    <hyperlink ref="D334" r:id="VerifiedLink339"/>
+    <hyperlink ref="D335" r:id="VerifiedLink340"/>
+    <hyperlink ref="D336" r:id="VerifiedLink341"/>
+    <hyperlink ref="D337" r:id="VerifiedLink342"/>
+    <hyperlink ref="D338" r:id="VerifiedLink343"/>
+    <hyperlink ref="D340" r:id="VerifiedLink344"/>
+    <hyperlink ref="D341" r:id="VerifiedLink345"/>
+    <hyperlink ref="D342" r:id="VerifiedLink346"/>
+    <hyperlink ref="D343" r:id="VerifiedLink347"/>
+    <hyperlink ref="D344" r:id="VerifiedLink348"/>
+    <hyperlink ref="D345" r:id="VerifiedLink349"/>
+    <hyperlink ref="D346" r:id="VerifiedLink350"/>
+    <hyperlink ref="D347" r:id="VerifiedLink351"/>
+    <hyperlink ref="D348" r:id="VerifiedLink352"/>
+    <hyperlink ref="D349" r:id="VerifiedLink353"/>
+    <hyperlink ref="D350" r:id="VerifiedLink354"/>
+    <hyperlink ref="D351" r:id="VerifiedLink355"/>
+    <hyperlink ref="D352" r:id="VerifiedLink356"/>
+    <hyperlink ref="D353" r:id="VerifiedLink357"/>
+    <hyperlink ref="D354" r:id="VerifiedLink358"/>
+    <hyperlink ref="D355" r:id="VerifiedLink359"/>
+    <hyperlink ref="D356" r:id="VerifiedLink360"/>
+    <hyperlink ref="D357" r:id="VerifiedLink362"/>
+    <hyperlink ref="D358" r:id="VerifiedLink363"/>
+    <hyperlink ref="D359" r:id="VerifiedLink364"/>
+    <hyperlink ref="D360" r:id="VerifiedLink365"/>
+    <hyperlink ref="D361" r:id="VerifiedLink366"/>
+    <hyperlink ref="D362" r:id="VerifiedLink367"/>
+    <hyperlink ref="D363" r:id="VerifiedLink368"/>
+    <hyperlink ref="D364" r:id="VerifiedLink369"/>
+    <hyperlink ref="D365" r:id="VerifiedLink370"/>
+    <hyperlink ref="D366" r:id="VerifiedLink371"/>
+    <hyperlink ref="D367" r:id="VerifiedLink372"/>
+    <hyperlink ref="D368" r:id="VerifiedLink373"/>
+    <hyperlink ref="D369" r:id="VerifiedLink374"/>
+    <hyperlink ref="D370" r:id="VerifiedLink375"/>
+    <hyperlink ref="D371" r:id="VerifiedLink376"/>
+    <hyperlink ref="D372" r:id="VerifiedLink377"/>
+    <hyperlink ref="D373" r:id="VerifiedLink378"/>
+    <hyperlink ref="D374" r:id="VerifiedLink379"/>
+    <hyperlink ref="D375" r:id="VerifiedLink380"/>
+    <hyperlink ref="D376" r:id="VerifiedLink381"/>
+    <hyperlink ref="D377" r:id="VerifiedLink382"/>
+    <hyperlink ref="D378" r:id="VerifiedLink383"/>
+    <hyperlink ref="D379" r:id="VerifiedLink384"/>
+    <hyperlink ref="D380" r:id="VerifiedLink385"/>
+    <hyperlink ref="D381" r:id="VerifiedLink386"/>
+    <hyperlink ref="D382" r:id="VerifiedLink388"/>
+    <hyperlink ref="D383" r:id="VerifiedLink389"/>
+    <hyperlink ref="D384" r:id="VerifiedLink390"/>
+    <hyperlink ref="D385" r:id="VerifiedLink391"/>
+    <hyperlink ref="D386" r:id="VerifiedLink392"/>
+    <hyperlink ref="D387" r:id="VerifiedLink393"/>
+    <hyperlink ref="D388" r:id="VerifiedLink394"/>
+    <hyperlink ref="D389" r:id="VerifiedLink395"/>
+    <hyperlink ref="D390" r:id="VerifiedLink396"/>
+    <hyperlink ref="D391" r:id="VerifiedLink397"/>
+    <hyperlink ref="D392" r:id="VerifiedLink398"/>
+    <hyperlink ref="D393" r:id="VerifiedLink399"/>
+    <hyperlink ref="D394" r:id="VerifiedLink400"/>
+    <hyperlink ref="D395" r:id="VerifiedLink401"/>
+    <hyperlink ref="D396" r:id="VerifiedLink402"/>
+    <hyperlink ref="D397" r:id="VerifiedLink403"/>
+    <hyperlink ref="D398" r:id="VerifiedLink404"/>
+    <hyperlink ref="D399" r:id="VerifiedLink405"/>
+    <hyperlink ref="D400" r:id="VerifiedLink406"/>
+    <hyperlink ref="D401" r:id="VerifiedLink407"/>
+    <hyperlink ref="D402" r:id="VerifiedLink408"/>
+    <hyperlink ref="D403" r:id="VerifiedLink409"/>
+    <hyperlink ref="D404" r:id="VerifiedLink410"/>
+    <hyperlink ref="D405" r:id="VerifiedLink411"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="Rc457a0efe6d44402"/>
+    <tablePart r:id="R9df4cb9b5947404c"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF234B65"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="19" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>Observable execution metrics</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
-      <x:c r="K1" s="5"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Input tokens are cumulative conversation replay, often cached, not unique research volume. Output tokens may include billed reasoning. Model latency sums overlap other activity and are not an exclusive wall-time breakdown. Empty tool statistics were not normalized for that run; see chronology links.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
-      <x:c r="J2" s="7"/>
-      <x:c r="K2" s="7"/>
-    </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="7"/>
-      <x:c r="B3" s="7"/>
-      <x:c r="C3" s="7"/>
-      <x:c r="D3" s="7"/>
-      <x:c r="E3" s="7"/>
-      <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7"/>
-      <x:c r="H3" s="7"/>
-      <x:c r="I3" s="7"/>
-      <x:c r="J3" s="7"/>
-      <x:c r="K3" s="7"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="C4" s="3"/>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="F4" s="3"/>
-      <x:c r="G4" s="3"/>
-      <x:c r="H4" s="3"/>
-      <x:c r="I4" s="3"/>
-      <x:c r="J4" s="3"/>
-      <x:c r="K4" s="3"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Run</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>Entity</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>Model calls</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="str">
-        <x:v>Input tokens</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="str">
-        <x:v>Cache-read tokens</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="str">
-        <x:v>Output tokens</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="str">
-        <x:v>Model latency sum</x:v>
-      </x:c>
-      <x:c r="H5" s="9" t="str">
-        <x:v>read_file calls</x:v>
-      </x:c>
-      <x:c r="I5" s="9" t="str">
-        <x:v>Exact repeat reads</x:v>
-      </x:c>
-      <x:c r="J5" s="9" t="str">
-        <x:v>Multi-tool batches</x:v>
-      </x:c>
-      <x:c r="K5" s="9" t="str">
-        <x:v>Largest batch</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="40" customHeight="1">
-      <x:c r="A6" s="3" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="B6" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C6" s="29" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D6" s="29" t="n">
-        <x:v>7510383</x:v>
-      </x:c>
-      <x:c r="E6" s="29" t="n">
-        <x:v>7032448</x:v>
-      </x:c>
-      <x:c r="F6" s="29" t="n">
-        <x:v>55061</x:v>
-      </x:c>
-      <x:c r="G6" s="19" t="n">
-        <x:v>0.009685034880892123</x:v>
-      </x:c>
-      <x:c r="H6" s="3"/>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
-      <x:c r="K6" s="3"/>
-    </x:row>
-    <x:row r="7" ht="40" customHeight="1">
-      <x:c r="A7" s="10" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>Todd Greer</x:v>
-      </x:c>
-      <x:c r="C7" s="30" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D7" s="30" t="n">
-        <x:v>4480655</x:v>
-      </x:c>
-      <x:c r="E7" s="30" t="n">
-        <x:v>3992448</x:v>
-      </x:c>
-      <x:c r="F7" s="30" t="n">
-        <x:v>49977</x:v>
-      </x:c>
-      <x:c r="G7" s="20" t="n">
-        <x:v>0.008370818903430416</x:v>
-      </x:c>
-      <x:c r="H7" s="10"/>
-      <x:c r="I7" s="10"/>
-      <x:c r="J7" s="10"/>
-      <x:c r="K7" s="10"/>
-    </x:row>
-    <x:row r="8" ht="40" customHeight="1">
-      <x:c r="A8" s="3" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D8" s="29" t="n">
-        <x:v>4530300</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="n">
-        <x:v>3682736</x:v>
-      </x:c>
-      <x:c r="F8" s="29" t="n">
-        <x:v>22772</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="n">
-        <x:v>0.004214679073551519</x:v>
-      </x:c>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
-    </x:row>
-    <x:row r="9" ht="40" customHeight="1">
-      <x:c r="A9" s="10" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>Beth Smith</x:v>
-      </x:c>
-      <x:c r="C9" s="30" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="30" t="n">
-        <x:v>1167061</x:v>
-      </x:c>
-      <x:c r="E9" s="30" t="n">
-        <x:v>768581</x:v>
-      </x:c>
-      <x:c r="F9" s="30" t="n">
-        <x:v>8674</x:v>
-      </x:c>
-      <x:c r="G9" s="20" t="n">
-        <x:v>0.0011590935344510298</x:v>
-      </x:c>
-      <x:c r="H9" s="10"/>
-      <x:c r="I9" s="10"/>
-      <x:c r="J9" s="10"/>
-      <x:c r="K9" s="10"/>
-    </x:row>
-    <x:row r="10" ht="40" customHeight="1">
-      <x:c r="A10" s="3" t="str">
-        <x:v>P3</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="n">
-        <x:v>5006007</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="n">
-        <x:v>4194375</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="n">
-        <x:v>25581</x:v>
-      </x:c>
-      <x:c r="G10" s="19" t="n">
-        <x:v>0.0036496065914306437</x:v>
-      </x:c>
-      <x:c r="H10" s="3" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I10" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="3" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="40" customHeight="1">
-      <x:c r="A11" s="10" t="str">
-        <x:v>P3</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>Beth Smith</x:v>
-      </x:c>
-      <x:c r="C11" s="30" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D11" s="30" t="n">
-        <x:v>6105419</x:v>
-      </x:c>
-      <x:c r="E11" s="30" t="n">
-        <x:v>5127164</x:v>
-      </x:c>
-      <x:c r="F11" s="30" t="n">
-        <x:v>37957</x:v>
-      </x:c>
-      <x:c r="G11" s="20" t="n">
-        <x:v>0.005133670711339046</x:v>
-      </x:c>
-      <x:c r="H11" s="10" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I11" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="10" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K11" s="10" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="40" customHeight="1">
-      <x:c r="A12" s="3" t="str">
-        <x:v>P4</x:v>
-      </x:c>
-      <x:c r="B12" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="n">
-        <x:v>8713627</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="n">
-        <x:v>7550592</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="n">
-        <x:v>109892</x:v>
-      </x:c>
-      <x:c r="G12" s="19" t="n">
-        <x:v>0.019005992113215377</x:v>
-      </x:c>
-      <x:c r="H12" s="3" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I12" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J12" s="3" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K12" s="3" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="40" customHeight="1">
-      <x:c r="A13" s="10" t="str">
-        <x:v>P4</x:v>
-      </x:c>
-      <x:c r="B13" s="10" t="str">
-        <x:v>Todd Greer</x:v>
-      </x:c>
-      <x:c r="C13" s="30" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D13" s="30" t="n">
-        <x:v>8506031</x:v>
-      </x:c>
-      <x:c r="E13" s="30" t="n">
-        <x:v>7564800</x:v>
-      </x:c>
-      <x:c r="F13" s="30" t="n">
-        <x:v>92508</x:v>
-      </x:c>
-      <x:c r="G13" s="20" t="n">
-        <x:v>0.015454453211291198</x:v>
-      </x:c>
-      <x:c r="H13" s="10" t="n">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="I13" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J13" s="10" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K13" s="10" t="n">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="40" customHeight="1">
-      <x:c r="A14" s="3" t="str">
-        <x:v>P5</x:v>
-      </x:c>
-      <x:c r="B14" s="3" t="str">
-        <x:v>Premier Gastroenterology</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D14" s="29" t="n">
-        <x:v>6774676</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="n">
-        <x:v>6408994</x:v>
-      </x:c>
-      <x:c r="F14" s="29" t="n">
-        <x:v>29724</x:v>
-      </x:c>
-      <x:c r="G14" s="19" t="n">
-        <x:v>0.003882188445156013</x:v>
-      </x:c>
-      <x:c r="H14" s="3" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="I14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J14" s="3" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="40" customHeight="1">
-      <x:c r="A15" s="10" t="str">
-        <x:v>P5</x:v>
-      </x:c>
-      <x:c r="B15" s="10" t="str">
-        <x:v>Todd Greer</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D15" s="30" t="n">
-        <x:v>3282972</x:v>
-      </x:c>
-      <x:c r="E15" s="30" t="n">
-        <x:v>2923560</x:v>
-      </x:c>
-      <x:c r="F15" s="30" t="n">
-        <x:v>12707</x:v>
-      </x:c>
-      <x:c r="G15" s="20" t="n">
-        <x:v>0.001884106977765138</x:v>
-      </x:c>
-      <x:c r="H15" s="10" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="I15" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="10" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="K15" s="10" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="40" customHeight="1">
-      <x:c r="A16" s="3" t="str">
-        <x:v>Z1</x:v>
-      </x:c>
-      <x:c r="B16" s="3" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D16" s="29" t="n">
-        <x:v>6346215</x:v>
-      </x:c>
-      <x:c r="E16" s="29" t="n">
-        <x:v>5812736</x:v>
-      </x:c>
-      <x:c r="F16" s="29" t="n">
-        <x:v>51179</x:v>
-      </x:c>
-      <x:c r="G16" s="19" t="n">
-        <x:v>0.009441726154567462</x:v>
-      </x:c>
-      <x:c r="H16" s="3"/>
-      <x:c r="I16" s="3"/>
-      <x:c r="J16" s="3"/>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" ht="40" customHeight="1">
-      <x:c r="A17" s="10" t="str">
-        <x:v>Z1</x:v>
-      </x:c>
-      <x:c r="B17" s="10" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C17" s="30" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D17" s="30" t="n">
-        <x:v>4402831</x:v>
-      </x:c>
-      <x:c r="E17" s="30" t="n">
-        <x:v>3946112</x:v>
-      </x:c>
-      <x:c r="F17" s="30" t="n">
-        <x:v>41241</x:v>
-      </x:c>
-      <x:c r="G17" s="20" t="n">
-        <x:v>0.007511529303608566</x:v>
-      </x:c>
-      <x:c r="H17" s="10"/>
-      <x:c r="I17" s="10"/>
-      <x:c r="J17" s="10"/>
-      <x:c r="K17" s="10"/>
-    </x:row>
-    <x:row r="18" ht="40" customHeight="1">
-      <x:c r="A18" s="3" t="str">
-        <x:v>Z1</x:v>
-      </x:c>
-      <x:c r="B18" s="3" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D18" s="29" t="n">
-        <x:v>6897840</x:v>
-      </x:c>
-      <x:c r="E18" s="29" t="n">
-        <x:v>6265344</x:v>
-      </x:c>
-      <x:c r="F18" s="29" t="n">
-        <x:v>48405</x:v>
-      </x:c>
-      <x:c r="G18" s="19" t="n">
-        <x:v>0.01044284500718479</x:v>
-      </x:c>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" ht="32" customHeight="1">
-      <x:c r="A19" s="10" t="str">
-        <x:v>Z2</x:v>
-      </x:c>
-      <x:c r="B19" s="10" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C19" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E19" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F19" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="10"/>
-      <x:c r="I19" s="10"/>
-      <x:c r="J19" s="10"/>
-      <x:c r="K19" s="10"/>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
-      <x:c r="A20" s="3" t="str">
-        <x:v>Z2</x:v>
-      </x:c>
-      <x:c r="B20" s="3" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E20" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F20" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="3"/>
-      <x:c r="I20" s="3"/>
-      <x:c r="J20" s="3"/>
-      <x:c r="K20" s="3"/>
-    </x:row>
-    <x:row r="21" ht="40" customHeight="1">
-      <x:c r="A21" s="10" t="str">
-        <x:v>Z2</x:v>
-      </x:c>
-      <x:c r="B21" s="10" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D21" s="30" t="n">
-        <x:v>7125036</x:v>
-      </x:c>
-      <x:c r="E21" s="30" t="n">
-        <x:v>6447488</x:v>
-      </x:c>
-      <x:c r="F21" s="30" t="n">
-        <x:v>54779</x:v>
-      </x:c>
-      <x:c r="G21" s="20" t="n">
-        <x:v>0.016823730784125034</x:v>
-      </x:c>
-      <x:c r="H21" s="10"/>
-      <x:c r="I21" s="10"/>
-      <x:c r="J21" s="10"/>
-      <x:c r="K21" s="10"/>
-    </x:row>
-    <x:row r="22" ht="32" customHeight="1">
-      <x:c r="A22" s="3" t="str">
-        <x:v>Z3</x:v>
-      </x:c>
-      <x:c r="B22" s="3" t="str">
-        <x:v>Tom Anthony</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E22" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F22" s="29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="3"/>
-      <x:c r="I22" s="3"/>
-      <x:c r="J22" s="3"/>
-      <x:c r="K22" s="3"/>
-    </x:row>
-    <x:row r="23" ht="32" customHeight="1">
-      <x:c r="A23" s="10" t="str">
-        <x:v>Z3</x:v>
-      </x:c>
-      <x:c r="B23" s="10" t="str">
-        <x:v>Kelly W.</x:v>
-      </x:c>
-      <x:c r="C23" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E23" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F23" s="30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="10"/>
-      <x:c r="I23" s="10"/>
-      <x:c r="J23" s="10"/>
-      <x:c r="K23" s="10"/>
-    </x:row>
-    <x:row r="24" ht="40" customHeight="1">
-      <x:c r="A24" s="3" t="str">
-        <x:v>Z3</x:v>
-      </x:c>
-      <x:c r="B24" s="3" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C24" s="29" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D24" s="29" t="n">
-        <x:v>3276036</x:v>
-      </x:c>
-      <x:c r="E24" s="29" t="n">
-        <x:v>3098752</x:v>
-      </x:c>
-      <x:c r="F24" s="29" t="n">
-        <x:v>15038</x:v>
-      </x:c>
-      <x:c r="G24" s="19" t="n">
-        <x:v>0.0011104480453839104</x:v>
-      </x:c>
-      <x:c r="H24" s="3"/>
-      <x:c r="I24" s="3"/>
-      <x:c r="J24" s="3"/>
-      <x:c r="K24" s="3"/>
-    </x:row>
-    <x:row r="25" ht="40" customHeight="1">
-      <x:c r="A25" s="10" t="str">
-        <x:v>Z4</x:v>
-      </x:c>
-      <x:c r="B25" s="10" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C25" s="30" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D25" s="30" t="n">
-        <x:v>1456640</x:v>
-      </x:c>
-      <x:c r="E25" s="30" t="n">
-        <x:v>1249728</x:v>
-      </x:c>
-      <x:c r="F25" s="30" t="n">
-        <x:v>20459</x:v>
-      </x:c>
-      <x:c r="G25" s="20" t="n">
-        <x:v>0.0008444537712192094</x:v>
-      </x:c>
-      <x:c r="H25" s="10"/>
-      <x:c r="I25" s="10"/>
-      <x:c r="J25" s="10"/>
-      <x:c r="K25" s="10"/>
-    </x:row>
-    <x:row r="26" ht="40" customHeight="1">
-      <x:c r="A26" s="3" t="str">
-        <x:v>Z5</x:v>
-      </x:c>
-      <x:c r="B26" s="3" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C26" s="29" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D26" s="29" t="n">
-        <x:v>1686303</x:v>
-      </x:c>
-      <x:c r="E26" s="29" t="n">
-        <x:v>1583872</x:v>
-      </x:c>
-      <x:c r="F26" s="29" t="n">
-        <x:v>15198</x:v>
-      </x:c>
-      <x:c r="G26" s="19" t="n">
-        <x:v>0.0014831790918860524</x:v>
-      </x:c>
-      <x:c r="H26" s="3"/>
-      <x:c r="I26" s="3"/>
-      <x:c r="J26" s="3"/>
-      <x:c r="K26" s="3"/>
-    </x:row>
-    <x:row r="27" ht="40" customHeight="1">
-      <x:c r="A27" s="10" t="str">
-        <x:v>Z5</x:v>
-      </x:c>
-      <x:c r="B27" s="10" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C27" s="30" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D27" s="30" t="n">
-        <x:v>9294601</x:v>
-      </x:c>
-      <x:c r="E27" s="30" t="n">
-        <x:v>8012800</x:v>
-      </x:c>
-      <x:c r="F27" s="30" t="n">
-        <x:v>70776</x:v>
-      </x:c>
-      <x:c r="G27" s="20" t="n">
-        <x:v>0.023875946789703447</x:v>
-      </x:c>
-      <x:c r="H27" s="10"/>
-      <x:c r="I27" s="10"/>
-      <x:c r="J27" s="10"/>
-      <x:c r="K27" s="10"/>
-    </x:row>
-    <x:row r="28" ht="40" customHeight="1">
-      <x:c r="A28" s="3" t="str">
-        <x:v>Z5</x:v>
-      </x:c>
-      <x:c r="B28" s="3" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C28" s="29" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D28" s="29" t="n">
-        <x:v>11427762</x:v>
-      </x:c>
-      <x:c r="E28" s="29" t="n">
-        <x:v>10770176</x:v>
-      </x:c>
-      <x:c r="F28" s="29" t="n">
-        <x:v>118748</x:v>
-      </x:c>
-      <x:c r="G28" s="19" t="n">
-        <x:v>0.013295368958327648</x:v>
-      </x:c>
-      <x:c r="H28" s="3"/>
-      <x:c r="I28" s="3"/>
-      <x:c r="J28" s="3"/>
-      <x:c r="K28" s="3"/>
-    </x:row>
-    <x:row r="29" ht="40" customHeight="1">
-      <x:c r="A29" s="10" t="str">
-        <x:v>Z6</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="str">
-        <x:v>Zafran Security</x:v>
-      </x:c>
-      <x:c r="C29" s="30" t="n">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D29" s="30" t="n">
-        <x:v>7091181</x:v>
-      </x:c>
-      <x:c r="E29" s="30" t="n">
-        <x:v>5410956</x:v>
-      </x:c>
-      <x:c r="F29" s="30" t="n">
-        <x:v>84270</x:v>
-      </x:c>
-      <x:c r="G29" s="20" t="n">
-        <x:v>0.009057984897781689</x:v>
-      </x:c>
-      <x:c r="H29" s="10"/>
-      <x:c r="I29" s="10"/>
-      <x:c r="J29" s="10"/>
-      <x:c r="K29" s="10"/>
-    </x:row>
-    <x:row r="30" ht="40" customHeight="1">
-      <x:c r="A30" s="3" t="str">
-        <x:v>Z6</x:v>
-      </x:c>
-      <x:c r="B30" s="3" t="str">
-        <x:v>Nick Fisher</x:v>
-      </x:c>
-      <x:c r="C30" s="29" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D30" s="29" t="n">
-        <x:v>9506277</x:v>
-      </x:c>
-      <x:c r="E30" s="29" t="n">
-        <x:v>7285675</x:v>
-      </x:c>
-      <x:c r="F30" s="29" t="n">
-        <x:v>70199</x:v>
-      </x:c>
-      <x:c r="G30" s="19" t="n">
-        <x:v>0.00889480455486962</x:v>
-      </x:c>
-      <x:c r="H30" s="3"/>
-      <x:c r="I30" s="3"/>
-      <x:c r="J30" s="3"/>
-      <x:c r="K30" s="3"/>
-    </x:row>
-    <x:row r="31" ht="40" customHeight="1">
-      <x:c r="A31" s="10" t="str">
-        <x:v>Z6</x:v>
-      </x:c>
-      <x:c r="B31" s="10" t="str">
-        <x:v>Vari Kaur</x:v>
-      </x:c>
-      <x:c r="C31" s="30" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D31" s="30" t="n">
-        <x:v>10973017</x:v>
-      </x:c>
-      <x:c r="E31" s="30" t="n">
-        <x:v>8361253</x:v>
-      </x:c>
-      <x:c r="F31" s="30" t="n">
-        <x:v>104293</x:v>
-      </x:c>
-      <x:c r="G31" s="20" t="n">
-        <x:v>0.01355818440767406</x:v>
-      </x:c>
-      <x:c r="H31" s="10"/>
-      <x:c r="I31" s="10"/>
-      <x:c r="J31" s="10"/>
-      <x:c r="K31" s="10"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:K1"/>
-    <x:mergeCell ref="A2:K3"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc48b787638c345f7"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF234B65"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="19" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="5" t="str">
+        <v>Observable execution metrics</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>Input tokens are cumulative conversation replay, often cached, not unique research volume. Output tokens may include billed reasoning. Model latency sums overlap other activity and are not an exclusive wall-time breakdown. Empty tool statistics were not normalized for that run; see chronology links.</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="str">
+        <v>Run</v>
+      </c>
+      <c r="B5" s="9" t="str">
+        <v>Entity</v>
+      </c>
+      <c r="C5" s="9" t="str">
+        <v>Model calls</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <v>Input tokens</v>
+      </c>
+      <c r="E5" s="9" t="str">
+        <v>Cache-read tokens</v>
+      </c>
+      <c r="F5" s="9" t="str">
+        <v>Output tokens</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <v>Model latency sum</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <v>read_file calls</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <v>Exact repeat reads</v>
+      </c>
+      <c r="J5" s="9" t="str">
+        <v>Multi-tool batches</v>
+      </c>
+      <c r="K5" s="9" t="str">
+        <v>Largest batch</v>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="3" t="str">
+        <v>P1</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>78</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>7510383</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>7032448</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>55061</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.009685034880892123</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="10" t="str">
+        <v>P1</v>
+      </c>
+      <c r="B7" s="10" t="str">
+        <v>Todd Greer</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>48</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>4480655</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>3992448</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>49977</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>0.008370818903430416</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="3" t="str">
+        <v>P2</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>4530300</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>3682736</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>22772</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.004214679073551519</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="10" t="str">
+        <v>P2</v>
+      </c>
+      <c r="B9" s="10" t="str">
+        <v>Beth Smith</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>1167061</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>768581</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>8674</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.0011590935344510298</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="3" t="str">
+        <v>P3</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>55</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>5006007</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>4194375</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>25581</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.0036496065914306437</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="10" t="str">
+        <v>P3</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <v>Beth Smith</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>61</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>6105419</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>5127164</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>37957</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.005133670711339046</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="3" t="str">
+        <v>P4</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>89</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>8713627</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>7550592</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>109892</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.019005992113215377</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="10" t="str">
+        <v>P4</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <v>Todd Greer</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>8506031</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>7564800</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>92508</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.015454453211291198</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="3" t="str">
+        <v>P5</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <v>Premier Gastroenterology</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>66</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>6774676</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>6408994</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>29724</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.003882188445156013</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="10" t="str">
+        <v>P5</v>
+      </c>
+      <c r="B15" s="10" t="str">
+        <v>Todd Greer</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>42</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>3282972</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>2923560</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>12707</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>0.001884106977765138</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="3" t="str">
+        <v>Z1</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>61</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>6346215</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>5812736</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>51179</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.009441726154567462</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="10" t="str">
+        <v>Z1</v>
+      </c>
+      <c r="B17" s="10" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>44</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>4402831</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>3946112</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>41241</v>
+      </c>
+      <c r="G17" s="20" t="n">
+        <v>0.007511529303608566</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="3" t="str">
+        <v>Z1</v>
+      </c>
+      <c r="B18" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>80</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>6897840</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>6265344</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>48405</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.01044284500718479</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="10" t="str">
+        <v>Z2</v>
+      </c>
+      <c r="B19" s="10" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="3" t="str">
+        <v>Z2</v>
+      </c>
+      <c r="B20" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="10" t="str">
+        <v>Z2</v>
+      </c>
+      <c r="B21" s="10" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>68</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>7125036</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>6447488</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>54779</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <v>0.016823730784125034</v>
+      </c>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="3" t="str">
+        <v>Z3</v>
+      </c>
+      <c r="B22" s="3" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="10" t="str">
+        <v>Z3</v>
+      </c>
+      <c r="B23" s="10" t="str">
+        <v>Kelly W.</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="3" t="str">
+        <v>Z3</v>
+      </c>
+      <c r="B24" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>3276036</v>
+      </c>
+      <c r="E24" s="29" t="n">
+        <v>3098752</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>15038</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.0011104480453839104</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="10" t="str">
+        <v>Z4</v>
+      </c>
+      <c r="B25" s="10" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>1456640</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>1249728</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>20459</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>0.0008444537712192094</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="3" t="str">
+        <v>Z5</v>
+      </c>
+      <c r="B26" s="3" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>1686303</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>1583872</v>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>15198</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0.0014831790918860524</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="10" t="str">
+        <v>Z5</v>
+      </c>
+      <c r="B27" s="10" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>89</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>9294601</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>8012800</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>70776</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>0.023875946789703447</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="3" t="str">
+        <v>Z5</v>
+      </c>
+      <c r="B28" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>124</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>11427762</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>10770176</v>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>118748</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>0.013295368958327648</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="10" t="str">
+        <v>Z6</v>
+      </c>
+      <c r="B29" s="10" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>79</v>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>7091181</v>
+      </c>
+      <c r="E29" s="30" t="n">
+        <v>5410956</v>
+      </c>
+      <c r="F29" s="30" t="n">
+        <v>84270</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0.009057984897781689</v>
+      </c>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="3" t="str">
+        <v>Z6</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>9506277</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>7285675</v>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>70199</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>0.00889480455486962</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="10" t="str">
+        <v>Z6</v>
+      </c>
+      <c r="B31" s="10" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>120</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>10973017</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>8361253</v>
+      </c>
+      <c r="F31" s="30" t="n">
+        <v>104293</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0.01355818440767406</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B32" s="3" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>51</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>5134226</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>4456865</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>42005</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>0.0037269259134228815</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B33" s="31" t="str">
+        <v>Vari Kaur</v>
+      </c>
+      <c r="C33" s="42" t="n">
+        <v>60</v>
+      </c>
+      <c r="D33" s="42" t="n">
+        <v>6275473</v>
+      </c>
+      <c r="E33" s="42" t="n">
+        <v>5591691</v>
+      </c>
+      <c r="F33" s="42" t="n">
+        <v>35604</v>
+      </c>
+      <c r="G33" s="38" t="n">
+        <v>0.004600416875007256</v>
+      </c>
+      <c r="H33" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="I33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="3" t="str">
+        <v>Z7</v>
+      </c>
+      <c r="B34" s="3" t="str">
+        <v>Nick Fisher</v>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>75</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>7301820</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>6315818</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>47665</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>0.00561840365011314</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B35" s="31" t="str">
+        <v>Zafran Security</v>
+      </c>
+      <c r="C35" s="42" t="n">
+        <v>86</v>
+      </c>
+      <c r="D35" s="42" t="n">
+        <v>7170188</v>
+      </c>
+      <c r="E35" s="42" t="n">
+        <v>6759424</v>
+      </c>
+      <c r="F35" s="42" t="n">
+        <v>56886</v>
+      </c>
+      <c r="G35" s="38" t="n">
+        <v>0.006401342648101423</v>
+      </c>
+      <c r="H35" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="I35" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="3" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B36" s="3" t="str">
+        <v>Tom Anthony</v>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>61</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>4760075</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>4345024</v>
+      </c>
+      <c r="F36" s="29" t="n">
+        <v>40689</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>0.005046711105743371</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="31" t="str">
+        <v>Z8</v>
+      </c>
+      <c r="B37" s="31" t="str">
+        <v>Sanaz Yashar</v>
+      </c>
+      <c r="C37" s="42" t="n">
+        <v>99</v>
+      </c>
+      <c r="D37" s="42" t="n">
+        <v>8656079</v>
+      </c>
+      <c r="E37" s="42" t="n">
+        <v>7966720</v>
+      </c>
+      <c r="F37" s="42" t="n">
+        <v>51556</v>
+      </c>
+      <c r="G37" s="38" t="n">
+        <v>0.01885840894488663</v>
+      </c>
+      <c r="H37" s="31" t="n">
+        <v>74</v>
+      </c>
+      <c r="I37" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="Ra3fb2ddfff2e48a7"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF234B65"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="135" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>How to read the comparison</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Current snapshot: 28 September 2026. All amounts in USD unless labelled AI Ark credits. This workbook is a decision aid grounded in retained run artifacts; it does not assign unsupported quality scores.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-    </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="7"/>
-      <x:c r="B3" s="7"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Topic</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>Definition / interpretation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="40" customHeight="1">
-      <x:c r="A6" s="3" t="str">
-        <x:v>Scope</x:v>
-      </x:c>
-      <x:c r="B6" s="3" t="str">
-        <x:v>11 substantive research attempts (5 Premier, 6 Zafran), plus three Muse setup failures. Premier baseline began September 27 UTC but September 28 in Asia/Kolkata. No new paid calls made for this report.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="54" customHeight="1">
-      <x:c r="A7" s="10" t="str">
-        <x:v>Recommendation</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>Use Grok 4.6 medium as current research-quality baseline; Muse xhigh remains a promising lower-cost account candidate, and Muse max has unique person-depth strengths. No model completed every formal lifecycle stage without issues.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="40" customHeight="1">
-      <x:c r="A8" s="3" t="str">
-        <x:v>Two workloads</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="str">
-        <x:v>Premier: Insight Health seller, one account plus one selected person (Todd or Beth). Zafran: Clue seller, account plus fixed Nick and Vari. Raw total costs across these workloads are not like-for-like.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="40" customHeight="1">
-      <x:c r="A9" s="10" t="str">
-        <x:v>Effort</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>medium/high/xhigh/max are the actual requested settings where checked. They are provider-specific controls, not equal hidden compute budgets. No private reasoning content is reconstructed.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="3" t="str">
-        <x:v>Resources versus runtime</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="str">
-        <x:v>Revision-24 resources and common retained context within each comparison; side-chat runtime fixes changed code between some launches. Muse also uses provider-specific tool/schema adaptations. Not a randomized model-only experiment.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="10" t="str">
-        <x:v>Wall time</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>Runs shows earliest research start to final research completion/failure/cancellation. Jobs overlap. Costs includes reconciliation and other listed paid work even if after research. Extra settlement time is in the report/run sources.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="54" customHeight="1">
-      <x:c r="A12" s="3" t="str">
-        <x:v>Settlement boundaries</x:v>
-      </x:c>
-      <x:c r="B12" s="3" t="str">
-        <x:v>P1 worker stop about31m22s including old continuation (approximate); P4 final no-op about51m46s; Z1 30m15.5s; Z5 57m55.2s; Z6 36m03.5s including failed reconciliation. These should not be confused with successful end-to-end duration.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="54" customHeight="1">
-      <x:c r="A13" s="10" t="str">
-        <x:v>Cost</x:v>
-      </x:c>
-      <x:c r="B13" s="10" t="str">
-        <x:v>Sum recorded researcher/provider result rows once; exclude estimate duplication. USD and AI Ark credits remain separate. P2 pending Exa, P1 possible in-flight continuation, Z2 failed call/probe leave unpriced uncertainty. No invoice reconciliation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="40" customHeight="1">
-      <x:c r="A14" s="3" t="str">
-        <x:v>Setup cost</x:v>
-      </x:c>
-      <x:c r="B14" s="3" t="str">
-        <x:v>S1 paid Head brief $0.118116; reused by later Premier runs and counted once. S2 tool-choice and S3 schema setup failures have no recorded priced research usage.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="40" customHeight="1">
-      <x:c r="A15" s="10" t="str">
-        <x:v>Findings</x:v>
-      </x:c>
-      <x:c r="B15" s="10" t="str">
-        <x:v>Authored dossier records are not all account claims. Typed AI Ark enrichment excluded from authored counts. Z2 has30 drafts but0 imported. P1 initial52 findings became60 through old continuations.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="54" customHeight="1">
-      <x:c r="A16" s="3" t="str">
-        <x:v>Quality method</x:v>
-      </x:c>
-      <x:c r="B16" s="3" t="str">
-        <x:v>Read initial and latest dossiers, source payloads, narratives and tool traces. Classify acquired-but-omitted, not-acquired-in-targeted-scan, unsupported inference, wrong ownership, bad conflict or incomplete output separately. No blanket loss percentage.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="40" customHeight="1">
-      <x:c r="A17" s="10" t="str">
-        <x:v>Narrative attribution</x:v>
-      </x:c>
-      <x:c r="B17" s="10" t="str">
-        <x:v>Researchers write initial account/contact narratives. Later focused reconciliation uses common Muse; its text is not proof of another researcher model’s writing quality. Draft failed writes are not published narratives.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="54" customHeight="1">
-      <x:c r="A18" s="3" t="str">
-        <x:v>Trace boundary</x:v>
-      </x:c>
-      <x:c r="B18" s="3" t="str">
-        <x:v>Model-call CSVs, public assignments, tool chronology and Langfuse links expose observable activity. Reasoning effort and billable output tokens do not reveal internal reasoning quality. ID-match checks do not prove every callback exported.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="40" customHeight="1">
-      <x:c r="A19" s="10" t="str">
-        <x:v>Source reliability</x:v>
-      </x:c>
-      <x:c r="B19" s="10" t="str">
-        <x:v>This assesses fidelity to retrieved sources, not independent proof that every public source is true. Dates and unknown affiliation are retained qualifications.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="40" customHeight="1">
-      <x:c r="A20" s="3" t="str">
-        <x:v>Missing data</x:v>
-      </x:c>
-      <x:c r="B20" s="3" t="str">
-        <x:v>Blank numeric milestone means unavailable or never reached, not zero time. Not produced / unavailable in Outputs is deliberate. Failed jobs may still have durable dossiers and narratives.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="40" customHeight="1">
-      <x:c r="A21" s="10" t="str">
-        <x:v>Next evaluation</x:v>
-      </x:c>
-      <x:c r="B21" s="10" t="str">
-        <x:v>Fix/replay deterministic completion, parent-reference and narrative/reconciliation contract failures against saved artifacts, then compare fixed-evidence authoring for fidelity before buying fresh discovery runs.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:B1"/>
-    <x:mergeCell ref="A2:B3"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0099d23a28014fec"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF234B65"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="135" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="5" t="str">
+        <v>How to read the comparison</v>
+      </c>
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>Current snapshot: 28 September 2026. All amounts in USD unless labelled AI Ark credits. This workbook is a decision aid grounded in retained run artifacts; it does not assign unsupported quality scores.</v>
+      </c>
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="str">
+        <v>Topic</v>
+      </c>
+      <c r="B5" s="9" t="str">
+        <v>Definition / interpretation</v>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="3" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <v>13 substantive attempts: 5 Premier and 8 Zafran, plus three setup failures. Latest update adds Muse xhigh same-person quality comparison and GLM final status/artifacts. No new paid research for this report.</v>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="10" t="str">
+        <v>Recommendation</v>
+      </c>
+      <c r="B7" s="10" t="str">
+        <v>Keep Grok 4.6 medium as quality baseline. Muse xhigh is cheaper/faster and strong on Nick, but account omissions and Vari wrong-employer attribution remain. Its retry completed all research and reconciliation after repairs; runtime differences limit model-only conclusions.</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="3" t="str">
+        <v>Two workloads</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <v>Premier: Insight Health seller, one account plus one selected person (Todd or Beth). Zafran: Clue seller, account plus fixed Nick and Vari. Raw total costs across these workloads are not like-for-like.</v>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="10" t="str">
+        <v>Effort</v>
+      </c>
+      <c r="B9" s="10" t="str">
+        <v>medium/high/xhigh/max are the actual requested settings where checked. They are provider-specific controls, not equal hidden compute budgets. No private reasoning content is reconstructed.</v>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="3" t="str">
+        <v>Resources versus runtime</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <v>Revision-24 resources and common retained context within each comparison; side-chat runtime fixes changed code between some launches. Muse also uses provider-specific tool/schema adaptations. Not a randomized model-only experiment.</v>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="10" t="str">
+        <v>Wall time</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <v>Runs shows earliest research start to final research completion/failure/cancellation. Jobs overlap. Costs includes reconciliation and other listed paid work even if after research. Extra settlement time is in the report/run sources.</v>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="3" t="str">
+        <v>Settlement boundaries</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <v>P1 worker stop about31m22s including old continuation (approximate); P4 final no-op about51m46s; Z1 30m15.5s; Z5 57m55.2s; Z6 36m03.5s including failed reconciliation. These should not be confused with successful end-to-end duration.</v>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="10" t="str">
+        <v>Cost</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <v>Sum recorded researcher/provider result rows once; exclude estimate duplication. USD and AI Ark credits remain separate. P2 pending Exa, P1 possible in-flight continuation, Z2 failed call/probe leave unpriced uncertainty. No invoice reconciliation.</v>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="3" t="str">
+        <v>Setup cost</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <v>S1 paid Head brief $0.118116; reused by later Premier runs and counted once. S2 tool-choice and S3 schema setup failures have no recorded priced research usage.</v>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="10" t="str">
+        <v>Findings</v>
+      </c>
+      <c r="B15" s="10" t="str">
+        <v>Authored dossier records are not all account claims. Typed AI Ark enrichment excluded from authored counts. Z2 has30 drafts but0 imported. P1 initial52 findings became60 through old continuations.</v>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="3" t="str">
+        <v>Quality method</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <v>Read initial and latest dossiers, source payloads, narratives and tool traces. Classify acquired-but-omitted, not-acquired-in-targeted-scan, unsupported inference, wrong ownership, bad conflict or incomplete output separately. No blanket loss percentage.</v>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="10" t="str">
+        <v>Narrative attribution</v>
+      </c>
+      <c r="B17" s="10" t="str">
+        <v>Researchers write initial account/contact narratives. Later focused reconciliation uses common Muse; its text is not proof of another researcher model’s writing quality. Draft failed writes are not published narratives.</v>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="3" t="str">
+        <v>Trace boundary</v>
+      </c>
+      <c r="B18" s="3" t="str">
+        <v>Model-call CSVs, public assignments, tool chronology and Langfuse links expose observable activity. Reasoning effort and billable output tokens do not reveal internal reasoning quality. ID-match checks do not prove every callback exported.</v>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="10" t="str">
+        <v>Source reliability</v>
+      </c>
+      <c r="B19" s="10" t="str">
+        <v>This assesses fidelity to retrieved sources, not independent proof that every public source is true. Dates and unknown affiliation are retained qualifications.</v>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="3" t="str">
+        <v>Missing data</v>
+      </c>
+      <c r="B20" s="3" t="str">
+        <v>Blank numeric milestone means unavailable or never reached, not zero time. Not produced / unavailable in Outputs is deliberate. Failed jobs may still have durable dossiers and narratives.</v>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="10" t="str">
+        <v>Next evaluation</v>
+      </c>
+      <c r="B21" s="10" t="str">
+        <v>Fix/replay deterministic completion, parent-reference and narrative/reconciliation contract failures against saved artifacts, then compare fixed-evidence authoring for fidelity before buying fresh discovery runs.</v>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="3" t="str">
+        <v>Latest retry audit</v>
+      </c>
+      <c r="B22" s="3" t="str">
+        <v>Z7 is Muse xhigh on the same Zafran/Nick/Vari workload: all109 authored findings reviewed, 20 comparative probes plus attribution/citation/import checks. Z8 adds GLM final lifecycle and artifacts only; Tom/Sanaz differ from the fixed comparison.</v>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="str">
+        <v>No complete truth set</v>
+      </c>
+      <c r="B23" s="31" t="str">
+        <v>At least five source-specific account omissions established for Z7; not a denominator for percentage recall. Grok also omitted useful evidence. Successful import/completion is not semantic validation.</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="Rbf0c034a08f24f85"/>
+  </tableParts>
+</worksheet>
 </file>